--- a/5_other_input_files/phantom_height_weight_organ_comparison.xlsx
+++ b/5_other_input_files/phantom_height_weight_organ_comparison.xlsx
@@ -18,7 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
   <fonts count="6">
     <font>
       <name val="Calibri"/>
@@ -115,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -137,6 +139,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -144,6 +149,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -509,18 +517,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I196"/>
+  <dimension ref="A1:M196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="3" customWidth="1" min="5" max="5"/>
-    <col width="27" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="3" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -546,44 +558,68 @@
       <c r="B4" s="4" t="n"/>
       <c r="C4" s="4" t="n"/>
       <c r="D4" s="4" t="n"/>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
       <c r="I4" s="6" t="n"/>
+      <c r="J4" s="6" t="n"/>
+      <c r="K4" s="6" t="n"/>
+      <c r="L4" s="6" t="n"/>
+      <c r="M4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr"/>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>ICRP145</t>
+          <t>ICRP145 density</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>ICRP145 mass</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
+          <t>Filipino density</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>Filipino mass</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
           <t>% Difference</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr"/>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>ICRP145</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>Filipino</t>
-        </is>
-      </c>
+      <c r="H5" s="7" t="inlineStr"/>
       <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>ICRP145 density</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>ICRP145 mass</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>Filipino density</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>Filipino mass</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
         <is>
           <t>% Difference</t>
         </is>
@@ -595,27 +631,31 @@
           <t>Height (cm)</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n">
+      <c r="B6" s="9" t="inlineStr"/>
+      <c r="C6" s="10" t="n">
         <v>176.004707</v>
       </c>
-      <c r="C6" s="9" t="n">
+      <c r="D6" s="9" t="inlineStr"/>
+      <c r="E6" s="10" t="n">
         <v>163.349998</v>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="F6" s="10" t="n">
         <v>-7.189983276981335</v>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>Height (cm)</t>
         </is>
       </c>
-      <c r="G6" s="9" t="n">
+      <c r="I6" s="9" t="inlineStr"/>
+      <c r="J6" s="10" t="n">
         <v>163.01744</v>
       </c>
-      <c r="H6" s="9" t="n">
+      <c r="K6" s="9" t="inlineStr"/>
+      <c r="L6" s="10" t="n">
         <v>151.799996</v>
       </c>
-      <c r="I6" s="9" t="n">
+      <c r="M6" s="10" t="n">
         <v>-6.881131245834784</v>
       </c>
     </row>
@@ -625,47 +665,55 @@
           <t>Weight (kg)</t>
         </is>
       </c>
-      <c r="B7" s="9" t="n">
+      <c r="B7" s="9" t="inlineStr"/>
+      <c r="C7" s="10" t="n">
         <v>72.98570586325702</v>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="D7" s="9" t="inlineStr"/>
+      <c r="E7" s="10" t="n">
         <v>62.91348692506308</v>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="F7" s="10" t="n">
         <v>-13.80026241996596</v>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>Weight (kg)</t>
         </is>
       </c>
-      <c r="G7" s="9" t="n">
+      <c r="I7" s="9" t="inlineStr"/>
+      <c r="J7" s="10" t="n">
         <v>60.00184214232205</v>
       </c>
-      <c r="H7" s="9" t="n">
+      <c r="K7" s="9" t="inlineStr"/>
+      <c r="L7" s="10" t="n">
         <v>56.54339762483536</v>
       </c>
-      <c r="I7" s="9" t="n">
+      <c r="M7" s="10" t="n">
         <v>-5.763897230494016</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>Organ mass (g)</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="n"/>
-      <c r="C9" s="11" t="n"/>
-      <c r="D9" s="11" t="n"/>
-      <c r="F9" s="10" t="inlineStr">
-        <is>
-          <t>Organ mass (g)</t>
-        </is>
-      </c>
-      <c r="G9" s="11" t="n"/>
-      <c r="H9" s="11" t="n"/>
-      <c r="I9" s="11" t="n"/>
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>Density (g cm⁻³) / Organ mass (g)</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="n"/>
+      <c r="C9" s="12" t="n"/>
+      <c r="D9" s="12" t="n"/>
+      <c r="E9" s="12" t="n"/>
+      <c r="F9" s="12" t="n"/>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>Density (g cm⁻³) / Organ mass (g)</t>
+        </is>
+      </c>
+      <c r="I9" s="12" t="n"/>
+      <c r="J9" s="12" t="n"/>
+      <c r="K9" s="12" t="n"/>
+      <c r="L9" s="12" t="n"/>
+      <c r="M9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -673,27 +721,39 @@
           <t>Adrenal, left</t>
         </is>
       </c>
-      <c r="B10" s="9" t="n">
+      <c r="B10" s="13" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="C10" s="10" t="n">
         <v>8.682739521973351</v>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="D10" s="13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E10" s="10" t="n">
         <v>7.339557366386806</v>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="F10" s="10" t="n">
         <v>-15.46956639880032</v>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>Adrenal, left</t>
         </is>
       </c>
-      <c r="G10" s="9" t="n">
+      <c r="I10" s="13" t="n">
+        <v>1.035</v>
+      </c>
+      <c r="J10" s="10" t="n">
         <v>6.816533157629252</v>
       </c>
-      <c r="H10" s="9" t="n">
+      <c r="K10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" s="10" t="n">
         <v>6.05584898587334</v>
       </c>
-      <c r="I10" s="9" t="n">
+      <c r="M10" s="10" t="n">
         <v>-11.15939956815927</v>
       </c>
     </row>
@@ -703,27 +763,39 @@
           <t>Adrenal, right</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n">
+      <c r="B11" s="13" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="C11" s="10" t="n">
         <v>8.682743131787394</v>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="D11" s="13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E11" s="10" t="n">
         <v>7.339559914050722</v>
       </c>
-      <c r="D11" s="9" t="n">
+      <c r="F11" s="10" t="n">
         <v>-15.46957220027964</v>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>Adrenal, right</t>
         </is>
       </c>
-      <c r="G11" s="9" t="n">
+      <c r="I11" s="13" t="n">
+        <v>1.035</v>
+      </c>
+      <c r="J11" s="10" t="n">
         <v>8.648553977873142</v>
       </c>
-      <c r="H11" s="9" t="n">
+      <c r="K11" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" s="10" t="n">
         <v>4.097004458301134</v>
       </c>
-      <c r="I11" s="9" t="n">
+      <c r="M11" s="10" t="n">
         <v>-52.62786740091929</v>
       </c>
     </row>
@@ -733,27 +805,39 @@
           <t>ET1, 0~8 um</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n">
+      <c r="B12" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="C12" s="10" t="n">
         <v>0.02230901100703183</v>
       </c>
-      <c r="C12" s="9" t="n">
+      <c r="D12" s="13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E12" s="10" t="n">
         <v>0.02125042772631844</v>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="F12" s="10" t="n">
         <v>-4.745092825404593</v>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>ET1, 0~8 um</t>
         </is>
       </c>
-      <c r="G12" s="9" t="n">
+      <c r="I12" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="J12" s="10" t="n">
         <v>0.008564642407083769</v>
       </c>
-      <c r="H12" s="9" t="n">
+      <c r="K12" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L12" s="10" t="n">
         <v>0.008410948723628473</v>
       </c>
-      <c r="I12" s="9" t="n">
+      <c r="M12" s="10" t="n">
         <v>-1.794513724568074</v>
       </c>
     </row>
@@ -763,27 +847,39 @@
           <t>ET1, 8~40 um</t>
         </is>
       </c>
-      <c r="B13" s="9" t="n">
+      <c r="B13" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="C13" s="10" t="n">
         <v>0.08953171140055799</v>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="D13" s="13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E13" s="10" t="n">
         <v>0.08528914288194016</v>
       </c>
-      <c r="D13" s="9" t="n">
+      <c r="F13" s="10" t="n">
         <v>-4.73862104527066</v>
       </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>ET1, 8~40 um</t>
         </is>
       </c>
-      <c r="G13" s="9" t="n">
+      <c r="I13" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="J13" s="10" t="n">
         <v>0.03455088067062102</v>
       </c>
-      <c r="H13" s="9" t="n">
+      <c r="K13" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L13" s="10" t="n">
         <v>0.03392911240254263</v>
       </c>
-      <c r="I13" s="9" t="n">
+      <c r="M13" s="10" t="n">
         <v>-1.799572850272045</v>
       </c>
     </row>
@@ -793,27 +889,39 @@
           <t>ET1, 40~50 um</t>
         </is>
       </c>
-      <c r="B14" s="9" t="n">
+      <c r="B14" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="C14" s="10" t="n">
         <v>0.02807649464708244</v>
       </c>
-      <c r="C14" s="9" t="n">
+      <c r="D14" s="13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E14" s="10" t="n">
         <v>0.02674445354528913</v>
       </c>
-      <c r="D14" s="9" t="n">
+      <c r="F14" s="10" t="n">
         <v>-4.744328373384499</v>
       </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>ET1, 40~50 um</t>
         </is>
       </c>
-      <c r="G14" s="9" t="n">
+      <c r="I14" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="J14" s="10" t="n">
         <v>0.01089318298576057</v>
       </c>
-      <c r="H14" s="9" t="n">
+      <c r="K14" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L14" s="10" t="n">
         <v>0.01069726232972778</v>
       </c>
-      <c r="I14" s="9" t="n">
+      <c r="M14" s="10" t="n">
         <v>-1.798562057471073</v>
       </c>
     </row>
@@ -823,27 +931,39 @@
           <t>ET1, 50 um~surface</t>
         </is>
       </c>
-      <c r="B15" s="9" t="n">
+      <c r="B15" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="C15" s="10" t="n">
         <v>11.29120583068137</v>
       </c>
-      <c r="C15" s="9" t="n">
+      <c r="D15" s="13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E15" s="10" t="n">
         <v>10.76390915840156</v>
       </c>
-      <c r="D15" s="9" t="n">
+      <c r="F15" s="10" t="n">
         <v>-4.66997661885672</v>
       </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="H15" s="8" t="inlineStr">
         <is>
           <t>ET1, 50 um~surface</t>
         </is>
       </c>
-      <c r="G15" s="9" t="n">
+      <c r="I15" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="J15" s="10" t="n">
         <v>4.374578837248131</v>
       </c>
-      <c r="H15" s="9" t="n">
+      <c r="K15" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L15" s="10" t="n">
         <v>4.293978282219366</v>
       </c>
-      <c r="I15" s="9" t="n">
+      <c r="M15" s="10" t="n">
         <v>-1.842475768009413</v>
       </c>
     </row>
@@ -853,27 +973,39 @@
           <t>ET2, -15~0 um</t>
         </is>
       </c>
-      <c r="B16" s="9" t="n">
+      <c r="B16" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="10" t="n">
         <v>0.1412003875280059</v>
       </c>
-      <c r="C16" s="9" t="n">
+      <c r="D16" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="10" t="n">
         <v>0.1263888525014296</v>
       </c>
-      <c r="D16" s="9" t="n">
+      <c r="F16" s="10" t="n">
         <v>-10.48972689514647</v>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="H16" s="8" t="inlineStr">
         <is>
           <t>ET2, -15~0 um</t>
         </is>
       </c>
-      <c r="G16" s="9" t="n">
+      <c r="I16" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" s="10" t="n">
         <v>0.1041581236049957</v>
       </c>
-      <c r="H16" s="9" t="n">
+      <c r="K16" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" s="10" t="n">
         <v>0.09897407557955046</v>
       </c>
-      <c r="I16" s="9" t="n">
+      <c r="M16" s="10" t="n">
         <v>-4.977094292812867</v>
       </c>
     </row>
@@ -883,27 +1015,39 @@
           <t>ET2, 0~40 um</t>
         </is>
       </c>
-      <c r="B17" s="9" t="n">
+      <c r="B17" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="C17" s="10" t="n">
         <v>0.3898324431019095</v>
       </c>
-      <c r="C17" s="9" t="n">
+      <c r="D17" s="13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E17" s="10" t="n">
         <v>0.3655267692846555</v>
       </c>
-      <c r="D17" s="9" t="n">
+      <c r="F17" s="10" t="n">
         <v>-6.234902776139659</v>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="H17" s="8" t="inlineStr">
         <is>
           <t>ET2, 0~40 um</t>
         </is>
       </c>
-      <c r="G17" s="9" t="n">
+      <c r="I17" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="J17" s="10" t="n">
         <v>0.2878573921651795</v>
       </c>
-      <c r="H17" s="9" t="n">
+      <c r="K17" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L17" s="10" t="n">
         <v>0.2812323022116488</v>
       </c>
-      <c r="I17" s="9" t="n">
+      <c r="M17" s="10" t="n">
         <v>-2.301518089807829</v>
       </c>
     </row>
@@ -913,27 +1057,39 @@
           <t>ET2, 40~50 um</t>
         </is>
       </c>
-      <c r="B18" s="9" t="n">
+      <c r="B18" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="C18" s="10" t="n">
         <v>0.09782525443563121</v>
       </c>
-      <c r="C18" s="9" t="n">
+      <c r="D18" s="13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E18" s="10" t="n">
         <v>0.09171705682984466</v>
       </c>
-      <c r="D18" s="9" t="n">
+      <c r="F18" s="10" t="n">
         <v>-6.243988468034842</v>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>ET2, 40~50 um</t>
         </is>
       </c>
-      <c r="G18" s="9" t="n">
+      <c r="I18" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="J18" s="10" t="n">
         <v>0.07230681899474375</v>
       </c>
-      <c r="H18" s="9" t="n">
+      <c r="K18" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L18" s="10" t="n">
         <v>0.07063967180354462</v>
       </c>
-      <c r="I18" s="9" t="n">
+      <c r="M18" s="10" t="n">
         <v>-2.305656941318805</v>
       </c>
     </row>
@@ -943,27 +1099,39 @@
           <t>ET2, 50~55 um</t>
         </is>
       </c>
-      <c r="B19" s="9" t="n">
+      <c r="B19" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="C19" s="10" t="n">
         <v>0.04897425006887976</v>
       </c>
-      <c r="C19" s="9" t="n">
+      <c r="D19" s="13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E19" s="10" t="n">
         <v>0.04591906397866724</v>
       </c>
-      <c r="D19" s="9" t="n">
+      <c r="F19" s="10" t="n">
         <v>-6.238351962338489</v>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="H19" s="8" t="inlineStr">
         <is>
           <t>ET2, 50~55 um</t>
         </is>
       </c>
-      <c r="G19" s="9" t="n">
+      <c r="I19" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="J19" s="10" t="n">
         <v>0.03623167406135289</v>
       </c>
-      <c r="H19" s="9" t="n">
+      <c r="K19" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L19" s="10" t="n">
         <v>0.03539904418691992</v>
       </c>
-      <c r="I19" s="9" t="n">
+      <c r="M19" s="10" t="n">
         <v>-2.298071772844496</v>
       </c>
     </row>
@@ -973,27 +1141,39 @@
           <t>ET2, 55~65 um</t>
         </is>
       </c>
-      <c r="B20" s="9" t="n">
+      <c r="B20" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="C20" s="10" t="n">
         <v>0.09805441233887986</v>
       </c>
-      <c r="C20" s="9" t="n">
+      <c r="D20" s="13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E20" s="10" t="n">
         <v>0.09194757000853794</v>
       </c>
-      <c r="D20" s="9" t="n">
+      <c r="F20" s="10" t="n">
         <v>-6.228013798335191</v>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="H20" s="8" t="inlineStr">
         <is>
           <t>ET2, 55~65 um</t>
         </is>
       </c>
-      <c r="G20" s="9" t="n">
+      <c r="I20" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="J20" s="10" t="n">
         <v>0.07248044633739224</v>
       </c>
-      <c r="H20" s="9" t="n">
+      <c r="K20" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L20" s="10" t="n">
         <v>0.07080761196426144</v>
       </c>
-      <c r="I20" s="9" t="n">
+      <c r="M20" s="10" t="n">
         <v>-2.307980231445949</v>
       </c>
     </row>
@@ -1003,27 +1183,39 @@
           <t>ET2, 65 um~surface</t>
         </is>
       </c>
-      <c r="B21" s="9" t="n">
+      <c r="B21" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="C21" s="10" t="n">
         <v>28.8084848041517</v>
       </c>
-      <c r="C21" s="9" t="n">
+      <c r="D21" s="13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E21" s="10" t="n">
         <v>27.09475870979821</v>
       </c>
-      <c r="D21" s="9" t="n">
+      <c r="F21" s="10" t="n">
         <v>-5.948685277979348</v>
       </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>ET2, 65 um~surface</t>
         </is>
       </c>
-      <c r="G21" s="9" t="n">
+      <c r="I21" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="J21" s="10" t="n">
         <v>14.18033102289283</v>
       </c>
-      <c r="H21" s="9" t="n">
+      <c r="K21" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L21" s="10" t="n">
         <v>13.84739733110791</v>
       </c>
-      <c r="I21" s="9" t="n">
+      <c r="M21" s="10" t="n">
         <v>-2.347855570137523</v>
       </c>
     </row>
@@ -1033,27 +1225,39 @@
           <t>Oral mucosa, tongue</t>
         </is>
       </c>
-      <c r="B22" s="9" t="n">
+      <c r="B22" s="13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="C22" s="10" t="n">
         <v>0.08596550427504501</v>
       </c>
-      <c r="C22" s="9" t="n">
+      <c r="D22" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E22" s="10" t="n">
         <v>0.07623877513173967</v>
       </c>
-      <c r="D22" s="9" t="n">
+      <c r="F22" s="10" t="n">
         <v>-11.31468863625211</v>
       </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>Oral mucosa, tongue</t>
         </is>
       </c>
-      <c r="G22" s="9" t="n">
+      <c r="I22" s="13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="J22" s="10" t="n">
         <v>0.06614430714606362</v>
       </c>
-      <c r="H22" s="9" t="n">
+      <c r="K22" s="13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L22" s="10" t="n">
         <v>0.06065239059580604</v>
       </c>
-      <c r="I22" s="9" t="n">
+      <c r="M22" s="10" t="n">
         <v>-8.302931555591039</v>
       </c>
     </row>
@@ -1063,27 +1267,39 @@
           <t>Oral mucosa, mouth floor</t>
         </is>
       </c>
-      <c r="B23" s="9" t="n">
+      <c r="B23" s="13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="C23" s="10" t="n">
         <v>0.02351556738006675</v>
       </c>
-      <c r="C23" s="9" t="n">
+      <c r="D23" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E23" s="10" t="n">
         <v>0.02098066498705533</v>
       </c>
-      <c r="D23" s="9" t="n">
+      <c r="F23" s="10" t="n">
         <v>-10.77967778553434</v>
       </c>
-      <c r="F23" s="8" t="inlineStr">
+      <c r="H23" s="8" t="inlineStr">
         <is>
           <t>Oral mucosa, mouth floor</t>
         </is>
       </c>
-      <c r="G23" s="9" t="n">
+      <c r="I23" s="13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="J23" s="10" t="n">
         <v>0.01611757950807718</v>
       </c>
-      <c r="H23" s="9" t="n">
+      <c r="K23" s="13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L23" s="10" t="n">
         <v>0.01489776103213657</v>
       </c>
-      <c r="I23" s="9" t="n">
+      <c r="M23" s="10" t="n">
         <v>-7.568248540851369</v>
       </c>
     </row>
@@ -1093,27 +1309,39 @@
           <t>Oral mucosa, lips, and cheeks</t>
         </is>
       </c>
-      <c r="B24" s="9" t="n">
+      <c r="B24" s="13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="C24" s="10" t="n">
         <v>0.02307768471916582</v>
       </c>
-      <c r="C24" s="9" t="n">
+      <c r="D24" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E24" s="10" t="n">
         <v>0.02054267046457646</v>
       </c>
-      <c r="D24" s="9" t="n">
+      <c r="F24" s="10" t="n">
         <v>-10.98469922541257</v>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="H24" s="8" t="inlineStr">
         <is>
           <t>Oral mucosa, lips, and cheeks</t>
         </is>
       </c>
-      <c r="G24" s="9" t="n">
+      <c r="I24" s="13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="J24" s="10" t="n">
         <v>0.01882475852179709</v>
       </c>
-      <c r="H24" s="9" t="n">
+      <c r="K24" s="13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L24" s="10" t="n">
         <v>0.01732746305027016</v>
       </c>
-      <c r="I24" s="9" t="n">
+      <c r="M24" s="10" t="n">
         <v>-7.9538628333172</v>
       </c>
     </row>
@@ -1123,27 +1351,39 @@
           <t>Trachea</t>
         </is>
       </c>
-      <c r="B25" s="9" t="n">
+      <c r="B25" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="C25" s="10" t="n">
         <v>10.36360878445904</v>
       </c>
-      <c r="C25" s="9" t="n">
+      <c r="D25" s="13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E25" s="10" t="n">
         <v>7.050574731750703</v>
       </c>
-      <c r="D25" s="9" t="n">
+      <c r="F25" s="10" t="n">
         <v>-31.96795750990202</v>
       </c>
-      <c r="F25" s="8" t="inlineStr">
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>Trachea</t>
         </is>
       </c>
-      <c r="G25" s="9" t="n">
+      <c r="I25" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="J25" s="10" t="n">
         <v>8.201122819042673</v>
       </c>
-      <c r="H25" s="9" t="n">
+      <c r="K25" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L25" s="10" t="n">
         <v>7.759348437868989</v>
       </c>
-      <c r="I25" s="9" t="n">
+      <c r="M25" s="10" t="n">
         <v>-5.386754849566478</v>
       </c>
     </row>
@@ -1153,27 +1393,39 @@
           <t>BB1, -11~-6 um</t>
         </is>
       </c>
-      <c r="B26" s="9" t="n">
+      <c r="B26" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="10" t="n">
         <v>0.02516398226537089</v>
       </c>
-      <c r="C26" s="9" t="n">
+      <c r="D26" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="10" t="n">
         <v>0.0216049584538451</v>
       </c>
-      <c r="D26" s="9" t="n">
+      <c r="F26" s="10" t="n">
         <v>-14.14332506673038</v>
       </c>
-      <c r="F26" s="8" t="inlineStr">
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>BB1, -11~-6 um</t>
         </is>
       </c>
-      <c r="G26" s="9" t="n">
+      <c r="I26" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" s="10" t="n">
         <v>0.01023395670827489</v>
       </c>
-      <c r="H26" s="9" t="n">
+      <c r="K26" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" s="10" t="n">
         <v>0.009411244813274365</v>
       </c>
-      <c r="I26" s="9" t="n">
+      <c r="M26" s="10" t="n">
         <v>-8.039040211449208</v>
       </c>
     </row>
@@ -1183,27 +1435,39 @@
           <t>BB1, -6~0 um</t>
         </is>
       </c>
-      <c r="B27" s="9" t="n">
+      <c r="B27" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="C27" s="10" t="n">
         <v>0.0311633585954477</v>
       </c>
-      <c r="C27" s="9" t="n">
+      <c r="D27" s="13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E27" s="10" t="n">
         <v>0.02802473126232362</v>
       </c>
-      <c r="D27" s="9" t="n">
+      <c r="F27" s="10" t="n">
         <v>-10.07153103703836</v>
       </c>
-      <c r="F27" s="8" t="inlineStr">
+      <c r="H27" s="8" t="inlineStr">
         <is>
           <t>BB1, -6~0 um</t>
         </is>
       </c>
-      <c r="G27" s="9" t="n">
+      <c r="I27" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="J27" s="10" t="n">
         <v>0.01263400073905283</v>
       </c>
-      <c r="H27" s="9" t="n">
+      <c r="K27" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L27" s="10" t="n">
         <v>0.01194409998084939</v>
       </c>
-      <c r="I27" s="9" t="n">
+      <c r="M27" s="10" t="n">
         <v>-5.460667388366439</v>
       </c>
     </row>
@@ -1213,27 +1477,39 @@
           <t>BB1, 0~10 um</t>
         </is>
       </c>
-      <c r="B28" s="9" t="n">
+      <c r="B28" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="C28" s="10" t="n">
         <v>0.05201120782342172</v>
       </c>
-      <c r="C28" s="9" t="n">
+      <c r="D28" s="13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E28" s="10" t="n">
         <v>0.04678203018261107</v>
       </c>
-      <c r="D28" s="9" t="n">
+      <c r="F28" s="10" t="n">
         <v>-10.05394387025915</v>
       </c>
-      <c r="F28" s="8" t="inlineStr">
+      <c r="H28" s="8" t="inlineStr">
         <is>
           <t>BB1, 0~10 um</t>
         </is>
       </c>
-      <c r="G28" s="9" t="n">
+      <c r="I28" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="J28" s="10" t="n">
         <v>0.02110304104380938</v>
       </c>
-      <c r="H28" s="9" t="n">
+      <c r="K28" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L28" s="10" t="n">
         <v>0.01995009615506521</v>
       </c>
-      <c r="I28" s="9" t="n">
+      <c r="M28" s="10" t="n">
         <v>-5.463406370440562</v>
       </c>
     </row>
@@ -1243,27 +1519,39 @@
           <t>BB1, 10~35 um</t>
         </is>
       </c>
-      <c r="B29" s="9" t="n">
+      <c r="B29" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="C29" s="10" t="n">
         <v>0.1304111259961421</v>
       </c>
-      <c r="C29" s="9" t="n">
+      <c r="D29" s="13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E29" s="10" t="n">
         <v>0.1172843468865527</v>
       </c>
-      <c r="D29" s="9" t="n">
+      <c r="F29" s="10" t="n">
         <v>-10.06568957159205</v>
       </c>
-      <c r="F29" s="8" t="inlineStr">
+      <c r="H29" s="8" t="inlineStr">
         <is>
           <t>BB1, 10~35 um</t>
         </is>
       </c>
-      <c r="G29" s="9" t="n">
+      <c r="I29" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="J29" s="10" t="n">
         <v>0.0530281593109373</v>
       </c>
-      <c r="H29" s="9" t="n">
+      <c r="K29" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L29" s="10" t="n">
         <v>0.05013129316148755</v>
       </c>
-      <c r="I29" s="9" t="n">
+      <c r="M29" s="10" t="n">
         <v>-5.46288271569754</v>
       </c>
     </row>
@@ -1273,27 +1561,39 @@
           <t>BB1, 35~40 um</t>
         </is>
       </c>
-      <c r="B30" s="9" t="n">
+      <c r="B30" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="C30" s="10" t="n">
         <v>0.02615675686520097</v>
       </c>
-      <c r="C30" s="9" t="n">
+      <c r="D30" s="13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E30" s="10" t="n">
         <v>0.02352524680371814</v>
       </c>
-      <c r="D30" s="9" t="n">
+      <c r="F30" s="10" t="n">
         <v>-10.06053646116885</v>
       </c>
-      <c r="F30" s="8" t="inlineStr">
+      <c r="H30" s="8" t="inlineStr">
         <is>
           <t>BB1, 35~40 um</t>
         </is>
       </c>
-      <c r="G30" s="9" t="n">
+      <c r="I30" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="J30" s="10" t="n">
         <v>0.0106508083382203</v>
       </c>
-      <c r="H30" s="9" t="n">
+      <c r="K30" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L30" s="10" t="n">
         <v>0.01006694776787517</v>
       </c>
-      <c r="I30" s="9" t="n">
+      <c r="M30" s="10" t="n">
         <v>-5.481842802953765</v>
       </c>
     </row>
@@ -1303,27 +1603,39 @@
           <t>BB1, 40~50 um</t>
         </is>
       </c>
-      <c r="B31" s="9" t="n">
+      <c r="B31" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="C31" s="10" t="n">
         <v>0.05236504327091515</v>
       </c>
-      <c r="C31" s="9" t="n">
+      <c r="D31" s="13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E31" s="10" t="n">
         <v>0.04710105031320131</v>
       </c>
-      <c r="D31" s="9" t="n">
+      <c r="F31" s="10" t="n">
         <v>-10.05249423834162</v>
       </c>
-      <c r="F31" s="8" t="inlineStr">
+      <c r="H31" s="8" t="inlineStr">
         <is>
           <t>BB1, 40~50 um</t>
         </is>
       </c>
-      <c r="G31" s="9" t="n">
+      <c r="I31" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="J31" s="10" t="n">
         <v>0.02134790498527826</v>
       </c>
-      <c r="H31" s="9" t="n">
+      <c r="K31" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L31" s="10" t="n">
         <v>0.02018473800816965</v>
       </c>
-      <c r="I31" s="9" t="n">
+      <c r="M31" s="10" t="n">
         <v>-5.44862354367203</v>
       </c>
     </row>
@@ -1333,27 +1645,39 @@
           <t>BB1, 50~60 um</t>
         </is>
       </c>
-      <c r="B32" s="9" t="n">
+      <c r="B32" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="C32" s="10" t="n">
         <v>0.05246035062305502</v>
       </c>
-      <c r="C32" s="9" t="n">
+      <c r="D32" s="13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E32" s="10" t="n">
         <v>0.04717976261567303</v>
       </c>
-      <c r="D32" s="9" t="n">
+      <c r="F32" s="10" t="n">
         <v>-10.06586487636113</v>
       </c>
-      <c r="F32" s="8" t="inlineStr">
+      <c r="H32" s="8" t="inlineStr">
         <is>
           <t>BB1, 50~60 um</t>
         </is>
       </c>
-      <c r="G32" s="9" t="n">
+      <c r="I32" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="J32" s="10" t="n">
         <v>0.02141007120092797</v>
       </c>
-      <c r="H32" s="9" t="n">
+      <c r="K32" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L32" s="10" t="n">
         <v>0.02023802127805291</v>
       </c>
-      <c r="I32" s="9" t="n">
+      <c r="M32" s="10" t="n">
         <v>-5.474292504100871</v>
       </c>
     </row>
@@ -1363,27 +1687,39 @@
           <t>BB1, 60~70 um</t>
         </is>
       </c>
-      <c r="B33" s="9" t="n">
+      <c r="B33" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="C33" s="10" t="n">
         <v>0.05255009106040866</v>
       </c>
-      <c r="C33" s="9" t="n">
+      <c r="D33" s="13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E33" s="10" t="n">
         <v>0.04726347158867601</v>
       </c>
-      <c r="D33" s="9" t="n">
+      <c r="F33" s="10" t="n">
         <v>-10.06015282762394</v>
       </c>
-      <c r="F33" s="8" t="inlineStr">
+      <c r="H33" s="8" t="inlineStr">
         <is>
           <t>BB1, 60~70 um</t>
         </is>
       </c>
-      <c r="G33" s="9" t="n">
+      <c r="I33" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="J33" s="10" t="n">
         <v>0.0214697634194093</v>
       </c>
-      <c r="H33" s="9" t="n">
+      <c r="K33" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L33" s="10" t="n">
         <v>0.02029788427351089</v>
       </c>
-      <c r="I33" s="9" t="n">
+      <c r="M33" s="10" t="n">
         <v>-5.458276940485514</v>
       </c>
     </row>
@@ -1393,27 +1729,39 @@
           <t>BB1, 70 um~surface</t>
         </is>
       </c>
-      <c r="B34" s="9" t="n">
+      <c r="B34" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="C34" s="10" t="n">
         <v>2.776674508378841</v>
       </c>
-      <c r="C34" s="9" t="n">
+      <c r="D34" s="13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E34" s="10" t="n">
         <v>2.497251507932316</v>
       </c>
-      <c r="D34" s="9" t="n">
+      <c r="F34" s="10" t="n">
         <v>-10.0632248973851</v>
       </c>
-      <c r="F34" s="8" t="inlineStr">
+      <c r="H34" s="8" t="inlineStr">
         <is>
           <t>BB1, 70 um~surface</t>
         </is>
       </c>
-      <c r="G34" s="9" t="n">
+      <c r="I34" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="J34" s="10" t="n">
         <v>1.179008613906296</v>
       </c>
-      <c r="H34" s="9" t="n">
+      <c r="K34" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L34" s="10" t="n">
         <v>1.114590808172409</v>
       </c>
-      <c r="I34" s="9" t="n">
+      <c r="M34" s="10" t="n">
         <v>-5.463726471043989</v>
       </c>
     </row>
@@ -1423,27 +1771,39 @@
           <t>Blood in large arteries, head</t>
         </is>
       </c>
-      <c r="B35" s="9" t="n">
+      <c r="B35" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="C35" s="10" t="n">
         <v>1.504030783401192</v>
       </c>
-      <c r="C35" s="9" t="n">
+      <c r="D35" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E35" s="10" t="n">
         <v>287.2113698967393</v>
       </c>
-      <c r="D35" s="9" t="n">
+      <c r="F35" s="10" t="n">
         <v>18996.10980483018</v>
       </c>
-      <c r="F35" s="8" t="inlineStr">
+      <c r="H35" s="8" t="inlineStr">
         <is>
           <t>Blood in large arteries, head</t>
         </is>
       </c>
-      <c r="G35" s="9" t="n">
+      <c r="I35" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="J35" s="10" t="n">
         <v>1.905949095522094</v>
       </c>
-      <c r="H35" s="9" t="n">
+      <c r="K35" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="L35" s="10" t="n">
         <v>220.3213635320002</v>
       </c>
-      <c r="I35" s="9" t="n">
+      <c r="M35" s="10" t="n">
         <v>11459.66673242382</v>
       </c>
     </row>
@@ -1453,27 +1813,39 @@
           <t>Blood in large veins, head</t>
         </is>
       </c>
-      <c r="B36" s="9" t="n">
+      <c r="B36" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="C36" s="10" t="n">
         <v>6.943591122847132</v>
       </c>
-      <c r="C36" s="9" t="n">
+      <c r="D36" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E36" s="10" t="n">
         <v>862.0404712643776</v>
       </c>
-      <c r="D36" s="9" t="n">
+      <c r="F36" s="10" t="n">
         <v>12314.90830915903</v>
       </c>
-      <c r="F36" s="8" t="inlineStr">
+      <c r="H36" s="8" t="inlineStr">
         <is>
           <t>Blood in large veins, head</t>
         </is>
       </c>
-      <c r="G36" s="9" t="n">
+      <c r="I36" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="J36" s="10" t="n">
         <v>3.007187080501874</v>
       </c>
-      <c r="H36" s="9" t="n">
+      <c r="K36" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="L36" s="10" t="n">
         <v>660.9901172946738</v>
       </c>
-      <c r="I36" s="9" t="n">
+      <c r="M36" s="10" t="n">
         <v>21880.3457383955</v>
       </c>
     </row>
@@ -1483,27 +1855,39 @@
           <t>Blood in large arteries, trunk</t>
         </is>
       </c>
-      <c r="B37" s="9" t="n">
+      <c r="B37" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="C37" s="10" t="n">
         <v>193.1967825021003</v>
       </c>
-      <c r="C37" s="9" t="n">
+      <c r="D37" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E37" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D37" s="9" t="n">
+      <c r="F37" s="10" t="n">
         <v>-100</v>
       </c>
-      <c r="F37" s="8" t="inlineStr">
+      <c r="H37" s="8" t="inlineStr">
         <is>
           <t>Blood in large arteries, trunk</t>
         </is>
       </c>
-      <c r="G37" s="9" t="n">
+      <c r="I37" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="J37" s="10" t="n">
         <v>117.8720728338028</v>
       </c>
-      <c r="H37" s="9" t="n">
+      <c r="K37" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="L37" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="I37" s="9" t="n">
+      <c r="M37" s="10" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -1513,27 +1897,39 @@
           <t>Blood in large veins, trunk</t>
         </is>
       </c>
-      <c r="B38" s="9" t="n">
+      <c r="B38" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="C38" s="10" t="n">
         <v>444.0353949335862</v>
       </c>
-      <c r="C38" s="9" t="n">
+      <c r="D38" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E38" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D38" s="9" t="n">
+      <c r="F38" s="10" t="n">
         <v>-100</v>
       </c>
-      <c r="F38" s="8" t="inlineStr">
+      <c r="H38" s="8" t="inlineStr">
         <is>
           <t>Blood in large veins, trunk</t>
         </is>
       </c>
-      <c r="G38" s="9" t="n">
+      <c r="I38" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="J38" s="10" t="n">
         <v>239.8512390237402</v>
       </c>
-      <c r="H38" s="9" t="n">
+      <c r="K38" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="L38" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="I38" s="9" t="n">
+      <c r="M38" s="10" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -1543,27 +1939,39 @@
           <t>Blood in large arteries, arms</t>
         </is>
       </c>
-      <c r="B39" s="9" t="n">
+      <c r="B39" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="C39" s="10" t="n">
         <v>32.46345325332425</v>
       </c>
-      <c r="C39" s="9" t="n">
+      <c r="D39" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E39" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D39" s="9" t="n">
+      <c r="F39" s="10" t="n">
         <v>-100</v>
       </c>
-      <c r="F39" s="8" t="inlineStr">
+      <c r="H39" s="8" t="inlineStr">
         <is>
           <t>Blood in large arteries, arms</t>
         </is>
       </c>
-      <c r="G39" s="9" t="n">
+      <c r="I39" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="J39" s="10" t="n">
         <v>46.31249862253036</v>
       </c>
-      <c r="H39" s="9" t="n">
+      <c r="K39" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="L39" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="I39" s="9" t="n">
+      <c r="M39" s="10" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -1573,27 +1981,39 @@
           <t>Blood in large veins, arms</t>
         </is>
       </c>
-      <c r="B40" s="9" t="n">
+      <c r="B40" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="C40" s="10" t="n">
         <v>167.2694020912145</v>
       </c>
-      <c r="C40" s="9" t="n">
+      <c r="D40" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E40" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D40" s="9" t="n">
+      <c r="F40" s="10" t="n">
         <v>-100</v>
       </c>
-      <c r="F40" s="8" t="inlineStr">
+      <c r="H40" s="8" t="inlineStr">
         <is>
           <t>Blood in large veins, arms</t>
         </is>
       </c>
-      <c r="G40" s="9" t="n">
+      <c r="I40" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="J40" s="10" t="n">
         <v>139.5278927113592</v>
       </c>
-      <c r="H40" s="9" t="n">
+      <c r="K40" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="L40" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="I40" s="9" t="n">
+      <c r="M40" s="10" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -1603,27 +2023,39 @@
           <t>Blood in large arteries, legs</t>
         </is>
       </c>
-      <c r="B41" s="9" t="n">
+      <c r="B41" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="C41" s="10" t="n">
         <v>108.8315671468713</v>
       </c>
-      <c r="C41" s="9" t="n">
+      <c r="D41" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E41" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D41" s="9" t="n">
+      <c r="F41" s="10" t="n">
         <v>-100</v>
       </c>
-      <c r="F41" s="8" t="inlineStr">
+      <c r="H41" s="8" t="inlineStr">
         <is>
           <t>Blood in large arteries, legs</t>
         </is>
       </c>
-      <c r="G41" s="9" t="n">
+      <c r="I41" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="J41" s="10" t="n">
         <v>79.90579478361157</v>
       </c>
-      <c r="H41" s="9" t="n">
+      <c r="K41" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="L41" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="I41" s="9" t="n">
+      <c r="M41" s="10" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -1633,27 +2065,39 @@
           <t>Blood in large veins, legs</t>
         </is>
       </c>
-      <c r="B42" s="9" t="n">
+      <c r="B42" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="C42" s="10" t="n">
         <v>389.7405461384459</v>
       </c>
-      <c r="C42" s="9" t="n">
+      <c r="D42" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E42" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D42" s="9" t="n">
+      <c r="F42" s="10" t="n">
         <v>-100</v>
       </c>
-      <c r="F42" s="8" t="inlineStr">
+      <c r="H42" s="8" t="inlineStr">
         <is>
           <t>Blood in large veins, legs</t>
         </is>
       </c>
-      <c r="G42" s="9" t="n">
+      <c r="I42" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="J42" s="10" t="n">
         <v>355.6121419216337</v>
       </c>
-      <c r="H42" s="9" t="n">
+      <c r="K42" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="L42" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="I42" s="9" t="n">
+      <c r="M42" s="10" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -1663,27 +2107,39 @@
           <t>Humeri, upper, cortical</t>
         </is>
       </c>
-      <c r="B43" s="9" t="n">
+      <c r="B43" s="13" t="n">
+        <v>1.904</v>
+      </c>
+      <c r="C43" s="10" t="n">
         <v>159.1964516527676</v>
       </c>
-      <c r="C43" s="9" t="n">
+      <c r="D43" s="13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="E43" s="10" t="n">
         <v>230.2248473291947</v>
       </c>
-      <c r="D43" s="9" t="n">
+      <c r="F43" s="10" t="n">
         <v>44.61682087698229</v>
       </c>
-      <c r="F43" s="8" t="inlineStr">
+      <c r="H43" s="8" t="inlineStr">
         <is>
           <t>Humeri, upper, cortical</t>
         </is>
       </c>
-      <c r="G43" s="9" t="n">
+      <c r="I43" s="13" t="n">
+        <v>1.904</v>
+      </c>
+      <c r="J43" s="10" t="n">
         <v>113.6814173945742</v>
       </c>
-      <c r="H43" s="9" t="n">
+      <c r="K43" s="13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="L43" s="10" t="n">
         <v>201.1871079938352</v>
       </c>
-      <c r="I43" s="9" t="n">
+      <c r="M43" s="10" t="n">
         <v>76.97448941504624</v>
       </c>
     </row>
@@ -1693,27 +2149,39 @@
           <t>Humeri, upper, spongiosa</t>
         </is>
       </c>
-      <c r="B44" s="9" t="n">
+      <c r="B44" s="13" t="n">
+        <v>1.233</v>
+      </c>
+      <c r="C44" s="10" t="n">
         <v>145.6886556628159</v>
       </c>
-      <c r="C44" s="9" t="n">
+      <c r="D44" s="13" t="n">
+        <v>1.143</v>
+      </c>
+      <c r="E44" s="10" t="n">
         <v>115.9528394111348</v>
       </c>
-      <c r="D44" s="9" t="n">
+      <c r="F44" s="10" t="n">
         <v>-20.41052277982586</v>
       </c>
-      <c r="F44" s="8" t="inlineStr">
+      <c r="H44" s="8" t="inlineStr">
         <is>
           <t>Humeri, upper, spongiosa</t>
         </is>
       </c>
-      <c r="G44" s="9" t="n">
+      <c r="I44" s="13" t="n">
+        <v>1.185</v>
+      </c>
+      <c r="J44" s="10" t="n">
         <v>107.7174852567564</v>
       </c>
-      <c r="H44" s="9" t="n">
+      <c r="K44" s="13" t="n">
+        <v>1.046</v>
+      </c>
+      <c r="L44" s="10" t="n">
         <v>87.42819379837928</v>
       </c>
-      <c r="I44" s="9" t="n">
+      <c r="M44" s="10" t="n">
         <v>-18.83565273550096</v>
       </c>
     </row>
@@ -1723,27 +2191,39 @@
           <t>Humeri, upper, medullary cavity</t>
         </is>
       </c>
-      <c r="B45" s="9" t="n">
+      <c r="B45" s="13" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="C45" s="10" t="n">
         <v>34.24398253797597</v>
       </c>
-      <c r="C45" s="9" t="n">
+      <c r="D45" s="13" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="E45" s="10" t="n">
         <v>61.5082918060824</v>
       </c>
-      <c r="D45" s="9" t="n">
+      <c r="F45" s="10" t="n">
         <v>79.61781091866521</v>
       </c>
-      <c r="F45" s="8" t="inlineStr">
+      <c r="H45" s="8" t="inlineStr">
         <is>
           <t>Humeri, upper, medullary cavity</t>
         </is>
       </c>
-      <c r="G45" s="9" t="n">
+      <c r="I45" s="13" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="J45" s="10" t="n">
         <v>20.51623487405778</v>
       </c>
-      <c r="H45" s="9" t="n">
+      <c r="K45" s="13" t="n">
+        <v>0.962</v>
+      </c>
+      <c r="L45" s="10" t="n">
         <v>36.97752520188451</v>
       </c>
-      <c r="I45" s="9" t="n">
+      <c r="M45" s="10" t="n">
         <v>80.23543515112313</v>
       </c>
     </row>
@@ -1753,27 +2233,39 @@
           <t>Humeri, lower, cortical</t>
         </is>
       </c>
-      <c r="B46" s="9" t="n">
+      <c r="B46" s="13" t="n">
+        <v>1.904</v>
+      </c>
+      <c r="C46" s="10" t="n">
         <v>106.7201245829649</v>
       </c>
-      <c r="C46" s="9" t="n">
+      <c r="D46" s="13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="E46" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D46" s="9" t="n">
+      <c r="F46" s="10" t="n">
         <v>-100</v>
       </c>
-      <c r="F46" s="8" t="inlineStr">
+      <c r="H46" s="8" t="inlineStr">
         <is>
           <t>Humeri, lower, cortical</t>
         </is>
       </c>
-      <c r="G46" s="9" t="n">
+      <c r="I46" s="13" t="n">
+        <v>1.904</v>
+      </c>
+      <c r="J46" s="10" t="n">
         <v>103.2956325790116</v>
       </c>
-      <c r="H46" s="9" t="n">
+      <c r="K46" s="13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="L46" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="I46" s="9" t="n">
+      <c r="M46" s="10" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -1783,27 +2275,39 @@
           <t>Humeri, lower, spongiosa</t>
         </is>
       </c>
-      <c r="B47" s="9" t="n">
+      <c r="B47" s="13" t="n">
+        <v>1.109</v>
+      </c>
+      <c r="C47" s="10" t="n">
         <v>50.8897893178414</v>
       </c>
-      <c r="C47" s="9" t="n">
+      <c r="D47" s="13" t="n">
+        <v>1.142</v>
+      </c>
+      <c r="E47" s="10" t="n">
         <v>44.99223282206611</v>
       </c>
-      <c r="D47" s="9" t="n">
+      <c r="F47" s="10" t="n">
         <v>-11.58887976317024</v>
       </c>
-      <c r="F47" s="8" t="inlineStr">
+      <c r="H47" s="8" t="inlineStr">
         <is>
           <t>Humeri, lower, spongiosa</t>
         </is>
       </c>
-      <c r="G47" s="9" t="n">
+      <c r="I47" s="13" t="n">
+        <v>1.117</v>
+      </c>
+      <c r="J47" s="10" t="n">
         <v>50.26410179342064</v>
       </c>
-      <c r="H47" s="9" t="n">
+      <c r="K47" s="13" t="n">
+        <v>1.1082</v>
+      </c>
+      <c r="L47" s="10" t="n">
         <v>45.85375901772784</v>
       </c>
-      <c r="I47" s="9" t="n">
+      <c r="M47" s="10" t="n">
         <v>-8.774339177130372</v>
       </c>
     </row>
@@ -1813,27 +2317,39 @@
           <t>Humeri, lower, medullary cavity</t>
         </is>
       </c>
-      <c r="B48" s="9" t="n">
+      <c r="B48" s="13" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="C48" s="10" t="n">
         <v>37.39695522125388</v>
       </c>
-      <c r="C48" s="9" t="n">
+      <c r="D48" s="13" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="E48" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D48" s="9" t="n">
+      <c r="F48" s="10" t="n">
         <v>-100</v>
       </c>
-      <c r="F48" s="8" t="inlineStr">
+      <c r="H48" s="8" t="inlineStr">
         <is>
           <t>Humeri, lower, medullary cavity</t>
         </is>
       </c>
-      <c r="G48" s="9" t="n">
+      <c r="I48" s="13" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="J48" s="10" t="n">
         <v>20.49282148673207</v>
       </c>
-      <c r="H48" s="9" t="n">
+      <c r="K48" s="13" t="n">
+        <v>0.962</v>
+      </c>
+      <c r="L48" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="I48" s="9" t="n">
+      <c r="M48" s="10" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -1843,27 +2359,39 @@
           <t>Ulnae and radii, cortical</t>
         </is>
       </c>
-      <c r="B49" s="9" t="n">
+      <c r="B49" s="13" t="n">
+        <v>1.904</v>
+      </c>
+      <c r="C49" s="10" t="n">
         <v>273.4089197129907</v>
       </c>
-      <c r="C49" s="9" t="n">
+      <c r="D49" s="13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="E49" s="10" t="n">
         <v>236.5822151494687</v>
       </c>
-      <c r="D49" s="9" t="n">
+      <c r="F49" s="10" t="n">
         <v>-13.46945981213072</v>
       </c>
-      <c r="F49" s="8" t="inlineStr">
+      <c r="H49" s="8" t="inlineStr">
         <is>
           <t>Ulnae and radii, cortical</t>
         </is>
       </c>
-      <c r="G49" s="9" t="n">
+      <c r="I49" s="13" t="n">
+        <v>1.904</v>
+      </c>
+      <c r="J49" s="10" t="n">
         <v>156.7082606463714</v>
       </c>
-      <c r="H49" s="9" t="n">
+      <c r="K49" s="13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="L49" s="10" t="n">
         <v>145.3042168967101</v>
       </c>
-      <c r="I49" s="9" t="n">
+      <c r="M49" s="10" t="n">
         <v>-7.277244800384675</v>
       </c>
     </row>
@@ -1873,27 +2401,39 @@
           <t>Ulnae and radii, spongiosa</t>
         </is>
       </c>
-      <c r="B50" s="9" t="n">
+      <c r="B50" s="13" t="n">
+        <v>1.109</v>
+      </c>
+      <c r="C50" s="10" t="n">
         <v>154.980985482116</v>
       </c>
-      <c r="C50" s="9" t="n">
+      <c r="D50" s="13" t="n">
+        <v>1.068</v>
+      </c>
+      <c r="E50" s="10" t="n">
         <v>128.1417179444475</v>
       </c>
-      <c r="D50" s="9" t="n">
+      <c r="F50" s="10" t="n">
         <v>-17.31778092272204</v>
       </c>
-      <c r="F50" s="8" t="inlineStr">
+      <c r="H50" s="8" t="inlineStr">
         <is>
           <t>Ulnae and radii, spongiosa</t>
         </is>
       </c>
-      <c r="G50" s="9" t="n">
+      <c r="I50" s="13" t="n">
+        <v>1.117</v>
+      </c>
+      <c r="J50" s="10" t="n">
         <v>86.88276399941033</v>
       </c>
-      <c r="H50" s="9" t="n">
+      <c r="K50" s="13" t="n">
+        <v>1.082</v>
+      </c>
+      <c r="L50" s="10" t="n">
         <v>77.38552908723808</v>
       </c>
-      <c r="I50" s="9" t="n">
+      <c r="M50" s="10" t="n">
         <v>-10.93109205438803</v>
       </c>
     </row>
@@ -1903,27 +2443,39 @@
           <t>Ulnae and radii, medullary cavity</t>
         </is>
       </c>
-      <c r="B51" s="9" t="n">
+      <c r="B51" s="13" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="C51" s="10" t="n">
         <v>22.99634576016832</v>
       </c>
-      <c r="C51" s="9" t="n">
+      <c r="D51" s="13" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="E51" s="10" t="n">
         <v>19.74382700112291</v>
       </c>
-      <c r="D51" s="9" t="n">
+      <c r="F51" s="10" t="n">
         <v>-14.14363304920845</v>
       </c>
-      <c r="F51" s="8" t="inlineStr">
+      <c r="H51" s="8" t="inlineStr">
         <is>
           <t>Ulnae and radii, medullary cavity</t>
         </is>
       </c>
-      <c r="G51" s="9" t="n">
+      <c r="I51" s="13" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="J51" s="10" t="n">
         <v>34.06820067408791</v>
       </c>
-      <c r="H51" s="9" t="n">
+      <c r="K51" s="13" t="n">
+        <v>0.962</v>
+      </c>
+      <c r="L51" s="10" t="n">
         <v>30.71901710978328</v>
       </c>
-      <c r="I51" s="9" t="n">
+      <c r="M51" s="10" t="n">
         <v>-9.830820231289767</v>
       </c>
     </row>
@@ -1933,27 +2485,39 @@
           <t>Wrists and hand bones, cortical</t>
         </is>
       </c>
-      <c r="B52" s="9" t="n">
+      <c r="B52" s="13" t="n">
+        <v>1.904</v>
+      </c>
+      <c r="C52" s="10" t="n">
         <v>181.5289884775256</v>
       </c>
-      <c r="C52" s="9" t="n">
+      <c r="D52" s="13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="E52" s="10" t="n">
         <v>157.1638888942083</v>
       </c>
-      <c r="D52" s="9" t="n">
+      <c r="F52" s="10" t="n">
         <v>-13.4221535566667</v>
       </c>
-      <c r="F52" s="8" t="inlineStr">
+      <c r="H52" s="8" t="inlineStr">
         <is>
           <t>Wrists and hand bones, cortical</t>
         </is>
       </c>
-      <c r="G52" s="9" t="n">
+      <c r="I52" s="13" t="n">
+        <v>1.904</v>
+      </c>
+      <c r="J52" s="10" t="n">
         <v>105.131548343243</v>
       </c>
-      <c r="H52" s="9" t="n">
+      <c r="K52" s="13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="L52" s="10" t="n">
         <v>97.48082351362096</v>
       </c>
-      <c r="I52" s="9" t="n">
+      <c r="M52" s="10" t="n">
         <v>-7.277287313074894</v>
       </c>
     </row>
@@ -1963,27 +2527,39 @@
           <t>Wrists and hand bones, spongiosa</t>
         </is>
       </c>
-      <c r="B53" s="9" t="n">
+      <c r="B53" s="13" t="n">
+        <v>1.109</v>
+      </c>
+      <c r="C53" s="10" t="n">
         <v>118.9268865563859</v>
       </c>
-      <c r="C53" s="9" t="n">
+      <c r="D53" s="13" t="n">
+        <v>1.169</v>
+      </c>
+      <c r="E53" s="10" t="n">
         <v>107.6305393691159</v>
       </c>
-      <c r="D53" s="9" t="n">
+      <c r="F53" s="10" t="n">
         <v>-9.498564634427067</v>
       </c>
-      <c r="F53" s="8" t="inlineStr">
+      <c r="H53" s="8" t="inlineStr">
         <is>
           <t>Wrists and hand bones, spongiosa</t>
         </is>
       </c>
-      <c r="G53" s="9" t="n">
+      <c r="I53" s="13" t="n">
+        <v>1.117</v>
+      </c>
+      <c r="J53" s="10" t="n">
         <v>69.36022515983421</v>
       </c>
-      <c r="H53" s="9" t="n">
+      <c r="K53" s="13" t="n">
+        <v>1.082</v>
+      </c>
+      <c r="L53" s="10" t="n">
         <v>61.77838966258548</v>
       </c>
-      <c r="I53" s="9" t="n">
+      <c r="M53" s="10" t="n">
         <v>-10.93109989158354</v>
       </c>
     </row>
@@ -1993,27 +2569,39 @@
           <t>Clavicles, cortical</t>
         </is>
       </c>
-      <c r="B54" s="9" t="n">
+      <c r="B54" s="13" t="n">
+        <v>1.904</v>
+      </c>
+      <c r="C54" s="10" t="n">
         <v>48.25181226810412</v>
       </c>
-      <c r="C54" s="9" t="n">
+      <c r="D54" s="13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="E54" s="10" t="n">
         <v>41.77535452123023</v>
       </c>
-      <c r="D54" s="9" t="n">
+      <c r="F54" s="10" t="n">
         <v>-13.42220621867714</v>
       </c>
-      <c r="F54" s="8" t="inlineStr">
+      <c r="H54" s="8" t="inlineStr">
         <is>
           <t>Clavicles, cortical</t>
         </is>
       </c>
-      <c r="G54" s="9" t="n">
+      <c r="I54" s="13" t="n">
+        <v>1.904</v>
+      </c>
+      <c r="J54" s="10" t="n">
         <v>32.82525023736568</v>
       </c>
-      <c r="H54" s="9" t="n">
+      <c r="K54" s="13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="L54" s="10" t="n">
         <v>30.462225089101</v>
       </c>
-      <c r="I54" s="9" t="n">
+      <c r="M54" s="10" t="n">
         <v>-7.198803150553903</v>
       </c>
     </row>
@@ -2023,27 +2611,39 @@
           <t>Clavicles, spongiosa</t>
         </is>
       </c>
-      <c r="B55" s="9" t="n">
+      <c r="B55" s="13" t="n">
+        <v>1.157</v>
+      </c>
+      <c r="C55" s="10" t="n">
         <v>45.05701335680252</v>
       </c>
-      <c r="C55" s="9" t="n">
+      <c r="D55" s="13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E55" s="10" t="n">
         <v>36.7785191751308</v>
       </c>
-      <c r="D55" s="9" t="n">
+      <c r="F55" s="10" t="n">
         <v>-18.3733753414037</v>
       </c>
-      <c r="F55" s="8" t="inlineStr">
+      <c r="H55" s="8" t="inlineStr">
         <is>
           <t>Clavicles, spongiosa</t>
         </is>
       </c>
-      <c r="G55" s="9" t="n">
+      <c r="I55" s="13" t="n">
+        <v>1.192</v>
+      </c>
+      <c r="J55" s="10" t="n">
         <v>38.79822056974663</v>
       </c>
-      <c r="H55" s="9" t="n">
+      <c r="K55" s="13" t="n">
+        <v>1.039</v>
+      </c>
+      <c r="L55" s="10" t="n">
         <v>31.11705575880284</v>
       </c>
-      <c r="I55" s="9" t="n">
+      <c r="M55" s="10" t="n">
         <v>-19.79772447846041</v>
       </c>
     </row>
@@ -2053,27 +2653,39 @@
           <t>Cranium, cortical</t>
         </is>
       </c>
-      <c r="B56" s="9" t="n">
+      <c r="B56" s="13" t="n">
+        <v>1.904</v>
+      </c>
+      <c r="C56" s="10" t="n">
         <v>568.4694168021932</v>
       </c>
-      <c r="C56" s="9" t="n">
+      <c r="D56" s="13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="E56" s="10" t="n">
         <v>529.705814552004</v>
       </c>
-      <c r="D56" s="9" t="n">
+      <c r="F56" s="10" t="n">
         <v>-6.818942427588428</v>
       </c>
-      <c r="F56" s="8" t="inlineStr">
+      <c r="H56" s="8" t="inlineStr">
         <is>
           <t>Cranium, cortical</t>
         </is>
       </c>
-      <c r="G56" s="9" t="n">
+      <c r="I56" s="13" t="n">
+        <v>1.904</v>
+      </c>
+      <c r="J56" s="10" t="n">
         <v>407.6700225958504</v>
       </c>
-      <c r="H56" s="9" t="n">
+      <c r="K56" s="13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="L56" s="10" t="n">
         <v>401.3776132773282</v>
       </c>
-      <c r="I56" s="9" t="n">
+      <c r="M56" s="10" t="n">
         <v>-1.543505524015483</v>
       </c>
     </row>
@@ -2083,27 +2695,39 @@
           <t>Cranium, spongiosa</t>
         </is>
       </c>
-      <c r="B57" s="9" t="n">
+      <c r="B57" s="13" t="n">
+        <v>1.165</v>
+      </c>
+      <c r="C57" s="10" t="n">
         <v>382.0729263310096</v>
       </c>
-      <c r="C57" s="9" t="n">
+      <c r="D57" s="13" t="n">
+        <v>1.246</v>
+      </c>
+      <c r="E57" s="10" t="n">
         <v>377.5412025451843</v>
       </c>
-      <c r="D57" s="9" t="n">
+      <c r="F57" s="10" t="n">
         <v>-1.186088694988883</v>
       </c>
-      <c r="F57" s="8" t="inlineStr">
+      <c r="H57" s="8" t="inlineStr">
         <is>
           <t>Cranium, spongiosa</t>
         </is>
       </c>
-      <c r="G57" s="9" t="n">
+      <c r="I57" s="13" t="n">
+        <v>1.252</v>
+      </c>
+      <c r="J57" s="10" t="n">
         <v>391.3114655804995</v>
       </c>
-      <c r="H57" s="9" t="n">
+      <c r="K57" s="13" t="n">
+        <v>1.263</v>
+      </c>
+      <c r="L57" s="10" t="n">
         <v>384.2030953009521</v>
       </c>
-      <c r="I57" s="9" t="n">
+      <c r="M57" s="10" t="n">
         <v>-1.816550473163973</v>
       </c>
     </row>
@@ -2113,27 +2737,39 @@
           <t>Femora, upper, cortical</t>
         </is>
       </c>
-      <c r="B58" s="9" t="n">
+      <c r="B58" s="13" t="n">
+        <v>1.904</v>
+      </c>
+      <c r="C58" s="10" t="n">
         <v>253.5475845797583</v>
       </c>
-      <c r="C58" s="9" t="n">
+      <c r="D58" s="13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="E58" s="10" t="n">
         <v>476.8930839971037</v>
       </c>
-      <c r="D58" s="9" t="n">
+      <c r="F58" s="10" t="n">
         <v>88.08819842931213</v>
       </c>
-      <c r="F58" s="8" t="inlineStr">
+      <c r="H58" s="8" t="inlineStr">
         <is>
           <t>Femora, upper, cortical</t>
         </is>
       </c>
-      <c r="G58" s="9" t="n">
+      <c r="I58" s="13" t="n">
+        <v>1.904</v>
+      </c>
+      <c r="J58" s="10" t="n">
         <v>244.1262813453543</v>
       </c>
-      <c r="H58" s="9" t="n">
+      <c r="K58" s="13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="L58" s="10" t="n">
         <v>428.9066628027048</v>
       </c>
-      <c r="I58" s="9" t="n">
+      <c r="M58" s="10" t="n">
         <v>75.69049118310622</v>
       </c>
     </row>
@@ -2143,27 +2779,39 @@
           <t>Femora, upper, spongiosa</t>
         </is>
       </c>
-      <c r="B59" s="9" t="n">
+      <c r="B59" s="13" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="C59" s="10" t="n">
         <v>413.232292237906</v>
       </c>
-      <c r="C59" s="9" t="n">
+      <c r="D59" s="13" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="E59" s="10" t="n">
         <v>365.6957318364376</v>
       </c>
-      <c r="D59" s="9" t="n">
+      <c r="F59" s="10" t="n">
         <v>-11.50359284460291</v>
       </c>
-      <c r="F59" s="8" t="inlineStr">
+      <c r="H59" s="8" t="inlineStr">
         <is>
           <t>Femora, upper, spongiosa</t>
         </is>
       </c>
-      <c r="G59" s="9" t="n">
+      <c r="I59" s="13" t="n">
+        <v>1.046</v>
+      </c>
+      <c r="J59" s="10" t="n">
         <v>232.8040702002445</v>
       </c>
-      <c r="H59" s="9" t="n">
+      <c r="K59" s="13" t="n">
+        <v>1.128</v>
+      </c>
+      <c r="L59" s="10" t="n">
         <v>228.4189948372717</v>
       </c>
-      <c r="I59" s="9" t="n">
+      <c r="M59" s="10" t="n">
         <v>-1.883590505613159</v>
       </c>
     </row>
@@ -2173,27 +2821,39 @@
           <t>Femora, upper, medullary cavity</t>
         </is>
       </c>
-      <c r="B60" s="9" t="n">
+      <c r="B60" s="13" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="C60" s="10" t="n">
         <v>26.04535047202931</v>
       </c>
-      <c r="C60" s="9" t="n">
+      <c r="D60" s="13" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="E60" s="10" t="n">
         <v>90.71643477443247</v>
       </c>
-      <c r="D60" s="9" t="n">
+      <c r="F60" s="10" t="n">
         <v>248.3018394083616</v>
       </c>
-      <c r="F60" s="8" t="inlineStr">
+      <c r="H60" s="8" t="inlineStr">
         <is>
           <t>Femora, upper, medullary cavity</t>
         </is>
       </c>
-      <c r="G60" s="9" t="n">
+      <c r="I60" s="13" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="J60" s="10" t="n">
         <v>39.51633699157236</v>
       </c>
-      <c r="H60" s="9" t="n">
+      <c r="K60" s="13" t="n">
+        <v>0.962</v>
+      </c>
+      <c r="L60" s="10" t="n">
         <v>82.16810467669316</v>
       </c>
-      <c r="I60" s="9" t="n">
+      <c r="M60" s="10" t="n">
         <v>107.9345175495824</v>
       </c>
     </row>
@@ -2203,27 +2863,39 @@
           <t>Femora, lower, cortical</t>
         </is>
       </c>
-      <c r="B61" s="9" t="n">
+      <c r="B61" s="13" t="n">
+        <v>1.904</v>
+      </c>
+      <c r="C61" s="10" t="n">
         <v>307.760973463655</v>
       </c>
-      <c r="C61" s="9" t="n">
+      <c r="D61" s="13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="E61" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D61" s="9" t="n">
+      <c r="F61" s="10" t="n">
         <v>-100</v>
       </c>
-      <c r="F61" s="8" t="inlineStr">
+      <c r="H61" s="8" t="inlineStr">
         <is>
           <t>Femora, lower, cortical</t>
         </is>
       </c>
-      <c r="G61" s="9" t="n">
+      <c r="I61" s="13" t="n">
+        <v>1.904</v>
+      </c>
+      <c r="J61" s="10" t="n">
         <v>240.9294144816426</v>
       </c>
-      <c r="H61" s="9" t="n">
+      <c r="K61" s="13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="L61" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="I61" s="9" t="n">
+      <c r="M61" s="10" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -2233,27 +2905,39 @@
           <t>Femora, lower, spongiosa</t>
         </is>
       </c>
-      <c r="B62" s="9" t="n">
+      <c r="B62" s="13" t="n">
+        <v>1.109</v>
+      </c>
+      <c r="C62" s="10" t="n">
         <v>373.6519545295038</v>
       </c>
-      <c r="C62" s="9" t="n">
+      <c r="D62" s="13" t="n">
+        <v>1.108</v>
+      </c>
+      <c r="E62" s="10" t="n">
         <v>317.3479720860003</v>
       </c>
-      <c r="D62" s="9" t="n">
+      <c r="F62" s="10" t="n">
         <v>-15.06856360871992</v>
       </c>
-      <c r="F62" s="8" t="inlineStr">
+      <c r="H62" s="8" t="inlineStr">
         <is>
           <t>Femora, lower, spongiosa</t>
         </is>
       </c>
-      <c r="G62" s="9" t="n">
+      <c r="I62" s="13" t="n">
+        <v>1.117</v>
+      </c>
+      <c r="J62" s="10" t="n">
         <v>166.3336944750482</v>
       </c>
-      <c r="H62" s="9" t="n">
+      <c r="K62" s="13" t="n">
+        <v>1.082</v>
+      </c>
+      <c r="L62" s="10" t="n">
         <v>144.4325735996959</v>
       </c>
-      <c r="I62" s="9" t="n">
+      <c r="M62" s="10" t="n">
         <v>-13.16697795024189</v>
       </c>
     </row>
@@ -2263,27 +2947,39 @@
           <t>Femora, lower, medullary cavity</t>
         </is>
       </c>
-      <c r="B63" s="9" t="n">
+      <c r="B63" s="13" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="C63" s="10" t="n">
         <v>82.17888245638618</v>
       </c>
-      <c r="C63" s="9" t="n">
+      <c r="D63" s="13" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="E63" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D63" s="9" t="n">
+      <c r="F63" s="10" t="n">
         <v>-100</v>
       </c>
-      <c r="F63" s="8" t="inlineStr">
+      <c r="H63" s="8" t="inlineStr">
         <is>
           <t>Femora, lower, medullary cavity</t>
         </is>
       </c>
-      <c r="G63" s="9" t="n">
+      <c r="I63" s="13" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="J63" s="10" t="n">
         <v>56.76212663048454</v>
       </c>
-      <c r="H63" s="9" t="n">
+      <c r="K63" s="13" t="n">
+        <v>0.962</v>
+      </c>
+      <c r="L63" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="I63" s="9" t="n">
+      <c r="M63" s="10" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -2293,27 +2989,39 @@
           <t>Tibiae, fibulae, and patellae, cortical</t>
         </is>
       </c>
-      <c r="B64" s="9" t="n">
+      <c r="B64" s="13" t="n">
+        <v>1.904</v>
+      </c>
+      <c r="C64" s="10" t="n">
         <v>536.6511904030592</v>
       </c>
-      <c r="C64" s="9" t="n">
+      <c r="D64" s="13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="E64" s="10" t="n">
         <v>469.7195965884835</v>
       </c>
-      <c r="D64" s="9" t="n">
+      <c r="F64" s="10" t="n">
         <v>-12.47208522248983</v>
       </c>
-      <c r="F64" s="8" t="inlineStr">
+      <c r="H64" s="8" t="inlineStr">
         <is>
           <t>Tibiae, fibulae, and patellae, cortical</t>
         </is>
       </c>
-      <c r="G64" s="9" t="n">
+      <c r="I64" s="13" t="n">
+        <v>1.904</v>
+      </c>
+      <c r="J64" s="10" t="n">
         <v>544.8452248227562</v>
       </c>
-      <c r="H64" s="9" t="n">
+      <c r="K64" s="13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="L64" s="10" t="n">
         <v>514.1989095979508</v>
       </c>
-      <c r="I64" s="9" t="n">
+      <c r="M64" s="10" t="n">
         <v>-5.624774491650361</v>
       </c>
     </row>
@@ -2323,27 +3031,39 @@
           <t>Tibiae, fibulae, and patellae, spongiosa</t>
         </is>
       </c>
-      <c r="B65" s="9" t="n">
+      <c r="B65" s="13" t="n">
+        <v>1.109</v>
+      </c>
+      <c r="C65" s="10" t="n">
         <v>621.4076462600168</v>
       </c>
-      <c r="C65" s="9" t="n">
+      <c r="D65" s="13" t="n">
+        <v>1.108</v>
+      </c>
+      <c r="E65" s="10" t="n">
         <v>537.3251727742338</v>
       </c>
-      <c r="D65" s="9" t="n">
+      <c r="F65" s="10" t="n">
         <v>-13.53096859876749</v>
       </c>
-      <c r="F65" s="8" t="inlineStr">
+      <c r="H65" s="8" t="inlineStr">
         <is>
           <t>Tibiae, fibulae, and patellae, spongiosa</t>
         </is>
       </c>
-      <c r="G65" s="9" t="n">
+      <c r="I65" s="13" t="n">
+        <v>1.117</v>
+      </c>
+      <c r="J65" s="10" t="n">
         <v>558.5291489631189</v>
       </c>
-      <c r="H65" s="9" t="n">
+      <c r="K65" s="13" t="n">
+        <v>1.082</v>
+      </c>
+      <c r="L65" s="10" t="n">
         <v>505.0518950575055</v>
       </c>
-      <c r="I65" s="9" t="n">
+      <c r="M65" s="10" t="n">
         <v>-9.574657653032302</v>
       </c>
     </row>
@@ -2353,27 +3073,39 @@
           <t>Tibiae, fibulae, and patellae, medullary cavity</t>
         </is>
       </c>
-      <c r="B66" s="9" t="n">
+      <c r="B66" s="13" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="C66" s="10" t="n">
         <v>79.81493797477779</v>
       </c>
-      <c r="C66" s="9" t="n">
+      <c r="D66" s="13" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="E66" s="10" t="n">
         <v>69.5516653786115</v>
       </c>
-      <c r="D66" s="9" t="n">
+      <c r="F66" s="10" t="n">
         <v>-12.85883677490243</v>
       </c>
-      <c r="F66" s="8" t="inlineStr">
+      <c r="H66" s="8" t="inlineStr">
         <is>
           <t>Tibiae, fibulae, and patellae, medullary cavity</t>
         </is>
       </c>
-      <c r="G66" s="9" t="n">
+      <c r="I66" s="13" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="J66" s="10" t="n">
         <v>88.88342749908533</v>
       </c>
-      <c r="H66" s="9" t="n">
+      <c r="K66" s="13" t="n">
+        <v>0.962</v>
+      </c>
+      <c r="L66" s="10" t="n">
         <v>82.04822460350658</v>
       </c>
-      <c r="I66" s="9" t="n">
+      <c r="M66" s="10" t="n">
         <v>-7.690075740665024</v>
       </c>
     </row>
@@ -2383,27 +3115,39 @@
           <t>Ankles and foot, cortical</t>
         </is>
       </c>
-      <c r="B67" s="9" t="n">
+      <c r="B67" s="13" t="n">
+        <v>1.904</v>
+      </c>
+      <c r="C67" s="10" t="n">
         <v>234.8823427804357</v>
       </c>
-      <c r="C67" s="9" t="n">
+      <c r="D67" s="13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="E67" s="10" t="n">
         <v>211.1229883817119</v>
       </c>
-      <c r="D67" s="9" t="n">
+      <c r="F67" s="10" t="n">
         <v>-10.11542805537055</v>
       </c>
-      <c r="F67" s="8" t="inlineStr">
+      <c r="H67" s="8" t="inlineStr">
         <is>
           <t>Ankles and foot, cortical</t>
         </is>
       </c>
-      <c r="G67" s="9" t="n">
+      <c r="I67" s="13" t="n">
+        <v>1.904</v>
+      </c>
+      <c r="J67" s="10" t="n">
         <v>173.4757470187165</v>
       </c>
-      <c r="H67" s="9" t="n">
+      <c r="K67" s="13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="L67" s="10" t="n">
         <v>173.0474589083803</v>
       </c>
-      <c r="I67" s="9" t="n">
+      <c r="M67" s="10" t="n">
         <v>-0.246886448219187</v>
       </c>
     </row>
@@ -2413,27 +3157,39 @@
           <t>Ankles and foot, spongiosa</t>
         </is>
       </c>
-      <c r="B68" s="9" t="n">
+      <c r="B68" s="13" t="n">
+        <v>1.109</v>
+      </c>
+      <c r="C68" s="10" t="n">
         <v>432.6150423840299</v>
       </c>
-      <c r="C68" s="9" t="n">
+      <c r="D68" s="13" t="n">
+        <v>1.108</v>
+      </c>
+      <c r="E68" s="10" t="n">
         <v>385.1509133308857</v>
       </c>
-      <c r="D68" s="9" t="n">
+      <c r="F68" s="10" t="n">
         <v>-10.97144676051523</v>
       </c>
-      <c r="F68" s="8" t="inlineStr">
+      <c r="H68" s="8" t="inlineStr">
         <is>
           <t>Ankles and foot, spongiosa</t>
         </is>
       </c>
-      <c r="G68" s="9" t="n">
+      <c r="I68" s="13" t="n">
+        <v>1.117</v>
+      </c>
+      <c r="J68" s="10" t="n">
         <v>257.4510646483038</v>
       </c>
-      <c r="H68" s="9" t="n">
+      <c r="K68" s="13" t="n">
+        <v>1.082</v>
+      </c>
+      <c r="L68" s="10" t="n">
         <v>246.6050482317172</v>
       </c>
-      <c r="I68" s="9" t="n">
+      <c r="M68" s="10" t="n">
         <v>-4.212845820390387</v>
       </c>
     </row>
@@ -2443,27 +3199,39 @@
           <t>Mandible, cortical</t>
         </is>
       </c>
-      <c r="B69" s="9" t="n">
+      <c r="B69" s="13" t="n">
+        <v>1.904</v>
+      </c>
+      <c r="C69" s="10" t="n">
         <v>76.87705057615418</v>
       </c>
-      <c r="C69" s="9" t="n">
+      <c r="D69" s="13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="E69" s="10" t="n">
         <v>69.25944554349583</v>
       </c>
-      <c r="D69" s="9" t="n">
+      <c r="F69" s="10" t="n">
         <v>-9.908815407938121</v>
       </c>
-      <c r="F69" s="8" t="inlineStr">
+      <c r="H69" s="8" t="inlineStr">
         <is>
           <t>Mandible, cortical</t>
         </is>
       </c>
-      <c r="G69" s="9" t="n">
+      <c r="I69" s="13" t="n">
+        <v>1.904</v>
+      </c>
+      <c r="J69" s="10" t="n">
         <v>45.39409987461431</v>
       </c>
-      <c r="H69" s="9" t="n">
+      <c r="K69" s="13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="L69" s="10" t="n">
         <v>43.32609214136052</v>
       </c>
-      <c r="I69" s="9" t="n">
+      <c r="M69" s="10" t="n">
         <v>-4.55567516255626</v>
       </c>
     </row>
@@ -2473,27 +3241,39 @@
           <t>Mandible, spongiosa</t>
         </is>
       </c>
-      <c r="B70" s="9" t="n">
+      <c r="B70" s="13" t="n">
+        <v>1.271</v>
+      </c>
+      <c r="C70" s="10" t="n">
         <v>56.28731655252362</v>
       </c>
-      <c r="C70" s="9" t="n">
+      <c r="D70" s="13" t="n">
+        <v>1.058</v>
+      </c>
+      <c r="E70" s="10" t="n">
         <v>41.77709050068317</v>
       </c>
-      <c r="D70" s="9" t="n">
+      <c r="F70" s="10" t="n">
         <v>-25.77885559404925</v>
       </c>
-      <c r="F70" s="8" t="inlineStr">
+      <c r="H70" s="8" t="inlineStr">
         <is>
           <t>Mandible, spongiosa</t>
         </is>
       </c>
-      <c r="G70" s="9" t="n">
+      <c r="I70" s="13" t="n">
+        <v>1.189</v>
+      </c>
+      <c r="J70" s="10" t="n">
         <v>33.47875705671152</v>
       </c>
-      <c r="H70" s="9" t="n">
+      <c r="K70" s="13" t="n">
+        <v>1.282</v>
+      </c>
+      <c r="L70" s="10" t="n">
         <v>34.10600306007597</v>
       </c>
-      <c r="I70" s="9" t="n">
+      <c r="M70" s="10" t="n">
         <v>1.873564189679805</v>
       </c>
     </row>
@@ -2503,27 +3283,39 @@
           <t>Pelvis, cortical</t>
         </is>
       </c>
-      <c r="B71" s="9" t="n">
+      <c r="B71" s="13" t="n">
+        <v>1.904</v>
+      </c>
+      <c r="C71" s="10" t="n">
         <v>402.5946743318735</v>
       </c>
-      <c r="C71" s="9" t="n">
+      <c r="D71" s="13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="E71" s="10" t="n">
         <v>348.5577562187389</v>
       </c>
-      <c r="D71" s="9" t="n">
+      <c r="F71" s="10" t="n">
         <v>-13.4221641661832</v>
       </c>
-      <c r="F71" s="8" t="inlineStr">
+      <c r="H71" s="8" t="inlineStr">
         <is>
           <t>Pelvis, cortical</t>
         </is>
       </c>
-      <c r="G71" s="9" t="n">
+      <c r="I71" s="13" t="n">
+        <v>1.904</v>
+      </c>
+      <c r="J71" s="10" t="n">
         <v>262.4576300753822</v>
       </c>
-      <c r="H71" s="9" t="n">
+      <c r="K71" s="13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="L71" s="10" t="n">
         <v>243.3605178945173</v>
       </c>
-      <c r="I71" s="9" t="n">
+      <c r="M71" s="10" t="n">
         <v>-7.276264810963918</v>
       </c>
     </row>
@@ -2533,27 +3325,39 @@
           <t>Pelvis, spongiosa</t>
         </is>
       </c>
-      <c r="B72" s="9" t="n">
+      <c r="B72" s="13" t="n">
+        <v>1.121</v>
+      </c>
+      <c r="C72" s="10" t="n">
         <v>619.6715755278943</v>
       </c>
-      <c r="C72" s="9" t="n">
+      <c r="D72" s="13" t="n">
+        <v>1.119</v>
+      </c>
+      <c r="E72" s="10" t="n">
         <v>531.0782605875355</v>
       </c>
-      <c r="D72" s="9" t="n">
+      <c r="F72" s="10" t="n">
         <v>-14.296817610988</v>
       </c>
-      <c r="F72" s="8" t="inlineStr">
+      <c r="H72" s="8" t="inlineStr">
         <is>
           <t>Pelvis, spongiosa</t>
         </is>
       </c>
-      <c r="G72" s="9" t="n">
+      <c r="I72" s="13" t="n">
+        <v>1.105</v>
+      </c>
+      <c r="J72" s="10" t="n">
         <v>455.5985822992558</v>
       </c>
-      <c r="H72" s="9" t="n">
+      <c r="K72" s="13" t="n">
+        <v>1.102</v>
+      </c>
+      <c r="L72" s="10" t="n">
         <v>417.7857656740704</v>
       </c>
-      <c r="I72" s="9" t="n">
+      <c r="M72" s="10" t="n">
         <v>-8.29959049353414</v>
       </c>
     </row>
@@ -2563,27 +3367,39 @@
           <t>Ribs, cortical</t>
         </is>
       </c>
-      <c r="B73" s="9" t="n">
+      <c r="B73" s="13" t="n">
+        <v>1.904</v>
+      </c>
+      <c r="C73" s="10" t="n">
         <v>368.7971195707965</v>
       </c>
-      <c r="C73" s="9" t="n">
+      <c r="D73" s="13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="E73" s="10" t="n">
         <v>319.2966262583255</v>
       </c>
-      <c r="D73" s="9" t="n">
+      <c r="F73" s="10" t="n">
         <v>-13.42214748588039</v>
       </c>
-      <c r="F73" s="8" t="inlineStr">
+      <c r="H73" s="8" t="inlineStr">
         <is>
           <t>Ribs, cortical</t>
         </is>
       </c>
-      <c r="G73" s="9" t="n">
+      <c r="I73" s="13" t="n">
+        <v>1.904</v>
+      </c>
+      <c r="J73" s="10" t="n">
         <v>164.5039907825759</v>
       </c>
-      <c r="H73" s="9" t="n">
+      <c r="K73" s="13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="L73" s="10" t="n">
         <v>152.5401244466648</v>
       </c>
-      <c r="I73" s="9" t="n">
+      <c r="M73" s="10" t="n">
         <v>-7.272690637471343</v>
       </c>
     </row>
@@ -2593,27 +3409,39 @@
           <t>Ribs, spongiosa</t>
         </is>
       </c>
-      <c r="B74" s="9" t="n">
+      <c r="B74" s="13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="C74" s="10" t="n">
         <v>457.3511943175166</v>
       </c>
-      <c r="C74" s="9" t="n">
+      <c r="D74" s="13" t="n">
+        <v>1.144</v>
+      </c>
+      <c r="E74" s="10" t="n">
         <v>383.9392266767585</v>
       </c>
-      <c r="D74" s="9" t="n">
+      <c r="F74" s="10" t="n">
         <v>-16.05155262583434</v>
       </c>
-      <c r="F74" s="8" t="inlineStr">
+      <c r="H74" s="8" t="inlineStr">
         <is>
           <t>Ribs, spongiosa</t>
         </is>
       </c>
-      <c r="G74" s="9" t="n">
+      <c r="I74" s="13" t="n">
+        <v>1.087</v>
+      </c>
+      <c r="J74" s="10" t="n">
         <v>277.3248898477021</v>
       </c>
-      <c r="H74" s="9" t="n">
+      <c r="K74" s="13" t="n">
+        <v>1.122</v>
+      </c>
+      <c r="L74" s="10" t="n">
         <v>263.2110384218241</v>
       </c>
-      <c r="I74" s="9" t="n">
+      <c r="M74" s="10" t="n">
         <v>-5.089284064488004</v>
       </c>
     </row>
@@ -2623,27 +3451,39 @@
           <t>Scapulae, cortical</t>
         </is>
       </c>
-      <c r="B75" s="9" t="n">
+      <c r="B75" s="13" t="n">
+        <v>1.904</v>
+      </c>
+      <c r="C75" s="10" t="n">
         <v>223.3331223438105</v>
       </c>
-      <c r="C75" s="9" t="n">
+      <c r="D75" s="13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="E75" s="10" t="n">
         <v>193.3570415184743</v>
       </c>
-      <c r="D75" s="9" t="n">
+      <c r="F75" s="10" t="n">
         <v>-13.42213842297405</v>
       </c>
-      <c r="F75" s="8" t="inlineStr">
+      <c r="H75" s="8" t="inlineStr">
         <is>
           <t>Scapulae, cortical</t>
         </is>
       </c>
-      <c r="G75" s="9" t="n">
+      <c r="I75" s="13" t="n">
+        <v>1.904</v>
+      </c>
+      <c r="J75" s="10" t="n">
         <v>121.6643960915294</v>
       </c>
-      <c r="H75" s="9" t="n">
+      <c r="K75" s="13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="L75" s="10" t="n">
         <v>112.8302137540836</v>
       </c>
-      <c r="I75" s="9" t="n">
+      <c r="M75" s="10" t="n">
         <v>-7.261107292884418</v>
       </c>
     </row>
@@ -2653,27 +3493,39 @@
           <t>Scapulae, spongiosa</t>
         </is>
       </c>
-      <c r="B76" s="9" t="n">
+      <c r="B76" s="13" t="n">
+        <v>1.201</v>
+      </c>
+      <c r="C76" s="10" t="n">
         <v>156.6702567564742</v>
       </c>
-      <c r="C76" s="9" t="n">
+      <c r="D76" s="13" t="n">
+        <v>1.186</v>
+      </c>
+      <c r="E76" s="10" t="n">
         <v>132.8313721393768</v>
       </c>
-      <c r="D76" s="9" t="n">
+      <c r="F76" s="10" t="n">
         <v>-15.21596064922018</v>
       </c>
-      <c r="F76" s="8" t="inlineStr">
+      <c r="H76" s="8" t="inlineStr">
         <is>
           <t>Scapulae, spongiosa</t>
         </is>
       </c>
-      <c r="G76" s="9" t="n">
+      <c r="I76" s="13" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="J76" s="10" t="n">
         <v>96.73013880387251</v>
       </c>
-      <c r="H76" s="9" t="n">
+      <c r="K76" s="13" t="n">
+        <v>1.121</v>
+      </c>
+      <c r="L76" s="10" t="n">
         <v>88.63232418777415</v>
       </c>
-      <c r="I76" s="9" t="n">
+      <c r="M76" s="10" t="n">
         <v>-8.371552771693295</v>
       </c>
     </row>
@@ -2683,27 +3535,39 @@
           <t>Cervical spine, cortical</t>
         </is>
       </c>
-      <c r="B77" s="9" t="n">
+      <c r="B77" s="13" t="n">
+        <v>1.904</v>
+      </c>
+      <c r="C77" s="10" t="n">
         <v>103.9434065885498</v>
       </c>
-      <c r="C77" s="9" t="n">
+      <c r="D77" s="13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="E77" s="10" t="n">
         <v>92.2290039689491</v>
       </c>
-      <c r="D77" s="9" t="n">
+      <c r="F77" s="10" t="n">
         <v>-11.26998142938592</v>
       </c>
-      <c r="F77" s="8" t="inlineStr">
+      <c r="H77" s="8" t="inlineStr">
         <is>
           <t>Cervical spine, cortical</t>
         </is>
       </c>
-      <c r="G77" s="9" t="n">
+      <c r="I77" s="13" t="n">
+        <v>1.904</v>
+      </c>
+      <c r="J77" s="10" t="n">
         <v>71.59649605583554</v>
       </c>
-      <c r="H77" s="9" t="n">
+      <c r="K77" s="13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="L77" s="10" t="n">
         <v>67.96930637862533</v>
       </c>
-      <c r="I77" s="9" t="n">
+      <c r="M77" s="10" t="n">
         <v>-5.066155296736164</v>
       </c>
     </row>
@@ -2713,27 +3577,39 @@
           <t>Cervical spine, spongiosa</t>
         </is>
       </c>
-      <c r="B78" s="9" t="n">
+      <c r="B78" s="13" t="n">
+        <v>1.049</v>
+      </c>
+      <c r="C78" s="10" t="n">
         <v>78.91527127702106</v>
       </c>
-      <c r="C78" s="9" t="n">
+      <c r="D78" s="13" t="n">
+        <v>1.176</v>
+      </c>
+      <c r="E78" s="10" t="n">
         <v>77.9381854077111</v>
       </c>
-      <c r="D78" s="9" t="n">
+      <c r="F78" s="10" t="n">
         <v>-1.238145486290019</v>
       </c>
-      <c r="F78" s="8" t="inlineStr">
+      <c r="H78" s="8" t="inlineStr">
         <is>
           <t>Cervical spine, spongiosa</t>
         </is>
       </c>
-      <c r="G78" s="9" t="n">
+      <c r="I78" s="13" t="n">
+        <v>1.129</v>
+      </c>
+      <c r="J78" s="10" t="n">
         <v>75.60121987196192</v>
       </c>
-      <c r="H78" s="9" t="n">
+      <c r="K78" s="13" t="n">
+        <v>1.131</v>
+      </c>
+      <c r="L78" s="10" t="n">
         <v>71.23321071777416</v>
       </c>
-      <c r="I78" s="9" t="n">
+      <c r="M78" s="10" t="n">
         <v>-5.777696658315054</v>
       </c>
     </row>
@@ -2743,27 +3619,39 @@
           <t>Thoracic spine, cortical</t>
         </is>
       </c>
-      <c r="B79" s="9" t="n">
+      <c r="B79" s="13" t="n">
+        <v>1.904</v>
+      </c>
+      <c r="C79" s="10" t="n">
         <v>289.4401290938737</v>
       </c>
-      <c r="C79" s="9" t="n">
+      <c r="D79" s="13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="E79" s="10" t="n">
         <v>250.5910112654597</v>
       </c>
-      <c r="D79" s="9" t="n">
+      <c r="F79" s="10" t="n">
         <v>-13.42216020633894</v>
       </c>
-      <c r="F79" s="8" t="inlineStr">
+      <c r="H79" s="8" t="inlineStr">
         <is>
           <t>Thoracic spine, cortical</t>
         </is>
       </c>
-      <c r="G79" s="9" t="n">
+      <c r="I79" s="13" t="n">
+        <v>1.904</v>
+      </c>
+      <c r="J79" s="10" t="n">
         <v>205.8277997231691</v>
       </c>
-      <c r="H79" s="9" t="n">
+      <c r="K79" s="13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="L79" s="10" t="n">
         <v>190.8491621175247</v>
       </c>
-      <c r="I79" s="9" t="n">
+      <c r="M79" s="10" t="n">
         <v>-7.277266543095817</v>
       </c>
     </row>
@@ -2773,27 +3661,39 @@
           <t>Thoracic spine, spongiosa</t>
         </is>
       </c>
-      <c r="B80" s="9" t="n">
+      <c r="B80" s="13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="C80" s="10" t="n">
         <v>345.2217732828088</v>
       </c>
-      <c r="C80" s="9" t="n">
+      <c r="D80" s="13" t="n">
+        <v>1.128</v>
+      </c>
+      <c r="E80" s="10" t="n">
         <v>312.4611115611329</v>
       </c>
-      <c r="D80" s="9" t="n">
+      <c r="F80" s="10" t="n">
         <v>-9.489743769677604</v>
       </c>
-      <c r="F80" s="8" t="inlineStr">
+      <c r="H80" s="8" t="inlineStr">
         <is>
           <t>Thoracic spine, spongiosa</t>
         </is>
       </c>
-      <c r="G80" s="9" t="n">
+      <c r="I80" s="13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="J80" s="10" t="n">
         <v>271.9154945745766</v>
       </c>
-      <c r="H80" s="9" t="n">
+      <c r="K80" s="13" t="n">
+        <v>1.073</v>
+      </c>
+      <c r="L80" s="10" t="n">
         <v>248.4058947544106</v>
       </c>
-      <c r="I80" s="9" t="n">
+      <c r="M80" s="10" t="n">
         <v>-8.645921357643784</v>
       </c>
     </row>
@@ -2803,27 +3703,39 @@
           <t>Lumbar spine, cortical</t>
         </is>
       </c>
-      <c r="B81" s="9" t="n">
+      <c r="B81" s="13" t="n">
+        <v>1.904</v>
+      </c>
+      <c r="C81" s="10" t="n">
         <v>188.0474514135563</v>
       </c>
-      <c r="C81" s="9" t="n">
+      <c r="D81" s="13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="E81" s="10" t="n">
         <v>162.8074637577067</v>
       </c>
-      <c r="D81" s="9" t="n">
+      <c r="F81" s="10" t="n">
         <v>-13.42213758608272</v>
       </c>
-      <c r="F81" s="8" t="inlineStr">
+      <c r="H81" s="8" t="inlineStr">
         <is>
           <t>Lumbar spine, cortical</t>
         </is>
       </c>
-      <c r="G81" s="9" t="n">
+      <c r="I81" s="13" t="n">
+        <v>1.904</v>
+      </c>
+      <c r="J81" s="10" t="n">
         <v>156.1749221177983</v>
       </c>
-      <c r="H81" s="9" t="n">
+      <c r="K81" s="13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="L81" s="10" t="n">
         <v>144.8096673364435</v>
       </c>
-      <c r="I81" s="9" t="n">
+      <c r="M81" s="10" t="n">
         <v>-7.277259772079405</v>
       </c>
     </row>
@@ -2833,27 +3745,39 @@
           <t>Lumbar spine, spongiosa</t>
         </is>
       </c>
-      <c r="B82" s="9" t="n">
+      <c r="B82" s="13" t="n">
+        <v>1.108</v>
+      </c>
+      <c r="C82" s="10" t="n">
         <v>291.5843646006671</v>
       </c>
-      <c r="C82" s="9" t="n">
+      <c r="D82" s="13" t="n">
+        <v>1.121</v>
+      </c>
+      <c r="E82" s="10" t="n">
         <v>253.2809870790819</v>
       </c>
-      <c r="D82" s="9" t="n">
+      <c r="F82" s="10" t="n">
         <v>-13.1362933585423</v>
       </c>
-      <c r="F82" s="8" t="inlineStr">
+      <c r="H82" s="8" t="inlineStr">
         <is>
           <t>Lumbar spine, spongiosa</t>
         </is>
       </c>
-      <c r="G82" s="9" t="n">
+      <c r="I82" s="13" t="n">
+        <v>1.165</v>
+      </c>
+      <c r="J82" s="10" t="n">
         <v>264.9755764768744</v>
       </c>
-      <c r="H82" s="9" t="n">
+      <c r="K82" s="13" t="n">
+        <v>1.053</v>
+      </c>
+      <c r="L82" s="10" t="n">
         <v>220.2217703911557</v>
       </c>
-      <c r="I82" s="9" t="n">
+      <c r="M82" s="10" t="n">
         <v>-16.88978534579188</v>
       </c>
     </row>
@@ -2863,27 +3787,39 @@
           <t>Sacrum, cortical</t>
         </is>
       </c>
-      <c r="B83" s="9" t="n">
+      <c r="B83" s="13" t="n">
+        <v>1.904</v>
+      </c>
+      <c r="C83" s="10" t="n">
         <v>110.3202882636614</v>
       </c>
-      <c r="C83" s="9" t="n">
+      <c r="D83" s="13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="E83" s="10" t="n">
         <v>95.51294005459862</v>
       </c>
-      <c r="D83" s="9" t="n">
+      <c r="F83" s="10" t="n">
         <v>-13.42214423304787</v>
       </c>
-      <c r="F83" s="8" t="inlineStr">
+      <c r="H83" s="8" t="inlineStr">
         <is>
           <t>Sacrum, cortical</t>
         </is>
       </c>
-      <c r="G83" s="9" t="n">
+      <c r="I83" s="13" t="n">
+        <v>1.904</v>
+      </c>
+      <c r="J83" s="10" t="n">
         <v>80.24045854089545</v>
       </c>
-      <c r="H83" s="9" t="n">
+      <c r="K83" s="13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="L83" s="10" t="n">
         <v>74.40116340204167</v>
       </c>
-      <c r="I83" s="9" t="n">
+      <c r="M83" s="10" t="n">
         <v>-7.277245475706883</v>
       </c>
     </row>
@@ -2893,27 +3829,39 @@
           <t>Sacrum, spongiosa</t>
         </is>
       </c>
-      <c r="B84" s="9" t="n">
+      <c r="B84" s="13" t="n">
+        <v>1.033</v>
+      </c>
+      <c r="C84" s="10" t="n">
         <v>192.2239989586902</v>
       </c>
-      <c r="C84" s="9" t="n">
+      <c r="D84" s="13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E84" s="10" t="n">
         <v>172.5454335837504</v>
       </c>
-      <c r="D84" s="9" t="n">
+      <c r="F84" s="10" t="n">
         <v>-10.23730932742107</v>
       </c>
-      <c r="F84" s="8" t="inlineStr">
+      <c r="H84" s="8" t="inlineStr">
         <is>
           <t>Sacrum, spongiosa</t>
         </is>
       </c>
-      <c r="G84" s="9" t="n">
+      <c r="I84" s="13" t="n">
+        <v>1.052</v>
+      </c>
+      <c r="J84" s="10" t="n">
         <v>154.8396844742894</v>
       </c>
-      <c r="H84" s="9" t="n">
+      <c r="K84" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="L84" s="10" t="n">
         <v>139.5330708667508</v>
       </c>
-      <c r="I84" s="9" t="n">
+      <c r="M84" s="10" t="n">
         <v>-9.885459053670559</v>
       </c>
     </row>
@@ -2923,27 +3871,39 @@
           <t>Sternum, cortical</t>
         </is>
       </c>
-      <c r="B85" s="9" t="n">
+      <c r="B85" s="13" t="n">
+        <v>1.904</v>
+      </c>
+      <c r="C85" s="10" t="n">
         <v>9.990523424843239</v>
       </c>
-      <c r="C85" s="9" t="n">
+      <c r="D85" s="13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="E85" s="10" t="n">
         <v>8.649563831982755</v>
       </c>
-      <c r="D85" s="9" t="n">
+      <c r="F85" s="10" t="n">
         <v>-13.42231568694335</v>
       </c>
-      <c r="F85" s="8" t="inlineStr">
+      <c r="H85" s="8" t="inlineStr">
         <is>
           <t>Sternum, cortical</t>
         </is>
       </c>
-      <c r="G85" s="9" t="n">
+      <c r="I85" s="13" t="n">
+        <v>1.904</v>
+      </c>
+      <c r="J85" s="10" t="n">
         <v>1.685296248133067</v>
       </c>
-      <c r="H85" s="9" t="n">
+      <c r="K85" s="13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="L85" s="10" t="n">
         <v>1.562657706787305</v>
       </c>
-      <c r="I85" s="9" t="n">
+      <c r="M85" s="10" t="n">
         <v>-7.276972311640639</v>
       </c>
     </row>
@@ -2953,27 +3913,39 @@
           <t>Sternum, spongiosa</t>
         </is>
       </c>
-      <c r="B86" s="9" t="n">
+      <c r="B86" s="13" t="n">
+        <v>1.041</v>
+      </c>
+      <c r="C86" s="10" t="n">
         <v>61.42008371703705</v>
       </c>
-      <c r="C86" s="9" t="n">
+      <c r="D86" s="13" t="n">
+        <v>1.131</v>
+      </c>
+      <c r="E86" s="10" t="n">
         <v>57.29210655749119</v>
       </c>
-      <c r="D86" s="9" t="n">
+      <c r="F86" s="10" t="n">
         <v>-6.720891457203949</v>
       </c>
-      <c r="F86" s="8" t="inlineStr">
+      <c r="H86" s="8" t="inlineStr">
         <is>
           <t>Sternum, spongiosa</t>
         </is>
       </c>
-      <c r="G86" s="9" t="n">
+      <c r="I86" s="13" t="n">
+        <v>1.073</v>
+      </c>
+      <c r="J86" s="10" t="n">
         <v>51.34696060100694</v>
       </c>
-      <c r="H86" s="9" t="n">
+      <c r="K86" s="13" t="n">
+        <v>1.035</v>
+      </c>
+      <c r="L86" s="10" t="n">
         <v>45.54150485321176</v>
       </c>
-      <c r="I86" s="9" t="n">
+      <c r="M86" s="10" t="n">
         <v>-11.30632793030662</v>
       </c>
     </row>
@@ -2983,27 +3955,39 @@
           <t>Cartilage, costal</t>
         </is>
       </c>
-      <c r="B87" s="9" t="n">
+      <c r="B87" s="13" t="n">
+        <v>1.099</v>
+      </c>
+      <c r="C87" s="10" t="n">
         <v>56.33146378933584</v>
       </c>
-      <c r="C87" s="9" t="n">
+      <c r="D87" s="13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E87" s="10" t="n">
         <v>48.40815238279955</v>
       </c>
-      <c r="D87" s="9" t="n">
+      <c r="F87" s="10" t="n">
         <v>-14.06551662880143</v>
       </c>
-      <c r="F87" s="8" t="inlineStr">
+      <c r="H87" s="8" t="inlineStr">
         <is>
           <t>Cartilage, costal</t>
         </is>
       </c>
-      <c r="G87" s="9" t="n">
+      <c r="I87" s="13" t="n">
+        <v>1.099</v>
+      </c>
+      <c r="J87" s="10" t="n">
         <v>41.95907371777562</v>
       </c>
-      <c r="H87" s="9" t="n">
+      <c r="K87" s="13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="L87" s="10" t="n">
         <v>37.91438212385106</v>
       </c>
-      <c r="I87" s="9" t="n">
+      <c r="M87" s="10" t="n">
         <v>-9.639611258174781</v>
       </c>
     </row>
@@ -3013,27 +3997,39 @@
           <t>Cartilage, discs</t>
         </is>
       </c>
-      <c r="B88" s="9" t="n">
+      <c r="B88" s="13" t="n">
+        <v>1.099</v>
+      </c>
+      <c r="C88" s="10" t="n">
         <v>82.06297945824626</v>
       </c>
-      <c r="C88" s="9" t="n">
+      <c r="D88" s="13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E88" s="10" t="n">
         <v>70.59826231047724</v>
       </c>
-      <c r="D88" s="9" t="n">
+      <c r="F88" s="10" t="n">
         <v>-13.97063234049683</v>
       </c>
-      <c r="F88" s="8" t="inlineStr">
+      <c r="H88" s="8" t="inlineStr">
         <is>
           <t>Cartilage, discs</t>
         </is>
       </c>
-      <c r="G88" s="9" t="n">
+      <c r="I88" s="13" t="n">
+        <v>1.099</v>
+      </c>
+      <c r="J88" s="10" t="n">
         <v>69.35056397215195</v>
       </c>
-      <c r="H88" s="9" t="n">
+      <c r="K88" s="13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="L88" s="10" t="n">
         <v>62.7454476850912</v>
       </c>
-      <c r="I88" s="9" t="n">
+      <c r="M88" s="10" t="n">
         <v>-9.524243075677166</v>
       </c>
     </row>
@@ -3043,27 +4039,39 @@
           <t>Brain</t>
         </is>
       </c>
-      <c r="B89" s="9" t="n">
+      <c r="B89" s="13" t="n">
+        <v>1.041</v>
+      </c>
+      <c r="C89" s="10" t="n">
         <v>1517.389677890501</v>
       </c>
-      <c r="C89" s="9" t="n">
+      <c r="D89" s="13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E89" s="10" t="n">
         <v>1391.614789976581</v>
       </c>
-      <c r="D89" s="9" t="n">
+      <c r="F89" s="10" t="n">
         <v>-8.288898346057973</v>
       </c>
-      <c r="F89" s="8" t="inlineStr">
+      <c r="H89" s="8" t="inlineStr">
         <is>
           <t>Brain</t>
         </is>
       </c>
-      <c r="G89" s="9" t="n">
+      <c r="I89" s="13" t="n">
+        <v>1.041</v>
+      </c>
+      <c r="J89" s="10" t="n">
         <v>1349.568113424691</v>
       </c>
-      <c r="H89" s="9" t="n">
+      <c r="K89" s="13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L89" s="10" t="n">
         <v>1273.925538632035</v>
       </c>
-      <c r="I89" s="9" t="n">
+      <c r="M89" s="10" t="n">
         <v>-5.60494680040299</v>
       </c>
     </row>
@@ -3073,27 +4081,39 @@
           <t>Breast, left, adipose tissue</t>
         </is>
       </c>
-      <c r="B90" s="9" t="n">
+      <c r="B90" s="13" t="n">
+        <v>0.953</v>
+      </c>
+      <c r="C90" s="10" t="n">
         <v>7.769025257475426</v>
       </c>
-      <c r="C90" s="9" t="n">
+      <c r="D90" s="13" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="E90" s="10" t="n">
         <v>6.732042454204267</v>
       </c>
-      <c r="D90" s="9" t="n">
+      <c r="F90" s="10" t="n">
         <v>-13.34765648075819</v>
       </c>
-      <c r="F90" s="8" t="inlineStr">
+      <c r="H90" s="8" t="inlineStr">
         <is>
           <t>Breast, left, adipose tissue</t>
         </is>
       </c>
-      <c r="G90" s="9" t="n">
+      <c r="I90" s="13" t="n">
+        <v>0.952</v>
+      </c>
+      <c r="J90" s="10" t="n">
         <v>153.6633058179418</v>
       </c>
-      <c r="H90" s="9" t="n">
+      <c r="K90" s="13" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="L90" s="10" t="n">
         <v>153.1554866464738</v>
       </c>
-      <c r="I90" s="9" t="n">
+      <c r="M90" s="10" t="n">
         <v>-0.3304752352976655</v>
       </c>
     </row>
@@ -3103,27 +4123,39 @@
           <t>Breast, left, glandular tissue</t>
         </is>
       </c>
-      <c r="B91" s="9" t="n">
+      <c r="B91" s="13" t="n">
+        <v>1.021</v>
+      </c>
+      <c r="C91" s="10" t="n">
         <v>5.18013406814562</v>
       </c>
-      <c r="C91" s="9" t="n">
+      <c r="D91" s="13" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="E91" s="10" t="n">
         <v>4.31243793262585</v>
       </c>
-      <c r="D91" s="9" t="n">
+      <c r="F91" s="10" t="n">
         <v>-16.75045711375548</v>
       </c>
-      <c r="F91" s="8" t="inlineStr">
+      <c r="H91" s="8" t="inlineStr">
         <is>
           <t>Breast, left, glandular tissue</t>
         </is>
       </c>
-      <c r="G91" s="9" t="n">
+      <c r="I91" s="13" t="n">
+        <v>1.021</v>
+      </c>
+      <c r="J91" s="10" t="n">
         <v>102.4914601223685</v>
       </c>
-      <c r="H91" s="9" t="n">
+      <c r="K91" s="13" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L91" s="10" t="n">
         <v>91.37957759069934</v>
       </c>
-      <c r="I91" s="9" t="n">
+      <c r="M91" s="10" t="n">
         <v>-10.84176429763246</v>
       </c>
     </row>
@@ -3133,27 +4165,39 @@
           <t>Breast, right, adipose tissue</t>
         </is>
       </c>
-      <c r="B92" s="9" t="n">
+      <c r="B92" s="13" t="n">
+        <v>0.953</v>
+      </c>
+      <c r="C92" s="10" t="n">
         <v>7.769029192598022</v>
       </c>
-      <c r="C92" s="9" t="n">
+      <c r="D92" s="13" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="E92" s="10" t="n">
         <v>6.732193969063989</v>
       </c>
-      <c r="D92" s="9" t="n">
+      <c r="F92" s="10" t="n">
         <v>-13.34575012952561</v>
       </c>
-      <c r="F92" s="8" t="inlineStr">
+      <c r="H92" s="8" t="inlineStr">
         <is>
           <t>Breast, right, adipose tissue</t>
         </is>
       </c>
-      <c r="G92" s="9" t="n">
+      <c r="I92" s="13" t="n">
+        <v>0.952</v>
+      </c>
+      <c r="J92" s="10" t="n">
         <v>153.6633035399048</v>
       </c>
-      <c r="H92" s="9" t="n">
+      <c r="K92" s="13" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="L92" s="10" t="n">
         <v>153.2097315772018</v>
       </c>
-      <c r="I92" s="9" t="n">
+      <c r="M92" s="10" t="n">
         <v>-0.2951725963545866</v>
       </c>
     </row>
@@ -3163,27 +4207,39 @@
           <t>Breast, right, glandular tissue</t>
         </is>
       </c>
-      <c r="B93" s="9" t="n">
+      <c r="B93" s="13" t="n">
+        <v>1.021</v>
+      </c>
+      <c r="C93" s="10" t="n">
         <v>5.180136443151125</v>
       </c>
-      <c r="C93" s="9" t="n">
+      <c r="D93" s="13" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="E93" s="10" t="n">
         <v>4.312442428388342</v>
       </c>
-      <c r="D93" s="9" t="n">
+      <c r="F93" s="10" t="n">
         <v>-16.7504084937762</v>
       </c>
-      <c r="F93" s="8" t="inlineStr">
+      <c r="H93" s="8" t="inlineStr">
         <is>
           <t>Breast, right, glandular tissue</t>
         </is>
       </c>
-      <c r="G93" s="9" t="n">
+      <c r="I93" s="13" t="n">
+        <v>1.021</v>
+      </c>
+      <c r="J93" s="10" t="n">
         <v>102.4914613905986</v>
       </c>
-      <c r="H93" s="9" t="n">
+      <c r="K93" s="13" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L93" s="10" t="n">
         <v>91.37957860708529</v>
       </c>
-      <c r="I93" s="9" t="n">
+      <c r="M93" s="10" t="n">
         <v>-10.84176440919846</v>
       </c>
     </row>
@@ -3193,27 +4249,39 @@
           <t>Eye lens, sensitive, left</t>
         </is>
       </c>
-      <c r="B94" s="9" t="n">
+      <c r="B94" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="C94" s="10" t="n">
         <v>0.03888948807554384</v>
       </c>
-      <c r="C94" s="9" t="n">
+      <c r="D94" s="13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="E94" s="10" t="n">
         <v>0.03672736342168315</v>
       </c>
-      <c r="D94" s="9" t="n">
+      <c r="F94" s="10" t="n">
         <v>-5.559663448540935</v>
       </c>
-      <c r="F94" s="8" t="inlineStr">
+      <c r="H94" s="8" t="inlineStr">
         <is>
           <t>Eye lens, sensitive, left</t>
         </is>
       </c>
-      <c r="G94" s="9" t="n">
+      <c r="I94" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="J94" s="10" t="n">
         <v>0.03888949784434238</v>
       </c>
-      <c r="H94" s="9" t="n">
+      <c r="K94" s="13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="L94" s="10" t="n">
         <v>0.03845281954611536</v>
       </c>
-      <c r="I94" s="9" t="n">
+      <c r="M94" s="10" t="n">
         <v>-1.122869469734102</v>
       </c>
     </row>
@@ -3223,27 +4291,39 @@
           <t>Eye lens, insensitive, left</t>
         </is>
       </c>
-      <c r="B95" s="9" t="n">
+      <c r="B95" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="C95" s="10" t="n">
         <v>0.1892705687789634</v>
       </c>
-      <c r="C95" s="9" t="n">
+      <c r="D95" s="13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="E95" s="10" t="n">
         <v>0.1787473842862213</v>
       </c>
-      <c r="D95" s="9" t="n">
+      <c r="F95" s="10" t="n">
         <v>-5.559863089454482</v>
       </c>
-      <c r="F95" s="8" t="inlineStr">
+      <c r="H95" s="8" t="inlineStr">
         <is>
           <t>Eye lens, insensitive, left</t>
         </is>
       </c>
-      <c r="G95" s="9" t="n">
+      <c r="I95" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="J95" s="10" t="n">
         <v>0.1892705671457856</v>
       </c>
-      <c r="H95" s="9" t="n">
+      <c r="K95" s="13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="L95" s="10" t="n">
         <v>0.1871447666050843</v>
       </c>
-      <c r="I95" s="9" t="n">
+      <c r="M95" s="10" t="n">
         <v>-1.12315431435458</v>
       </c>
     </row>
@@ -3253,27 +4333,39 @@
           <t>Cornea, left</t>
         </is>
       </c>
-      <c r="B96" s="9" t="n">
+      <c r="B96" s="13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C96" s="10" t="n">
         <v>1.113285068612355</v>
       </c>
-      <c r="C96" s="9" t="n">
+      <c r="D96" s="13" t="n">
+        <v>1.075</v>
+      </c>
+      <c r="E96" s="10" t="n">
         <v>0.9992055347185655</v>
       </c>
-      <c r="D96" s="9" t="n">
+      <c r="F96" s="10" t="n">
         <v>-10.24710894901182</v>
       </c>
-      <c r="F96" s="8" t="inlineStr">
+      <c r="H96" s="8" t="inlineStr">
         <is>
           <t>Cornea, left</t>
         </is>
       </c>
-      <c r="G96" s="9" t="n">
+      <c r="I96" s="13" t="n">
+        <v>1.087</v>
+      </c>
+      <c r="J96" s="10" t="n">
         <v>1.100128016004906</v>
       </c>
-      <c r="H96" s="9" t="n">
+      <c r="K96" s="13" t="n">
+        <v>1.075</v>
+      </c>
+      <c r="L96" s="10" t="n">
         <v>1.046167727731152</v>
       </c>
-      <c r="I96" s="9" t="n">
+      <c r="M96" s="10" t="n">
         <v>-4.904909927638196</v>
       </c>
     </row>
@@ -3283,27 +4375,39 @@
           <t>Aqueous, left</t>
         </is>
       </c>
-      <c r="B97" s="9" t="n">
+      <c r="B97" s="13" t="n">
+        <v>1.025</v>
+      </c>
+      <c r="C97" s="10" t="n">
         <v>0.3075716047013278</v>
       </c>
-      <c r="C97" s="9" t="n">
+      <c r="D97" s="13" t="n">
+        <v>1.004</v>
+      </c>
+      <c r="E97" s="10" t="n">
         <v>0.2766889362010252</v>
       </c>
-      <c r="D97" s="9" t="n">
+      <c r="F97" s="10" t="n">
         <v>-10.04080611742156</v>
       </c>
-      <c r="F97" s="8" t="inlineStr">
+      <c r="H97" s="8" t="inlineStr">
         <is>
           <t>Aqueous, left</t>
         </is>
       </c>
-      <c r="G97" s="9" t="n">
+      <c r="I97" s="13" t="n">
+        <v>1.014</v>
+      </c>
+      <c r="J97" s="10" t="n">
         <v>0.3042709125857634</v>
       </c>
-      <c r="H97" s="9" t="n">
+      <c r="K97" s="13" t="n">
+        <v>1.004</v>
+      </c>
+      <c r="L97" s="10" t="n">
         <v>0.2896879255298594</v>
       </c>
-      <c r="I97" s="9" t="n">
+      <c r="M97" s="10" t="n">
         <v>-4.79276409696034</v>
       </c>
     </row>
@@ -3313,27 +4417,39 @@
           <t>Vitreous, left</t>
         </is>
       </c>
-      <c r="B98" s="9" t="n">
+      <c r="B98" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="C98" s="10" t="n">
         <v>6.121993940073037</v>
       </c>
-      <c r="C98" s="9" t="n">
+      <c r="D98" s="13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="E98" s="10" t="n">
         <v>5.507983367131021</v>
       </c>
-      <c r="D98" s="9" t="n">
+      <c r="F98" s="10" t="n">
         <v>-10.02958478810076</v>
       </c>
-      <c r="F98" s="8" t="inlineStr">
+      <c r="H98" s="8" t="inlineStr">
         <is>
           <t>Vitreous, left</t>
         </is>
       </c>
-      <c r="G98" s="9" t="n">
+      <c r="I98" s="13" t="n">
+        <v>1.019</v>
+      </c>
+      <c r="J98" s="10" t="n">
         <v>6.050738358097164</v>
       </c>
-      <c r="H98" s="9" t="n">
+      <c r="K98" s="13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L98" s="10" t="n">
         <v>5.76671494713745</v>
       </c>
-      <c r="I98" s="9" t="n">
+      <c r="M98" s="10" t="n">
         <v>-4.694028962260967</v>
       </c>
     </row>
@@ -3343,27 +4459,39 @@
           <t xml:space="preserve"> Eye lens, sensitive, right</t>
         </is>
       </c>
-      <c r="B99" s="9" t="n">
+      <c r="B99" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="C99" s="10" t="n">
         <v>0.03888931397097076</v>
       </c>
-      <c r="C99" s="9" t="n">
+      <c r="D99" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E99" s="10" t="n">
         <v>0.03571379299920699</v>
       </c>
-      <c r="D99" s="9" t="n">
+      <c r="F99" s="10" t="n">
         <v>-8.165536101084635</v>
       </c>
-      <c r="F99" s="8" t="inlineStr">
+      <c r="H99" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve"> Eye lens, sensitive, right</t>
         </is>
       </c>
-      <c r="G99" s="9" t="n">
+      <c r="I99" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="J99" s="10" t="n">
         <v>0.03888931586449868</v>
       </c>
-      <c r="H99" s="9" t="n">
+      <c r="K99" s="13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="L99" s="10" t="n">
         <v>0.03844699144957885</v>
       </c>
-      <c r="I99" s="9" t="n">
+      <c r="M99" s="10" t="n">
         <v>-1.137393150501845</v>
       </c>
     </row>
@@ -3373,27 +4501,39 @@
           <t>Eye lens, insensitive, right</t>
         </is>
       </c>
-      <c r="B100" s="9" t="n">
+      <c r="B100" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="C100" s="10" t="n">
         <v>0.1892706524250732</v>
       </c>
-      <c r="C100" s="9" t="n">
+      <c r="D100" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E100" s="10" t="n">
         <v>0.173815260029019</v>
       </c>
-      <c r="D100" s="9" t="n">
+      <c r="F100" s="10" t="n">
         <v>-8.165762730792363</v>
       </c>
-      <c r="F100" s="8" t="inlineStr">
+      <c r="H100" s="8" t="inlineStr">
         <is>
           <t>Eye lens, insensitive, right</t>
         </is>
       </c>
-      <c r="G100" s="9" t="n">
+      <c r="I100" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="J100" s="10" t="n">
         <v>0.1892706620145763</v>
       </c>
-      <c r="H100" s="9" t="n">
+      <c r="K100" s="13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="L100" s="10" t="n">
         <v>0.1871191385084229</v>
       </c>
-      <c r="I100" s="9" t="n">
+      <c r="M100" s="10" t="n">
         <v>-1.136744323316026</v>
       </c>
     </row>
@@ -3403,27 +4543,39 @@
           <t>Cornea, right</t>
         </is>
       </c>
-      <c r="B101" s="9" t="n">
+      <c r="B101" s="13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C101" s="10" t="n">
         <v>1.1132816955125</v>
       </c>
-      <c r="C101" s="9" t="n">
+      <c r="D101" s="13" t="n">
+        <v>1.075</v>
+      </c>
+      <c r="E101" s="10" t="n">
         <v>0.999156144210588</v>
       </c>
-      <c r="D101" s="9" t="n">
+      <c r="F101" s="10" t="n">
         <v>-10.25127348827686</v>
       </c>
-      <c r="F101" s="8" t="inlineStr">
+      <c r="H101" s="8" t="inlineStr">
         <is>
           <t>Cornea, right</t>
         </is>
       </c>
-      <c r="G101" s="9" t="n">
+      <c r="I101" s="13" t="n">
+        <v>1.087</v>
+      </c>
+      <c r="J101" s="10" t="n">
         <v>1.100123804647425</v>
       </c>
-      <c r="H101" s="9" t="n">
+      <c r="K101" s="13" t="n">
+        <v>1.075</v>
+      </c>
+      <c r="L101" s="10" t="n">
         <v>1.046000144123806</v>
       </c>
-      <c r="I101" s="9" t="n">
+      <c r="M101" s="10" t="n">
         <v>-4.919779055318644</v>
       </c>
     </row>
@@ -3433,27 +4585,39 @@
           <t>Aqueous, right</t>
         </is>
       </c>
-      <c r="B102" s="9" t="n">
+      <c r="B102" s="13" t="n">
+        <v>1.025</v>
+      </c>
+      <c r="C102" s="10" t="n">
         <v>0.3075715920117542</v>
       </c>
-      <c r="C102" s="9" t="n">
+      <c r="D102" s="13" t="n">
+        <v>1.004</v>
+      </c>
+      <c r="E102" s="10" t="n">
         <v>0.276668781803608</v>
       </c>
-      <c r="D102" s="9" t="n">
+      <c r="F102" s="10" t="n">
         <v>-10.04735515592257</v>
       </c>
-      <c r="F102" s="8" t="inlineStr">
+      <c r="H102" s="8" t="inlineStr">
         <is>
           <t>Aqueous, right</t>
         </is>
       </c>
-      <c r="G102" s="9" t="n">
+      <c r="I102" s="13" t="n">
+        <v>1.014</v>
+      </c>
+      <c r="J102" s="10" t="n">
         <v>0.3042708208962531</v>
       </c>
-      <c r="H102" s="9" t="n">
+      <c r="K102" s="13" t="n">
+        <v>1.004</v>
+      </c>
+      <c r="L102" s="10" t="n">
         <v>0.2896482989277734</v>
       </c>
-      <c r="I102" s="9" t="n">
+      <c r="M102" s="10" t="n">
         <v>-4.805758871457956</v>
       </c>
     </row>
@@ -3463,27 +4627,39 @@
           <t>Vitreous, right</t>
         </is>
       </c>
-      <c r="B103" s="9" t="n">
+      <c r="B103" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="C103" s="10" t="n">
         <v>6.12199522014182</v>
       </c>
-      <c r="C103" s="9" t="n">
+      <c r="D103" s="13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="E103" s="10" t="n">
         <v>5.507563821027222</v>
       </c>
-      <c r="D103" s="9" t="n">
+      <c r="F103" s="10" t="n">
         <v>-10.03645669459319</v>
       </c>
-      <c r="F103" s="8" t="inlineStr">
+      <c r="H103" s="8" t="inlineStr">
         <is>
           <t>Vitreous, right</t>
         </is>
       </c>
-      <c r="G103" s="9" t="n">
+      <c r="I103" s="13" t="n">
+        <v>1.019</v>
+      </c>
+      <c r="J103" s="10" t="n">
         <v>6.050740749821898</v>
       </c>
-      <c r="H103" s="9" t="n">
+      <c r="K103" s="13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L103" s="10" t="n">
         <v>5.76595580023578</v>
       </c>
-      <c r="I103" s="9" t="n">
+      <c r="M103" s="10" t="n">
         <v>-4.706612981137902</v>
       </c>
     </row>
@@ -3493,27 +4669,39 @@
           <t>Gallbladder wall</t>
         </is>
       </c>
-      <c r="B104" s="9" t="n">
+      <c r="B104" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="C104" s="10" t="n">
         <v>10.36361275982263</v>
       </c>
-      <c r="C104" s="9" t="n">
+      <c r="D104" s="13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E104" s="10" t="n">
         <v>7.523034707152386</v>
       </c>
-      <c r="D104" s="9" t="n">
+      <c r="F104" s="10" t="n">
         <v>-27.40914889914178</v>
       </c>
-      <c r="F104" s="8" t="inlineStr">
+      <c r="H104" s="8" t="inlineStr">
         <is>
           <t>Gallbladder wall</t>
         </is>
       </c>
-      <c r="G104" s="9" t="n">
+      <c r="I104" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="J104" s="10" t="n">
         <v>8.201118428032061</v>
       </c>
-      <c r="H104" s="9" t="n">
+      <c r="K104" s="13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L104" s="10" t="n">
         <v>6.74984845781629</v>
       </c>
-      <c r="I104" s="9" t="n">
+      <c r="M104" s="10" t="n">
         <v>-17.69600064858492</v>
       </c>
     </row>
@@ -3523,27 +4711,39 @@
           <t>Gallbladder contents</t>
         </is>
       </c>
-      <c r="B105" s="9" t="n">
+      <c r="B105" s="13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="C105" s="10" t="n">
         <v>57.99999932578972</v>
       </c>
-      <c r="C105" s="9" t="n">
+      <c r="D105" s="13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E105" s="10" t="n">
         <v>42.14348484254489</v>
       </c>
-      <c r="D105" s="9" t="n">
+      <c r="F105" s="10" t="n">
         <v>-27.3388183923551</v>
       </c>
-      <c r="F105" s="8" t="inlineStr">
+      <c r="H105" s="8" t="inlineStr">
         <is>
           <t>Gallbladder contents</t>
         </is>
       </c>
-      <c r="G105" s="9" t="n">
+      <c r="I105" s="13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="J105" s="10" t="n">
         <v>47.999998457865</v>
       </c>
-      <c r="H105" s="9" t="n">
+      <c r="K105" s="13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L105" s="10" t="n">
         <v>39.54429699521371</v>
       </c>
-      <c r="I105" s="9" t="n">
+      <c r="M105" s="10" t="n">
         <v>-17.61604527982186</v>
       </c>
     </row>
@@ -3553,27 +4753,39 @@
           <t>Stomach wall, 0~60 um</t>
         </is>
       </c>
-      <c r="B106" s="9" t="n">
+      <c r="B106" s="13" t="n">
+        <v>1.037</v>
+      </c>
+      <c r="C106" s="10" t="n">
         <v>1.783738388344085</v>
       </c>
-      <c r="C106" s="9" t="n">
+      <c r="D106" s="13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E106" s="10" t="n">
         <v>1.550660292666682</v>
       </c>
-      <c r="D106" s="9" t="n">
+      <c r="F106" s="10" t="n">
         <v>-13.06683184038992</v>
       </c>
-      <c r="F106" s="8" t="inlineStr">
+      <c r="H106" s="8" t="inlineStr">
         <is>
           <t>Stomach wall, 0~60 um</t>
         </is>
       </c>
-      <c r="G106" s="9" t="n">
+      <c r="I106" s="13" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="J106" s="10" t="n">
         <v>1.560964174616183</v>
       </c>
-      <c r="H106" s="9" t="n">
+      <c r="K106" s="13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L106" s="10" t="n">
         <v>1.426992562477645</v>
       </c>
-      <c r="I106" s="9" t="n">
+      <c r="M106" s="10" t="n">
         <v>-8.582619275774173</v>
       </c>
     </row>
@@ -3583,27 +4795,39 @@
           <t>Stomach wall, 60~100 um</t>
         </is>
       </c>
-      <c r="B107" s="9" t="n">
+      <c r="B107" s="13" t="n">
+        <v>1.037</v>
+      </c>
+      <c r="C107" s="10" t="n">
         <v>1.192821131229141</v>
       </c>
-      <c r="C107" s="9" t="n">
+      <c r="D107" s="13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E107" s="10" t="n">
         <v>1.036953335097191</v>
       </c>
-      <c r="D107" s="9" t="n">
+      <c r="F107" s="10" t="n">
         <v>-13.06715584182649</v>
       </c>
-      <c r="F107" s="8" t="inlineStr">
+      <c r="H107" s="8" t="inlineStr">
         <is>
           <t>Stomach wall, 60~100 um</t>
         </is>
       </c>
-      <c r="G107" s="9" t="n">
+      <c r="I107" s="13" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="J107" s="10" t="n">
         <v>1.043729984649013</v>
       </c>
-      <c r="H107" s="9" t="n">
+      <c r="K107" s="13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L107" s="10" t="n">
         <v>0.9541424047073794</v>
       </c>
-      <c r="I107" s="9" t="n">
+      <c r="M107" s="10" t="n">
         <v>-8.583405790699835</v>
       </c>
     </row>
@@ -3613,27 +4837,39 @@
           <t>Stomach wall, 100~300 um</t>
         </is>
       </c>
-      <c r="B108" s="9" t="n">
+      <c r="B108" s="13" t="n">
+        <v>1.037</v>
+      </c>
+      <c r="C108" s="10" t="n">
         <v>6.008017357407735</v>
       </c>
-      <c r="C108" s="9" t="n">
+      <c r="D108" s="13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E108" s="10" t="n">
         <v>5.222914525475723</v>
       </c>
-      <c r="D108" s="9" t="n">
+      <c r="F108" s="10" t="n">
         <v>-13.06758594770037</v>
       </c>
-      <c r="F108" s="8" t="inlineStr">
+      <c r="H108" s="8" t="inlineStr">
         <is>
           <t>Stomach wall, 100~300 um</t>
         </is>
       </c>
-      <c r="G108" s="9" t="n">
+      <c r="I108" s="13" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="J108" s="10" t="n">
         <v>5.256181108004264</v>
       </c>
-      <c r="H108" s="9" t="n">
+      <c r="K108" s="13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L108" s="10" t="n">
         <v>4.805066992636326</v>
       </c>
-      <c r="I108" s="9" t="n">
+      <c r="M108" s="10" t="n">
         <v>-8.582545123511219</v>
       </c>
     </row>
@@ -3643,27 +4879,39 @@
           <t>Stomach wall, 300 um~surface</t>
         </is>
       </c>
-      <c r="B109" s="9" t="n">
+      <c r="B109" s="13" t="n">
+        <v>1.037</v>
+      </c>
+      <c r="C109" s="10" t="n">
         <v>185.286098491188</v>
       </c>
-      <c r="C109" s="9" t="n">
+      <c r="D109" s="13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E109" s="10" t="n">
         <v>161.0741867673027</v>
       </c>
-      <c r="D109" s="9" t="n">
+      <c r="F109" s="10" t="n">
         <v>-13.06731153661631</v>
       </c>
-      <c r="F109" s="8" t="inlineStr">
+      <c r="H109" s="8" t="inlineStr">
         <is>
           <t>Stomach wall, 300 um~surface</t>
         </is>
       </c>
-      <c r="G109" s="9" t="n">
+      <c r="I109" s="13" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="J109" s="10" t="n">
         <v>165.0120124331308</v>
       </c>
-      <c r="H109" s="9" t="n">
+      <c r="K109" s="13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L109" s="10" t="n">
         <v>149.1450966152588</v>
       </c>
-      <c r="I109" s="9" t="n">
+      <c r="M109" s="10" t="n">
         <v>-9.615612575055343</v>
       </c>
     </row>
@@ -3673,27 +4921,39 @@
           <t>Stomach contents</t>
         </is>
       </c>
-      <c r="B110" s="9" t="n">
+      <c r="B110" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="C110" s="10" t="n">
         <v>249.9999865241507</v>
       </c>
-      <c r="C110" s="9" t="n">
+      <c r="D110" s="13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E110" s="10" t="n">
         <v>212.577033509906</v>
       </c>
-      <c r="D110" s="9" t="n">
+      <c r="F110" s="10" t="n">
         <v>-14.96918201258765</v>
       </c>
-      <c r="F110" s="8" t="inlineStr">
+      <c r="H110" s="8" t="inlineStr">
         <is>
           <t>Stomach contents</t>
         </is>
       </c>
-      <c r="G110" s="9" t="n">
+      <c r="I110" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="J110" s="10" t="n">
         <v>230.0000005520811</v>
       </c>
-      <c r="H110" s="9" t="n">
+      <c r="K110" s="13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L110" s="10" t="n">
         <v>205.384602506435</v>
       </c>
-      <c r="I110" s="9" t="n">
+      <c r="M110" s="10" t="n">
         <v>-10.70234695067845</v>
       </c>
     </row>
@@ -3703,27 +4963,39 @@
           <t>Small intestine wall, 0~130 um</t>
         </is>
       </c>
-      <c r="B111" s="9" t="n">
+      <c r="B111" s="13" t="n">
+        <v>1.037</v>
+      </c>
+      <c r="C111" s="10" t="n">
         <v>14.54747903922977</v>
       </c>
-      <c r="C111" s="9" t="n">
+      <c r="D111" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E111" s="10" t="n">
         <v>12.52605977435901</v>
       </c>
-      <c r="D111" s="9" t="n">
+      <c r="F111" s="10" t="n">
         <v>-13.89532344002461</v>
       </c>
-      <c r="F111" s="8" t="inlineStr">
+      <c r="H111" s="8" t="inlineStr">
         <is>
           <t>Small intestine wall, 0~130 um</t>
         </is>
       </c>
-      <c r="G111" s="9" t="n">
+      <c r="I111" s="13" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="J111" s="10" t="n">
         <v>12.34122772569162</v>
       </c>
-      <c r="H111" s="9" t="n">
+      <c r="K111" s="13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L111" s="10" t="n">
         <v>11.17251515131173</v>
       </c>
-      <c r="I111" s="9" t="n">
+      <c r="M111" s="10" t="n">
         <v>-9.469986295989814</v>
       </c>
     </row>
@@ -3733,27 +5005,39 @@
           <t>Small intestine wall, 130~150 um</t>
         </is>
       </c>
-      <c r="B112" s="9" t="n">
+      <c r="B112" s="13" t="n">
+        <v>1.037</v>
+      </c>
+      <c r="C112" s="10" t="n">
         <v>2.264442034599205</v>
       </c>
-      <c r="C112" s="9" t="n">
+      <c r="D112" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E112" s="10" t="n">
         <v>1.949794867676684</v>
       </c>
-      <c r="D112" s="9" t="n">
+      <c r="F112" s="10" t="n">
         <v>-13.89513010776678</v>
       </c>
-      <c r="F112" s="8" t="inlineStr">
+      <c r="H112" s="8" t="inlineStr">
         <is>
           <t>Small intestine wall, 130~150 um</t>
         </is>
       </c>
-      <c r="G112" s="9" t="n">
+      <c r="I112" s="13" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="J112" s="10" t="n">
         <v>1.921644612778237</v>
       </c>
-      <c r="H112" s="9" t="n">
+      <c r="K112" s="13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L112" s="10" t="n">
         <v>1.739663537968136</v>
       </c>
-      <c r="I112" s="9" t="n">
+      <c r="M112" s="10" t="n">
         <v>-9.470069210508189</v>
       </c>
     </row>
@@ -3763,27 +5047,39 @@
           <t>Small intestine wall, 150~200 um</t>
         </is>
       </c>
-      <c r="B113" s="9" t="n">
+      <c r="B113" s="13" t="n">
+        <v>1.037</v>
+      </c>
+      <c r="C113" s="10" t="n">
         <v>5.691843593243338</v>
       </c>
-      <c r="C113" s="9" t="n">
+      <c r="D113" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E113" s="10" t="n">
         <v>4.900942804304474</v>
       </c>
-      <c r="D113" s="9" t="n">
+      <c r="F113" s="10" t="n">
         <v>-13.89533594840387</v>
       </c>
-      <c r="F113" s="8" t="inlineStr">
+      <c r="H113" s="8" t="inlineStr">
         <is>
           <t>Small intestine wall, 150~200 um</t>
         </is>
       </c>
-      <c r="G113" s="9" t="n">
+      <c r="I113" s="13" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="J113" s="10" t="n">
         <v>4.831023157744231</v>
       </c>
-      <c r="H113" s="9" t="n">
+      <c r="K113" s="13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L113" s="10" t="n">
         <v>4.373519362157237</v>
       </c>
-      <c r="I113" s="9" t="n">
+      <c r="M113" s="10" t="n">
         <v>-9.470122180093577</v>
       </c>
     </row>
@@ -3793,27 +5089,39 @@
           <t>Small intestine wall, 200 um~surface</t>
         </is>
       </c>
-      <c r="B114" s="9" t="n">
+      <c r="B114" s="13" t="n">
+        <v>1.037</v>
+      </c>
+      <c r="C114" s="10" t="n">
         <v>840.0963485350128</v>
       </c>
-      <c r="C114" s="9" t="n">
+      <c r="D114" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E114" s="10" t="n">
         <v>723.3328910938814</v>
       </c>
-      <c r="D114" s="9" t="n">
+      <c r="F114" s="10" t="n">
         <v>-13.89881739692683</v>
       </c>
-      <c r="F114" s="8" t="inlineStr">
+      <c r="H114" s="8" t="inlineStr">
         <is>
           <t>Small intestine wall, 200 um~surface</t>
         </is>
       </c>
-      <c r="G114" s="9" t="n">
+      <c r="I114" s="13" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="J114" s="10" t="n">
         <v>736.6617235837316</v>
       </c>
-      <c r="H114" s="9" t="n">
+      <c r="K114" s="13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L114" s="10" t="n">
         <v>666.9105237767609</v>
       </c>
-      <c r="I114" s="9" t="n">
+      <c r="M114" s="10" t="n">
         <v>-9.468552196202513</v>
       </c>
     </row>
@@ -3823,27 +5131,39 @@
           <t>Small intestine contents, -500~0 um</t>
         </is>
       </c>
-      <c r="B115" s="9" t="n">
+      <c r="B115" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="C115" s="10" t="n">
         <v>53.33739729294845</v>
       </c>
-      <c r="C115" s="9" t="n">
+      <c r="D115" s="13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E115" s="10" t="n">
         <v>45.35323292114162</v>
       </c>
-      <c r="D115" s="9" t="n">
+      <c r="F115" s="10" t="n">
         <v>-14.96916755790479</v>
       </c>
-      <c r="F115" s="8" t="inlineStr">
+      <c r="H115" s="8" t="inlineStr">
         <is>
           <t>Small intestine contents, -500~0 um</t>
         </is>
       </c>
-      <c r="G115" s="9" t="n">
+      <c r="I115" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="J115" s="10" t="n">
         <v>45.22669118586805</v>
       </c>
-      <c r="H115" s="9" t="n">
+      <c r="K115" s="13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L115" s="10" t="n">
         <v>40.38637523449758</v>
       </c>
-      <c r="I115" s="9" t="n">
+      <c r="M115" s="10" t="n">
         <v>-10.7023437365299</v>
       </c>
     </row>
@@ -3853,27 +5173,39 @@
           <t>Small intestine contents, centre~500 um</t>
         </is>
       </c>
-      <c r="B116" s="9" t="n">
+      <c r="B116" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="C116" s="10" t="n">
         <v>296.6626081088315</v>
       </c>
-      <c r="C116" s="9" t="n">
+      <c r="D116" s="13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E116" s="10" t="n">
         <v>252.25465055939</v>
       </c>
-      <c r="D116" s="9" t="n">
+      <c r="F116" s="10" t="n">
         <v>-14.96917924120398</v>
       </c>
-      <c r="F116" s="8" t="inlineStr">
+      <c r="H116" s="8" t="inlineStr">
         <is>
           <t>Small intestine contents, centre~500 um</t>
         </is>
       </c>
-      <c r="G116" s="9" t="n">
+      <c r="I116" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="J116" s="10" t="n">
         <v>234.7733080654419</v>
       </c>
-      <c r="H116" s="9" t="n">
+      <c r="K116" s="13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L116" s="10" t="n">
         <v>209.6470462143766</v>
       </c>
-      <c r="I116" s="9" t="n">
+      <c r="M116" s="10" t="n">
         <v>-10.70235030468687</v>
       </c>
     </row>
@@ -3883,27 +5215,39 @@
           <t>Ascending colon wall, 0~280 um</t>
         </is>
       </c>
-      <c r="B117" s="9" t="n">
+      <c r="B117" s="13" t="n">
+        <v>1.037</v>
+      </c>
+      <c r="C117" s="10" t="n">
         <v>3.071450221763886</v>
       </c>
-      <c r="C117" s="9" t="n">
+      <c r="D117" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E117" s="10" t="n">
         <v>2.644663890620651</v>
       </c>
-      <c r="D117" s="9" t="n">
+      <c r="F117" s="10" t="n">
         <v>-13.89527097392249</v>
       </c>
-      <c r="F117" s="8" t="inlineStr">
+      <c r="H117" s="8" t="inlineStr">
         <is>
           <t>Ascending colon wall, 0~280 um</t>
         </is>
       </c>
-      <c r="G117" s="9" t="n">
+      <c r="I117" s="13" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="J117" s="10" t="n">
         <v>4.450855099029285</v>
       </c>
-      <c r="H117" s="9" t="n">
+      <c r="K117" s="13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L117" s="10" t="n">
         <v>4.029366503417194</v>
       </c>
-      <c r="I117" s="9" t="n">
+      <c r="M117" s="10" t="n">
         <v>-9.469834138253937</v>
       </c>
     </row>
@@ -3913,27 +5257,39 @@
           <t>Ascending colon wall, 280~300 um</t>
         </is>
       </c>
-      <c r="B118" s="9" t="n">
+      <c r="B118" s="13" t="n">
+        <v>1.037</v>
+      </c>
+      <c r="C118" s="10" t="n">
         <v>0.2233495664101676</v>
       </c>
-      <c r="C118" s="9" t="n">
+      <c r="D118" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E118" s="10" t="n">
         <v>0.192309961385078</v>
       </c>
-      <c r="D118" s="9" t="n">
+      <c r="F118" s="10" t="n">
         <v>-13.89732047569204</v>
       </c>
-      <c r="F118" s="8" t="inlineStr">
+      <c r="H118" s="8" t="inlineStr">
         <is>
           <t>Ascending colon wall, 280~300 um</t>
         </is>
       </c>
-      <c r="G118" s="9" t="n">
+      <c r="I118" s="13" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="J118" s="10" t="n">
         <v>0.3218907157540255</v>
       </c>
-      <c r="H118" s="9" t="n">
+      <c r="K118" s="13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L118" s="10" t="n">
         <v>0.2914126495673789</v>
       </c>
-      <c r="I118" s="9" t="n">
+      <c r="M118" s="10" t="n">
         <v>-9.468451463488805</v>
       </c>
     </row>
@@ -3943,27 +5299,39 @@
           <t>Ascending colon wall, 300 um~surface</t>
         </is>
       </c>
-      <c r="B119" s="9" t="n">
+      <c r="B119" s="13" t="n">
+        <v>1.037</v>
+      </c>
+      <c r="C119" s="10" t="n">
         <v>116.6341777582763</v>
       </c>
-      <c r="C119" s="9" t="n">
+      <c r="D119" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E119" s="10" t="n">
         <v>100.427558010898</v>
       </c>
-      <c r="D119" s="9" t="n">
+      <c r="F119" s="10" t="n">
         <v>-13.89525785569173</v>
       </c>
-      <c r="F119" s="8" t="inlineStr">
+      <c r="H119" s="8" t="inlineStr">
         <is>
           <t>Ascending colon wall, 300 um~surface</t>
         </is>
       </c>
-      <c r="G119" s="9" t="n">
+      <c r="I119" s="13" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="J119" s="10" t="n">
         <v>107.783989591372</v>
       </c>
-      <c r="H119" s="9" t="n">
+      <c r="K119" s="13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L119" s="10" t="n">
         <v>97.57681897711154</v>
       </c>
-      <c r="I119" s="9" t="n">
+      <c r="M119" s="10" t="n">
         <v>-9.470024864506927</v>
       </c>
     </row>
@@ -3973,27 +5341,39 @@
           <t>Ascending colon contents</t>
         </is>
       </c>
-      <c r="B120" s="9" t="n">
+      <c r="B120" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="C120" s="10" t="n">
         <v>55.00000063712194</v>
       </c>
-      <c r="C120" s="9" t="n">
+      <c r="D120" s="13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E120" s="10" t="n">
         <v>46.76695150012793</v>
       </c>
-      <c r="D120" s="9" t="n">
+      <c r="F120" s="10" t="n">
         <v>-14.9691800756765</v>
       </c>
-      <c r="F120" s="8" t="inlineStr">
+      <c r="H120" s="8" t="inlineStr">
         <is>
           <t>Ascending colon contents</t>
         </is>
       </c>
-      <c r="G120" s="9" t="n">
+      <c r="I120" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="J120" s="10" t="n">
         <v>100.007003512098</v>
       </c>
-      <c r="H120" s="9" t="n">
+      <c r="K120" s="13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L120" s="10" t="n">
         <v>89.30389593898633</v>
       </c>
-      <c r="I120" s="9" t="n">
+      <c r="M120" s="10" t="n">
         <v>-10.70235803217211</v>
       </c>
     </row>
@@ -4003,27 +5383,39 @@
           <t>Transverse colon wall, right, 0~280 um</t>
         </is>
       </c>
-      <c r="B121" s="9" t="n">
+      <c r="B121" s="13" t="n">
+        <v>1.037</v>
+      </c>
+      <c r="C121" s="10" t="n">
         <v>3.992697540998566</v>
       </c>
-      <c r="C121" s="9" t="n">
+      <c r="D121" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E121" s="10" t="n">
         <v>3.437901770630257</v>
       </c>
-      <c r="D121" s="9" t="n">
+      <c r="F121" s="10" t="n">
         <v>-13.89526165384308</v>
       </c>
-      <c r="F121" s="8" t="inlineStr">
+      <c r="H121" s="8" t="inlineStr">
         <is>
           <t>Transverse colon wall, right, 0~280 um</t>
         </is>
       </c>
-      <c r="G121" s="9" t="n">
+      <c r="I121" s="13" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="J121" s="10" t="n">
         <v>3.680164607595078</v>
       </c>
-      <c r="H121" s="9" t="n">
+      <c r="K121" s="13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L121" s="10" t="n">
         <v>3.331653627655341</v>
       </c>
-      <c r="I121" s="9" t="n">
+      <c r="M121" s="10" t="n">
         <v>-9.469983468143909</v>
       </c>
     </row>
@@ -4033,27 +5425,39 @@
           <t>Transverse colon wall, right, 280~300 um</t>
         </is>
       </c>
-      <c r="B122" s="9" t="n">
+      <c r="B122" s="13" t="n">
+        <v>1.037</v>
+      </c>
+      <c r="C122" s="10" t="n">
         <v>0.2886113450628562</v>
       </c>
-      <c r="C122" s="9" t="n">
+      <c r="D122" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E122" s="10" t="n">
         <v>0.2485144638293034</v>
       </c>
-      <c r="D122" s="9" t="n">
+      <c r="F122" s="10" t="n">
         <v>-13.89303709624449</v>
       </c>
-      <c r="F122" s="8" t="inlineStr">
+      <c r="H122" s="8" t="inlineStr">
         <is>
           <t>Transverse colon wall, right, 280~300 um</t>
         </is>
       </c>
-      <c r="G122" s="9" t="n">
+      <c r="I122" s="13" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="J122" s="10" t="n">
         <v>0.2663179478089344</v>
       </c>
-      <c r="H122" s="9" t="n">
+      <c r="K122" s="13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L122" s="10" t="n">
         <v>0.2410900248491814</v>
       </c>
-      <c r="I122" s="9" t="n">
+      <c r="M122" s="10" t="n">
         <v>-9.47285872668726</v>
       </c>
     </row>
@@ -4063,27 +5467,39 @@
           <t>Transverse colon wall, right, 300 um~surface</t>
         </is>
       </c>
-      <c r="B123" s="9" t="n">
+      <c r="B123" s="13" t="n">
+        <v>1.037</v>
+      </c>
+      <c r="C123" s="10" t="n">
         <v>75.67134897069351</v>
       </c>
-      <c r="C123" s="9" t="n">
+      <c r="D123" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E123" s="10" t="n">
         <v>65.1566038996156</v>
       </c>
-      <c r="D123" s="9" t="n">
+      <c r="F123" s="10" t="n">
         <v>-13.89527901128091</v>
       </c>
-      <c r="F123" s="8" t="inlineStr">
+      <c r="H123" s="8" t="inlineStr">
         <is>
           <t>Transverse colon wall, right, 300 um~surface</t>
         </is>
       </c>
-      <c r="G123" s="9" t="n">
+      <c r="I123" s="13" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="J123" s="10" t="n">
         <v>64.84744016411602</v>
       </c>
-      <c r="H123" s="9" t="n">
+      <c r="K123" s="13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L123" s="10" t="n">
         <v>58.70637168646003</v>
       </c>
-      <c r="I123" s="9" t="n">
+      <c r="M123" s="10" t="n">
         <v>-9.470024510010209</v>
       </c>
     </row>
@@ -4093,27 +5509,39 @@
           <t>Transverse colon contents, right</t>
         </is>
       </c>
-      <c r="B124" s="9" t="n">
+      <c r="B124" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="C124" s="10" t="n">
         <v>95.00000216962</v>
       </c>
-      <c r="C124" s="9" t="n">
+      <c r="D124" s="13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E124" s="10" t="n">
         <v>80.77928619475142</v>
       </c>
-      <c r="D124" s="9" t="n">
+      <c r="F124" s="10" t="n">
         <v>-14.9691743685204</v>
       </c>
-      <c r="F124" s="8" t="inlineStr">
+      <c r="H124" s="8" t="inlineStr">
         <is>
           <t>Transverse colon contents, right</t>
         </is>
       </c>
-      <c r="G124" s="9" t="n">
+      <c r="I124" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="J124" s="10" t="n">
         <v>59.99499313122701</v>
       </c>
-      <c r="H124" s="9" t="n">
+      <c r="K124" s="13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L124" s="10" t="n">
         <v>53.57411253457364</v>
       </c>
-      <c r="I124" s="9" t="n">
+      <c r="M124" s="10" t="n">
         <v>-10.70236074968621</v>
       </c>
     </row>
@@ -4123,27 +5551,39 @@
           <t>Transverse colon wall, left, 0~280 um</t>
         </is>
       </c>
-      <c r="B125" s="9" t="n">
+      <c r="B125" s="13" t="n">
+        <v>1.037</v>
+      </c>
+      <c r="C125" s="10" t="n">
         <v>2.823670214186225</v>
       </c>
-      <c r="C125" s="9" t="n">
+      <c r="D125" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E125" s="10" t="n">
         <v>2.431322366162526</v>
       </c>
-      <c r="D125" s="9" t="n">
+      <c r="F125" s="10" t="n">
         <v>-13.89496004358188</v>
       </c>
-      <c r="F125" s="8" t="inlineStr">
+      <c r="H125" s="8" t="inlineStr">
         <is>
           <t>Transverse colon wall, left, 0~280 um</t>
         </is>
       </c>
-      <c r="G125" s="9" t="n">
+      <c r="I125" s="13" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="J125" s="10" t="n">
         <v>2.19596582237084</v>
       </c>
-      <c r="H125" s="9" t="n">
+      <c r="K125" s="13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L125" s="10" t="n">
         <v>1.988005221670466</v>
       </c>
-      <c r="I125" s="9" t="n">
+      <c r="M125" s="10" t="n">
         <v>-9.470120098492799</v>
       </c>
     </row>
@@ -4153,27 +5593,39 @@
           <t>Transverse colon wall, left, 280~300 um</t>
         </is>
       </c>
-      <c r="B126" s="9" t="n">
+      <c r="B126" s="13" t="n">
+        <v>1.037</v>
+      </c>
+      <c r="C126" s="10" t="n">
         <v>0.2049723189797323</v>
       </c>
-      <c r="C126" s="9" t="n">
+      <c r="D126" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E126" s="10" t="n">
         <v>0.1764886914200704</v>
       </c>
-      <c r="D126" s="9" t="n">
+      <c r="F126" s="10" t="n">
         <v>-13.89632888062234</v>
       </c>
-      <c r="F126" s="8" t="inlineStr">
+      <c r="H126" s="8" t="inlineStr">
         <is>
           <t>Transverse colon wall, left, 280~300 um</t>
         </is>
       </c>
-      <c r="G126" s="9" t="n">
+      <c r="I126" s="13" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="J126" s="10" t="n">
         <v>0.1599963310129347</v>
       </c>
-      <c r="H126" s="9" t="n">
+      <c r="K126" s="13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L126" s="10" t="n">
         <v>0.1448513236027116</v>
       </c>
-      <c r="I126" s="9" t="n">
+      <c r="M126" s="10" t="n">
         <v>-9.465846694321225</v>
       </c>
     </row>
@@ -4183,27 +5635,39 @@
           <t>Transverse colon wall, left, 300 um~surface</t>
         </is>
       </c>
-      <c r="B127" s="9" t="n">
+      <c r="B127" s="13" t="n">
+        <v>1.037</v>
+      </c>
+      <c r="C127" s="10" t="n">
         <v>76.92402449697593</v>
       </c>
-      <c r="C127" s="9" t="n">
+      <c r="D127" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E127" s="10" t="n">
         <v>66.23523395006646</v>
       </c>
-      <c r="D127" s="9" t="n">
+      <c r="F127" s="10" t="n">
         <v>-13.89525654281086</v>
       </c>
-      <c r="F127" s="8" t="inlineStr">
+      <c r="H127" s="8" t="inlineStr">
         <is>
           <t>Transverse colon wall, left, 300 um~surface</t>
         </is>
       </c>
-      <c r="G127" s="9" t="n">
+      <c r="I127" s="13" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="J127" s="10" t="n">
         <v>66.42798484035693</v>
       </c>
-      <c r="H127" s="9" t="n">
+      <c r="K127" s="13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L127" s="10" t="n">
         <v>60.13723164833448</v>
       </c>
-      <c r="I127" s="9" t="n">
+      <c r="M127" s="10" t="n">
         <v>-9.470034665571603</v>
       </c>
     </row>
@@ -4213,27 +5677,39 @@
           <t>Transverse colon contents, left</t>
         </is>
       </c>
-      <c r="B128" s="9" t="n">
+      <c r="B128" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="C128" s="10" t="n">
         <v>39.99999290714094</v>
       </c>
-      <c r="C128" s="9" t="n">
+      <c r="D128" s="13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E128" s="10" t="n">
         <v>34.01231969532169</v>
       </c>
-      <c r="D128" s="9" t="n">
+      <c r="F128" s="10" t="n">
         <v>-14.96918568390623</v>
       </c>
-      <c r="F128" s="8" t="inlineStr">
+      <c r="H128" s="8" t="inlineStr">
         <is>
           <t>Transverse colon contents, left</t>
         </is>
       </c>
-      <c r="G128" s="9" t="n">
+      <c r="I128" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="J128" s="10" t="n">
         <v>30.00500129569646</v>
       </c>
-      <c r="H128" s="9" t="n">
+      <c r="K128" s="13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L128" s="10" t="n">
         <v>26.79375757139355</v>
       </c>
-      <c r="I128" s="9" t="n">
+      <c r="M128" s="10" t="n">
         <v>-10.70236155851619</v>
       </c>
     </row>
@@ -4243,27 +5719,39 @@
           <t>Descending colon wall, 0~280 um</t>
         </is>
       </c>
-      <c r="B129" s="9" t="n">
+      <c r="B129" s="13" t="n">
+        <v>1.037</v>
+      </c>
+      <c r="C129" s="10" t="n">
         <v>2.779434389899778</v>
       </c>
-      <c r="C129" s="9" t="n">
+      <c r="D129" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E129" s="10" t="n">
         <v>2.393223759790308</v>
       </c>
-      <c r="D129" s="9" t="n">
+      <c r="F129" s="10" t="n">
         <v>-13.89529580237351</v>
       </c>
-      <c r="F129" s="8" t="inlineStr">
+      <c r="H129" s="8" t="inlineStr">
         <is>
           <t>Descending colon wall, 0~280 um</t>
         </is>
       </c>
-      <c r="G129" s="9" t="n">
+      <c r="I129" s="13" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="J129" s="10" t="n">
         <v>3.020775327063151</v>
       </c>
-      <c r="H129" s="9" t="n">
+      <c r="K129" s="13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L129" s="10" t="n">
         <v>2.734705498820158</v>
       </c>
-      <c r="I129" s="9" t="n">
+      <c r="M129" s="10" t="n">
         <v>-9.470079607711678</v>
       </c>
     </row>
@@ -4273,27 +5761,39 @@
           <t>Descending colon wall, 280~300 um</t>
         </is>
       </c>
-      <c r="B130" s="9" t="n">
+      <c r="B130" s="13" t="n">
+        <v>1.037</v>
+      </c>
+      <c r="C130" s="10" t="n">
         <v>0.2033227535922421</v>
       </c>
-      <c r="C130" s="9" t="n">
+      <c r="D130" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E130" s="10" t="n">
         <v>0.1750698457632869</v>
       </c>
-      <c r="D130" s="9" t="n">
+      <c r="F130" s="10" t="n">
         <v>-13.89559571164158</v>
       </c>
-      <c r="F130" s="8" t="inlineStr">
+      <c r="H130" s="8" t="inlineStr">
         <is>
           <t>Descending colon wall, 280~300 um</t>
         </is>
       </c>
-      <c r="G130" s="9" t="n">
+      <c r="I130" s="13" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="J130" s="10" t="n">
         <v>0.2195368712725592</v>
       </c>
-      <c r="H130" s="9" t="n">
+      <c r="K130" s="13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L130" s="10" t="n">
         <v>0.1987531340979502</v>
       </c>
-      <c r="I130" s="9" t="n">
+      <c r="M130" s="10" t="n">
         <v>-9.467082706487883</v>
       </c>
     </row>
@@ -4303,27 +5803,39 @@
           <t>Descending colon wall, 300 um~surface</t>
         </is>
       </c>
-      <c r="B131" s="9" t="n">
+      <c r="B131" s="13" t="n">
+        <v>1.037</v>
+      </c>
+      <c r="C131" s="10" t="n">
         <v>116.9462205088255</v>
       </c>
-      <c r="C131" s="9" t="n">
+      <c r="D131" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E131" s="10" t="n">
         <v>100.6962453937203</v>
       </c>
-      <c r="D131" s="9" t="n">
+      <c r="F131" s="10" t="n">
         <v>-13.89525462593202</v>
       </c>
-      <c r="F131" s="8" t="inlineStr">
+      <c r="H131" s="8" t="inlineStr">
         <is>
           <t>Descending colon wall, 300 um~surface</t>
         </is>
       </c>
-      <c r="G131" s="9" t="n">
+      <c r="I131" s="13" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="J131" s="10" t="n">
         <v>109.320411376071</v>
       </c>
-      <c r="H131" s="9" t="n">
+      <c r="K131" s="13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L131" s="10" t="n">
         <v>98.9677265604314</v>
       </c>
-      <c r="I131" s="9" t="n">
+      <c r="M131" s="10" t="n">
         <v>-9.470038289579371</v>
       </c>
     </row>
@@ -4333,27 +5845,39 @@
           <t>Descending colon contents</t>
         </is>
       </c>
-      <c r="B132" s="9" t="n">
+      <c r="B132" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="C132" s="10" t="n">
         <v>35.00000917722327</v>
       </c>
-      <c r="C132" s="9" t="n">
+      <c r="D132" s="13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E132" s="10" t="n">
         <v>29.76079618756767</v>
       </c>
-      <c r="D132" s="9" t="n">
+      <c r="F132" s="10" t="n">
         <v>-14.96917604543113</v>
       </c>
-      <c r="F132" s="8" t="inlineStr">
+      <c r="H132" s="8" t="inlineStr">
         <is>
           <t>Descending colon contents</t>
         </is>
       </c>
-      <c r="G132" s="9" t="n">
+      <c r="I132" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="J132" s="10" t="n">
         <v>50.00299462946273</v>
       </c>
-      <c r="H132" s="9" t="n">
+      <c r="K132" s="13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L132" s="10" t="n">
         <v>44.6515009555737</v>
       </c>
-      <c r="I132" s="9" t="n">
+      <c r="M132" s="10" t="n">
         <v>-10.70234635654366</v>
       </c>
     </row>
@@ -4363,27 +5887,39 @@
           <t>Sigmoid colon wall, 0~280 um</t>
         </is>
       </c>
-      <c r="B133" s="9" t="n">
+      <c r="B133" s="13" t="n">
+        <v>1.037</v>
+      </c>
+      <c r="C133" s="10" t="n">
         <v>4.450942356500349</v>
       </c>
-      <c r="C133" s="9" t="n">
+      <c r="D133" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E133" s="10" t="n">
         <v>3.83246771152122</v>
       </c>
-      <c r="D133" s="9" t="n">
+      <c r="F133" s="10" t="n">
         <v>-13.89536406994535</v>
       </c>
-      <c r="F133" s="8" t="inlineStr">
+      <c r="H133" s="8" t="inlineStr">
         <is>
           <t>Sigmoid colon wall, 0~280 um</t>
         </is>
       </c>
-      <c r="G133" s="9" t="n">
+      <c r="I133" s="13" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="J133" s="10" t="n">
         <v>4.222046558248752</v>
       </c>
-      <c r="H133" s="9" t="n">
+      <c r="K133" s="13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L133" s="10" t="n">
         <v>3.822221617719863</v>
       </c>
-      <c r="I133" s="9" t="n">
+      <c r="M133" s="10" t="n">
         <v>-9.469932058132745</v>
       </c>
     </row>
@@ -4393,27 +5929,39 @@
           <t>Sigmoid colon wall, 280~300 um</t>
         </is>
       </c>
-      <c r="B134" s="9" t="n">
+      <c r="B134" s="13" t="n">
+        <v>1.037</v>
+      </c>
+      <c r="C134" s="10" t="n">
         <v>0.3235627550951706</v>
       </c>
-      <c r="C134" s="9" t="n">
+      <c r="D134" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E134" s="10" t="n">
         <v>0.2785956991817028</v>
       </c>
-      <c r="D134" s="9" t="n">
+      <c r="F134" s="10" t="n">
         <v>-13.89747590084697</v>
       </c>
-      <c r="F134" s="8" t="inlineStr">
+      <c r="H134" s="8" t="inlineStr">
         <is>
           <t>Sigmoid colon wall, 280~300 um</t>
         </is>
       </c>
-      <c r="G134" s="9" t="n">
+      <c r="I134" s="13" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="J134" s="10" t="n">
         <v>0.3059269267303278</v>
       </c>
-      <c r="H134" s="9" t="n">
+      <c r="K134" s="13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L134" s="10" t="n">
         <v>0.2769519630810269</v>
       </c>
-      <c r="I134" s="9" t="n">
+      <c r="M134" s="10" t="n">
         <v>-9.471204107130514</v>
       </c>
     </row>
@@ -4423,27 +5971,39 @@
           <t>Sigmoid colon wall, 300 um~surface</t>
         </is>
       </c>
-      <c r="B135" s="9" t="n">
+      <c r="B135" s="13" t="n">
+        <v>1.037</v>
+      </c>
+      <c r="C135" s="10" t="n">
         <v>48.52422396478801</v>
       </c>
-      <c r="C135" s="9" t="n">
+      <c r="D135" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E135" s="10" t="n">
         <v>41.78431515614489</v>
       </c>
-      <c r="D135" s="9" t="n">
+      <c r="F135" s="10" t="n">
         <v>-13.88978175835225</v>
       </c>
-      <c r="F135" s="8" t="inlineStr">
+      <c r="H135" s="8" t="inlineStr">
         <is>
           <t>Sigmoid colon wall, 300 um~surface</t>
         </is>
       </c>
-      <c r="G135" s="9" t="n">
+      <c r="I135" s="13" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="J135" s="10" t="n">
         <v>51.76085912945222</v>
       </c>
-      <c r="H135" s="9" t="n">
+      <c r="K135" s="13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L135" s="10" t="n">
         <v>46.84205754457982</v>
       </c>
-      <c r="I135" s="9" t="n">
+      <c r="M135" s="10" t="n">
         <v>-9.502936519215499</v>
       </c>
     </row>
@@ -4453,27 +6013,39 @@
           <t>Sigmoid colon contents</t>
         </is>
       </c>
-      <c r="B136" s="9" t="n">
+      <c r="B136" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="C136" s="10" t="n">
         <v>74.99999544936816</v>
       </c>
-      <c r="C136" s="9" t="n">
+      <c r="D136" s="13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E136" s="10" t="n">
         <v>63.77311416139975</v>
       </c>
-      <c r="D136" s="9" t="n">
+      <c r="F136" s="10" t="n">
         <v>-14.96917595888067</v>
       </c>
-      <c r="F136" s="8" t="inlineStr">
+      <c r="H136" s="8" t="inlineStr">
         <is>
           <t>Sigmoid colon contents</t>
         </is>
       </c>
-      <c r="G136" s="9" t="n">
+      <c r="I136" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="J136" s="10" t="n">
         <v>79.99299660652235</v>
       </c>
-      <c r="H136" s="9" t="n">
+      <c r="K136" s="13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L136" s="10" t="n">
         <v>71.43186308353971</v>
       </c>
-      <c r="I136" s="9" t="n">
+      <c r="M136" s="10" t="n">
         <v>-10.70235381366448</v>
       </c>
     </row>
@@ -4483,27 +6055,39 @@
           <t>Rectum wall</t>
         </is>
       </c>
-      <c r="B137" s="9" t="n">
+      <c r="B137" s="13" t="n">
+        <v>1.037</v>
+      </c>
+      <c r="C137" s="10" t="n">
         <v>39.97632661810045</v>
       </c>
-      <c r="C137" s="9" t="n">
+      <c r="D137" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E137" s="10" t="n">
         <v>34.27792809294245</v>
       </c>
-      <c r="D137" s="9" t="n">
+      <c r="F137" s="10" t="n">
         <v>-14.25443257854985</v>
       </c>
-      <c r="F137" s="8" t="inlineStr">
+      <c r="H137" s="8" t="inlineStr">
         <is>
           <t>Rectum wall</t>
         </is>
       </c>
-      <c r="G137" s="9" t="n">
+      <c r="I137" s="13" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="J137" s="10" t="n">
         <v>31.26769463334453</v>
       </c>
-      <c r="H137" s="9" t="n">
+      <c r="K137" s="13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L137" s="10" t="n">
         <v>28.24700398757959</v>
       </c>
-      <c r="I137" s="9" t="n">
+      <c r="M137" s="10" t="n">
         <v>-9.66073988244597</v>
       </c>
     </row>
@@ -4513,27 +6097,39 @@
           <t>Heart wall</t>
         </is>
       </c>
-      <c r="B138" s="9" t="n">
+      <c r="B138" s="13" t="n">
+        <v>1.051</v>
+      </c>
+      <c r="C138" s="10" t="n">
         <v>385.8388144993086</v>
       </c>
-      <c r="C138" s="9" t="n">
+      <c r="D138" s="13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E138" s="10" t="n">
         <v>274.1383372128245</v>
       </c>
-      <c r="D138" s="9" t="n">
+      <c r="F138" s="10" t="n">
         <v>-28.95003641130157</v>
       </c>
-      <c r="F138" s="8" t="inlineStr">
+      <c r="H138" s="8" t="inlineStr">
         <is>
           <t>Heart wall</t>
         </is>
       </c>
-      <c r="G138" s="9" t="n">
+      <c r="I138" s="13" t="n">
+        <v>1.051</v>
+      </c>
+      <c r="J138" s="10" t="n">
         <v>290.8899694672094</v>
       </c>
-      <c r="H138" s="9" t="n">
+      <c r="K138" s="13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L138" s="10" t="n">
         <v>218.3610186555152</v>
       </c>
-      <c r="I138" s="9" t="n">
+      <c r="M138" s="10" t="n">
         <v>-24.93346571713607</v>
       </c>
     </row>
@@ -4543,27 +6139,39 @@
           <t>Blood in heart chamber</t>
         </is>
       </c>
-      <c r="B139" s="9" t="n">
+      <c r="B139" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="C139" s="10" t="n">
         <v>510.0000095221753</v>
       </c>
-      <c r="C139" s="9" t="n">
+      <c r="D139" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E139" s="10" t="n">
         <v>369.8351520562338</v>
       </c>
-      <c r="D139" s="9" t="n">
+      <c r="F139" s="10" t="n">
         <v>-27.4833048723398</v>
       </c>
-      <c r="F139" s="8" t="inlineStr">
+      <c r="H139" s="8" t="inlineStr">
         <is>
           <t>Blood in heart chamber</t>
         </is>
       </c>
-      <c r="G139" s="9" t="n">
+      <c r="I139" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="J139" s="10" t="n">
         <v>370.0000059674408</v>
       </c>
-      <c r="H139" s="9" t="n">
+      <c r="K139" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="L139" s="10" t="n">
         <v>283.7235402157789</v>
       </c>
-      <c r="I139" s="9" t="n">
+      <c r="M139" s="10" t="n">
         <v>-23.31796334058817</v>
       </c>
     </row>
@@ -4573,27 +6181,39 @@
           <t>Kidney, left, cortex</t>
         </is>
       </c>
-      <c r="B140" s="9" t="n">
+      <c r="B140" s="13" t="n">
+        <v>1.053</v>
+      </c>
+      <c r="C140" s="10" t="n">
         <v>162.3384466140467</v>
       </c>
-      <c r="C140" s="9" t="n">
+      <c r="D140" s="13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E140" s="10" t="n">
         <v>140.4796945757485</v>
       </c>
-      <c r="D140" s="9" t="n">
+      <c r="F140" s="10" t="n">
         <v>-13.46492620461406</v>
       </c>
-      <c r="F140" s="8" t="inlineStr">
+      <c r="H140" s="8" t="inlineStr">
         <is>
           <t>Kidney, left, cortex</t>
         </is>
       </c>
-      <c r="G140" s="9" t="n">
+      <c r="I140" s="13" t="n">
+        <v>1.052</v>
+      </c>
+      <c r="J140" s="10" t="n">
         <v>149.0910820068956</v>
       </c>
-      <c r="H140" s="9" t="n">
+      <c r="K140" s="13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L140" s="10" t="n">
         <v>125.6431353979674</v>
       </c>
-      <c r="I140" s="9" t="n">
+      <c r="M140" s="10" t="n">
         <v>-15.72726302156939</v>
       </c>
     </row>
@@ -4603,27 +6223,39 @@
           <t>Kidney, left, medulla</t>
         </is>
       </c>
-      <c r="B141" s="9" t="n">
+      <c r="B141" s="13" t="n">
+        <v>1.053</v>
+      </c>
+      <c r="C141" s="10" t="n">
         <v>38.35928191888284</v>
       </c>
-      <c r="C141" s="9" t="n">
+      <c r="D141" s="13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E141" s="10" t="n">
         <v>33.19423558226249</v>
       </c>
-      <c r="D141" s="9" t="n">
+      <c r="F141" s="10" t="n">
         <v>-13.46491925355305</v>
       </c>
-      <c r="F141" s="8" t="inlineStr">
+      <c r="H141" s="8" t="inlineStr">
         <is>
           <t>Kidney, left, medulla</t>
         </is>
       </c>
-      <c r="G141" s="9" t="n">
+      <c r="I141" s="13" t="n">
+        <v>1.052</v>
+      </c>
+      <c r="J141" s="10" t="n">
         <v>37.44117632849867</v>
       </c>
-      <c r="H141" s="9" t="n">
+      <c r="K141" s="13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L141" s="10" t="n">
         <v>23.34362812513591</v>
       </c>
-      <c r="I141" s="9" t="n">
+      <c r="M141" s="10" t="n">
         <v>-37.65252480230513</v>
       </c>
     </row>
@@ -4633,27 +6265,39 @@
           <t>Kidney, left, pelvis</t>
         </is>
       </c>
-      <c r="B142" s="9" t="n">
+      <c r="B142" s="13" t="n">
+        <v>1.053</v>
+      </c>
+      <c r="C142" s="10" t="n">
         <v>7.651796291936333</v>
       </c>
-      <c r="C142" s="9" t="n">
+      <c r="D142" s="13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E142" s="10" t="n">
         <v>6.621484866096854</v>
       </c>
-      <c r="D142" s="9" t="n">
+      <c r="F142" s="10" t="n">
         <v>-13.46496151400748</v>
       </c>
-      <c r="F142" s="8" t="inlineStr">
+      <c r="H142" s="8" t="inlineStr">
         <is>
           <t>Kidney, left, pelvis</t>
         </is>
       </c>
-      <c r="G142" s="9" t="n">
+      <c r="I142" s="13" t="n">
+        <v>1.052</v>
+      </c>
+      <c r="J142" s="10" t="n">
         <v>7.494248015918648</v>
       </c>
-      <c r="H142" s="9" t="n">
+      <c r="K142" s="13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L142" s="10" t="n">
         <v>4.672474292028006</v>
       </c>
-      <c r="I142" s="9" t="n">
+      <c r="M142" s="10" t="n">
         <v>-37.65252654965339</v>
       </c>
     </row>
@@ -4663,27 +6307,39 @@
           <t>Kidney, right, cortex</t>
         </is>
       </c>
-      <c r="B143" s="9" t="n">
+      <c r="B143" s="13" t="n">
+        <v>1.053</v>
+      </c>
+      <c r="C143" s="10" t="n">
         <v>166.5419456531224</v>
       </c>
-      <c r="C143" s="9" t="n">
+      <c r="D143" s="13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E143" s="10" t="n">
         <v>132.584264910342</v>
       </c>
-      <c r="D143" s="9" t="n">
+      <c r="F143" s="10" t="n">
         <v>-20.38986671472439</v>
       </c>
-      <c r="F143" s="8" t="inlineStr">
+      <c r="H143" s="8" t="inlineStr">
         <is>
           <t>Kidney, right, cortex</t>
         </is>
       </c>
-      <c r="G143" s="9" t="n">
+      <c r="I143" s="13" t="n">
+        <v>1.052</v>
+      </c>
+      <c r="J143" s="10" t="n">
         <v>125.1467025281104</v>
       </c>
-      <c r="H143" s="9" t="n">
+      <c r="K143" s="13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L143" s="10" t="n">
         <v>111.8295619729389</v>
       </c>
-      <c r="I143" s="9" t="n">
+      <c r="M143" s="10" t="n">
         <v>-10.64122368879853</v>
       </c>
     </row>
@@ -4693,27 +6349,39 @@
           <t>Kidney, right, medulla</t>
         </is>
       </c>
-      <c r="B144" s="9" t="n">
+      <c r="B144" s="13" t="n">
+        <v>1.053</v>
+      </c>
+      <c r="C144" s="10" t="n">
         <v>39.36213815846305</v>
       </c>
-      <c r="C144" s="9" t="n">
+      <c r="D144" s="13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E144" s="10" t="n">
         <v>31.33625688361445</v>
       </c>
-      <c r="D144" s="9" t="n">
+      <c r="F144" s="10" t="n">
         <v>-20.38985088294294</v>
       </c>
-      <c r="F144" s="8" t="inlineStr">
+      <c r="H144" s="8" t="inlineStr">
         <is>
           <t>Kidney, right, medulla</t>
         </is>
       </c>
-      <c r="G144" s="9" t="n">
+      <c r="I144" s="13" t="n">
+        <v>1.052</v>
+      </c>
+      <c r="J144" s="10" t="n">
         <v>31.43977765770199</v>
       </c>
-      <c r="H144" s="9" t="n">
+      <c r="K144" s="13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L144" s="10" t="n">
         <v>21.71430839640914</v>
       </c>
-      <c r="I144" s="9" t="n">
+      <c r="M144" s="10" t="n">
         <v>-30.93364516498207</v>
       </c>
     </row>
@@ -4723,27 +6391,39 @@
           <t>Kidney, right, pelvis</t>
         </is>
       </c>
-      <c r="B145" s="9" t="n">
+      <c r="B145" s="13" t="n">
+        <v>1.053</v>
+      </c>
+      <c r="C145" s="10" t="n">
         <v>7.89248678926693</v>
       </c>
-      <c r="C145" s="9" t="n">
+      <c r="D145" s="13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E145" s="10" t="n">
         <v>6.283219472932138</v>
       </c>
-      <c r="D145" s="9" t="n">
+      <c r="F145" s="10" t="n">
         <v>-20.38986392125801</v>
       </c>
-      <c r="F145" s="8" t="inlineStr">
+      <c r="H145" s="8" t="inlineStr">
         <is>
           <t>Kidney, right, pelvis</t>
         </is>
       </c>
-      <c r="G145" s="9" t="n">
+      <c r="I145" s="13" t="n">
+        <v>1.052</v>
+      </c>
+      <c r="J145" s="10" t="n">
         <v>6.291959956334409</v>
       </c>
-      <c r="H145" s="9" t="n">
+      <c r="K145" s="13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L145" s="10" t="n">
         <v>4.345626974674415</v>
       </c>
-      <c r="I145" s="9" t="n">
+      <c r="M145" s="10" t="n">
         <v>-30.93365175823362</v>
       </c>
     </row>
@@ -4753,27 +6433,39 @@
           <t>Liver</t>
         </is>
       </c>
-      <c r="B146" s="9" t="n">
+      <c r="B146" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="C146" s="10" t="n">
         <v>2360.00000489757</v>
       </c>
-      <c r="C146" s="9" t="n">
+      <c r="D146" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E146" s="10" t="n">
         <v>1714.804464737489</v>
       </c>
-      <c r="D146" s="9" t="n">
+      <c r="F146" s="10" t="n">
         <v>-27.33879401784509</v>
       </c>
-      <c r="F146" s="8" t="inlineStr">
+      <c r="H146" s="8" t="inlineStr">
         <is>
           <t>Liver</t>
         </is>
       </c>
-      <c r="G146" s="9" t="n">
+      <c r="I146" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="J146" s="10" t="n">
         <v>1810.000002004941</v>
       </c>
-      <c r="H146" s="9" t="n">
+      <c r="K146" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L146" s="10" t="n">
         <v>1520.675208207552</v>
       </c>
-      <c r="I146" s="9" t="n">
+      <c r="M146" s="10" t="n">
         <v>-15.98479521971839</v>
       </c>
     </row>
@@ -4783,27 +6475,39 @@
           <t>Lung (AI), left</t>
         </is>
       </c>
-      <c r="B147" s="9" t="n">
+      <c r="B147" s="13" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="C147" s="10" t="n">
         <v>545.8768933536599</v>
       </c>
-      <c r="C147" s="9" t="n">
+      <c r="D147" s="13" t="n">
+        <v>0.41454</v>
+      </c>
+      <c r="E147" s="10" t="n">
         <v>467.5254383226713</v>
       </c>
-      <c r="D147" s="9" t="n">
+      <c r="F147" s="10" t="n">
         <v>-14.35331958266763</v>
       </c>
-      <c r="F147" s="8" t="inlineStr">
+      <c r="H147" s="8" t="inlineStr">
         <is>
           <t>Lung (AI), left</t>
         </is>
       </c>
-      <c r="G147" s="9" t="n">
+      <c r="I147" s="13" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="J147" s="10" t="n">
         <v>427.2556349688277</v>
       </c>
-      <c r="H147" s="9" t="n">
+      <c r="K147" s="13" t="n">
+        <v>0.4001</v>
+      </c>
+      <c r="L147" s="10" t="n">
         <v>380.5881721474989</v>
       </c>
-      <c r="I147" s="9" t="n">
+      <c r="M147" s="10" t="n">
         <v>-10.92260908969256</v>
       </c>
     </row>
@@ -4813,27 +6517,39 @@
           <t>Lung (AI), right</t>
         </is>
       </c>
-      <c r="B148" s="9" t="n">
+      <c r="B148" s="13" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="C148" s="10" t="n">
         <v>652.8614495578809</v>
       </c>
-      <c r="C148" s="9" t="n">
+      <c r="D148" s="13" t="n">
+        <v>0.41454</v>
+      </c>
+      <c r="E148" s="10" t="n">
         <v>559.9017914195127</v>
       </c>
-      <c r="D148" s="9" t="n">
+      <c r="F148" s="10" t="n">
         <v>-14.23880337877518</v>
       </c>
-      <c r="F148" s="8" t="inlineStr">
+      <c r="H148" s="8" t="inlineStr">
         <is>
           <t>Lung (AI), right</t>
         </is>
       </c>
-      <c r="G148" s="9" t="n">
+      <c r="I148" s="13" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="J148" s="10" t="n">
         <v>522.517709631839</v>
       </c>
-      <c r="H148" s="9" t="n">
+      <c r="K148" s="13" t="n">
+        <v>0.4001</v>
+      </c>
+      <c r="L148" s="10" t="n">
         <v>452.9431712689654</v>
       </c>
-      <c r="I148" s="9" t="n">
+      <c r="M148" s="10" t="n">
         <v>-13.31524981457473</v>
       </c>
     </row>
@@ -4843,27 +6559,39 @@
           <t>Lymphatic nodes, ET</t>
         </is>
       </c>
-      <c r="B149" s="9" t="n">
+      <c r="B149" s="13" t="n">
+        <v>1.032</v>
+      </c>
+      <c r="C149" s="10" t="n">
         <v>15.94918599780411</v>
       </c>
-      <c r="C149" s="9" t="n">
+      <c r="D149" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="E149" s="10" t="n">
         <v>14.36201620811298</v>
       </c>
-      <c r="D149" s="9" t="n">
+      <c r="F149" s="10" t="n">
         <v>-9.951415639078123</v>
       </c>
-      <c r="F149" s="8" t="inlineStr">
+      <c r="H149" s="8" t="inlineStr">
         <is>
           <t>Lymphatic nodes, ET</t>
         </is>
       </c>
-      <c r="G149" s="9" t="n">
+      <c r="I149" s="13" t="n">
+        <v>1.032</v>
+      </c>
+      <c r="J149" s="10" t="n">
         <v>12.69547045447637</v>
       </c>
-      <c r="H149" s="9" t="n">
+      <c r="K149" s="13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L149" s="10" t="n">
         <v>12.0859460439824</v>
       </c>
-      <c r="I149" s="9" t="n">
+      <c r="M149" s="10" t="n">
         <v>-4.801117159695716</v>
       </c>
     </row>
@@ -4873,27 +6601,39 @@
           <t>Lymphatic nodes, thoracic</t>
         </is>
       </c>
-      <c r="B150" s="9" t="n">
+      <c r="B150" s="13" t="n">
+        <v>1.032</v>
+      </c>
+      <c r="C150" s="10" t="n">
         <v>15.94920544665688</v>
       </c>
-      <c r="C150" s="9" t="n">
+      <c r="D150" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="E150" s="10" t="n">
         <v>13.68013265635331</v>
       </c>
-      <c r="D150" s="9" t="n">
+      <c r="F150" s="10" t="n">
         <v>-14.22687040989362</v>
       </c>
-      <c r="F150" s="8" t="inlineStr">
+      <c r="H150" s="8" t="inlineStr">
         <is>
           <t>Lymphatic nodes, thoracic</t>
         </is>
       </c>
-      <c r="G150" s="9" t="n">
+      <c r="I150" s="13" t="n">
+        <v>1.032</v>
+      </c>
+      <c r="J150" s="10" t="n">
         <v>12.69544256657785</v>
       </c>
-      <c r="H150" s="9" t="n">
+      <c r="K150" s="13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L150" s="10" t="n">
         <v>11.65084661768113</v>
       </c>
-      <c r="I150" s="9" t="n">
+      <c r="M150" s="10" t="n">
         <v>-8.228117636849692</v>
       </c>
     </row>
@@ -4903,27 +6643,39 @@
           <t>Lymphatic nodes, head</t>
         </is>
       </c>
-      <c r="B151" s="9" t="n">
+      <c r="B151" s="13" t="n">
+        <v>1.032</v>
+      </c>
+      <c r="C151" s="10" t="n">
         <v>5.509725193861101</v>
       </c>
-      <c r="C151" s="9" t="n">
+      <c r="D151" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="E151" s="10" t="n">
         <v>4.80089504910269</v>
       </c>
-      <c r="D151" s="9" t="n">
+      <c r="F151" s="10" t="n">
         <v>-12.86507257291496</v>
       </c>
-      <c r="F151" s="8" t="inlineStr">
+      <c r="H151" s="8" t="inlineStr">
         <is>
           <t>Lymphatic nodes, head</t>
         </is>
       </c>
-      <c r="G151" s="9" t="n">
+      <c r="I151" s="13" t="n">
+        <v>1.032</v>
+      </c>
+      <c r="J151" s="10" t="n">
         <v>4.385693183837502</v>
       </c>
-      <c r="H151" s="9" t="n">
+      <c r="K151" s="13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L151" s="10" t="n">
         <v>4.099060863161109</v>
       </c>
-      <c r="I151" s="9" t="n">
+      <c r="M151" s="10" t="n">
         <v>-6.535621819891841</v>
       </c>
     </row>
@@ -4933,27 +6685,39 @@
           <t>Lymphatic nodes, trunk</t>
         </is>
       </c>
-      <c r="B152" s="9" t="n">
+      <c r="B152" s="13" t="n">
+        <v>1.032</v>
+      </c>
+      <c r="C152" s="10" t="n">
         <v>130.2035223827786</v>
       </c>
-      <c r="C152" s="9" t="n">
+      <c r="D152" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="E152" s="10" t="n">
         <v>111.4050276053723</v>
       </c>
-      <c r="D152" s="9" t="n">
+      <c r="F152" s="10" t="n">
         <v>-14.43777743749633</v>
       </c>
-      <c r="F152" s="8" t="inlineStr">
+      <c r="H152" s="8" t="inlineStr">
         <is>
           <t>Lymphatic nodes, trunk</t>
         </is>
       </c>
-      <c r="G152" s="9" t="n">
+      <c r="I152" s="13" t="n">
+        <v>1.032</v>
+      </c>
+      <c r="J152" s="10" t="n">
         <v>103.6409331666635</v>
       </c>
-      <c r="H152" s="9" t="n">
+      <c r="K152" s="13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L152" s="10" t="n">
         <v>94.85631631621112</v>
       </c>
-      <c r="I152" s="9" t="n">
+      <c r="M152" s="10" t="n">
         <v>-8.476010956333175</v>
       </c>
     </row>
@@ -4963,27 +6727,39 @@
           <t>Lymphatic nodes, arms</t>
         </is>
       </c>
-      <c r="B153" s="9" t="n">
+      <c r="B153" s="13" t="n">
+        <v>1.032</v>
+      </c>
+      <c r="C153" s="10" t="n">
         <v>11.0194524245648</v>
       </c>
-      <c r="C153" s="9" t="n">
+      <c r="D153" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="E153" s="10" t="n">
         <v>9.451600812590613</v>
       </c>
-      <c r="D153" s="9" t="n">
+      <c r="F153" s="10" t="n">
         <v>-14.22803558259481</v>
       </c>
-      <c r="F153" s="8" t="inlineStr">
+      <c r="H153" s="8" t="inlineStr">
         <is>
           <t>Lymphatic nodes, arms</t>
         </is>
       </c>
-      <c r="G153" s="9" t="n">
+      <c r="I153" s="13" t="n">
+        <v>1.032</v>
+      </c>
+      <c r="J153" s="10" t="n">
         <v>8.771456480243959</v>
       </c>
-      <c r="H153" s="9" t="n">
+      <c r="K153" s="13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L153" s="10" t="n">
         <v>8.049729481631553</v>
       </c>
-      <c r="I153" s="9" t="n">
+      <c r="M153" s="10" t="n">
         <v>-8.228131784475687</v>
       </c>
     </row>
@@ -4993,27 +6769,39 @@
           <t>Lymphatic nodes, legs</t>
         </is>
       </c>
-      <c r="B154" s="9" t="n">
+      <c r="B154" s="13" t="n">
+        <v>1.032</v>
+      </c>
+      <c r="C154" s="10" t="n">
         <v>11.01945354812791</v>
       </c>
-      <c r="C154" s="9" t="n">
+      <c r="D154" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="E154" s="10" t="n">
         <v>9.394483251042432</v>
       </c>
-      <c r="D154" s="9" t="n">
+      <c r="F154" s="10" t="n">
         <v>-14.74637821184465</v>
       </c>
-      <c r="F154" s="8" t="inlineStr">
+      <c r="H154" s="8" t="inlineStr">
         <is>
           <t>Lymphatic nodes, legs</t>
         </is>
       </c>
-      <c r="G154" s="9" t="n">
+      <c r="I154" s="13" t="n">
+        <v>1.032</v>
+      </c>
+      <c r="J154" s="10" t="n">
         <v>8.771395775782777</v>
       </c>
-      <c r="H154" s="9" t="n">
+      <c r="K154" s="13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L154" s="10" t="n">
         <v>7.890915303883055</v>
       </c>
-      <c r="I154" s="9" t="n">
+      <c r="M154" s="10" t="n">
         <v>-10.03808851415265</v>
       </c>
     </row>
@@ -5023,27 +6811,39 @@
           <t>Muscle, head</t>
         </is>
       </c>
-      <c r="B155" s="9" t="n">
+      <c r="B155" s="13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="C155" s="10" t="n">
         <v>1200.827798892491</v>
       </c>
-      <c r="C155" s="9" t="n">
+      <c r="D155" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E155" s="10" t="n">
         <v>25243.22967994168</v>
       </c>
-      <c r="D155" s="9" t="n">
+      <c r="F155" s="10" t="n">
         <v>2002.152340512369</v>
       </c>
-      <c r="F155" s="8" t="inlineStr">
+      <c r="H155" s="8" t="inlineStr">
         <is>
           <t>Muscle, head</t>
         </is>
       </c>
-      <c r="G155" s="9" t="n">
+      <c r="I155" s="13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="J155" s="10" t="n">
         <v>445.0216280506071</v>
       </c>
-      <c r="H155" s="9" t="n">
+      <c r="K155" s="13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L155" s="10" t="n">
         <v>15869.57530639098</v>
       </c>
-      <c r="I155" s="9" t="n">
+      <c r="M155" s="10" t="n">
         <v>3466.023380909999</v>
       </c>
     </row>
@@ -5053,27 +6853,39 @@
           <t>Muscle, trunk</t>
         </is>
       </c>
-      <c r="B156" s="9" t="n">
+      <c r="B156" s="13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="C156" s="10" t="n">
         <v>14844.72969345579</v>
       </c>
-      <c r="C156" s="9" t="n">
+      <c r="D156" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E156" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D156" s="9" t="n">
+      <c r="F156" s="10" t="n">
         <v>-100</v>
       </c>
-      <c r="F156" s="8" t="inlineStr">
+      <c r="H156" s="8" t="inlineStr">
         <is>
           <t>Muscle, trunk</t>
         </is>
       </c>
-      <c r="G156" s="9" t="n">
+      <c r="I156" s="13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="J156" s="10" t="n">
         <v>8324.972880760226</v>
       </c>
-      <c r="H156" s="9" t="n">
+      <c r="K156" s="13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L156" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="I156" s="9" t="n">
+      <c r="M156" s="10" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -5083,27 +6895,39 @@
           <t>Muscle, arms</t>
         </is>
       </c>
-      <c r="B157" s="9" t="n">
+      <c r="B157" s="13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="C157" s="10" t="n">
         <v>2843.506922075566</v>
       </c>
-      <c r="C157" s="9" t="n">
+      <c r="D157" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E157" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D157" s="9" t="n">
+      <c r="F157" s="10" t="n">
         <v>-100</v>
       </c>
-      <c r="F157" s="8" t="inlineStr">
+      <c r="H157" s="8" t="inlineStr">
         <is>
           <t>Muscle, arms</t>
         </is>
       </c>
-      <c r="G157" s="9" t="n">
+      <c r="I157" s="13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="J157" s="10" t="n">
         <v>1479.723864479042</v>
       </c>
-      <c r="H157" s="9" t="n">
+      <c r="K157" s="13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L157" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="I157" s="9" t="n">
+      <c r="M157" s="10" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -5113,27 +6937,39 @@
           <t>Muscle, legs</t>
         </is>
       </c>
-      <c r="B158" s="9" t="n">
+      <c r="B158" s="13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="C158" s="10" t="n">
         <v>10887.72912520177</v>
       </c>
-      <c r="C158" s="9" t="n">
+      <c r="D158" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E158" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D158" s="9" t="n">
+      <c r="F158" s="10" t="n">
         <v>-100</v>
       </c>
-      <c r="F158" s="8" t="inlineStr">
+      <c r="H158" s="8" t="inlineStr">
         <is>
           <t>Muscle, legs</t>
         </is>
       </c>
-      <c r="G158" s="9" t="n">
+      <c r="I158" s="13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="J158" s="10" t="n">
         <v>7676.719926990449</v>
       </c>
-      <c r="H158" s="9" t="n">
+      <c r="K158" s="13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L158" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="I158" s="9" t="n">
+      <c r="M158" s="10" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -5143,27 +6979,39 @@
           <t>Oesophagus wall, 0~190 um</t>
         </is>
       </c>
-      <c r="B159" s="9" t="n">
+      <c r="B159" s="13" t="n">
+        <v>1.037</v>
+      </c>
+      <c r="C159" s="10" t="n">
         <v>1.919393001278257</v>
       </c>
-      <c r="C159" s="9" t="n">
+      <c r="D159" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E159" s="10" t="n">
         <v>1.652793330161714</v>
       </c>
-      <c r="D159" s="9" t="n">
+      <c r="F159" s="10" t="n">
         <v>-13.88979072753707</v>
       </c>
-      <c r="F159" s="8" t="inlineStr">
+      <c r="H159" s="8" t="inlineStr">
         <is>
           <t>Oesophagus wall, 0~190 um</t>
         </is>
       </c>
-      <c r="G159" s="9" t="n">
+      <c r="I159" s="13" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="J159" s="10" t="n">
         <v>1.871018153166933</v>
       </c>
-      <c r="H159" s="9" t="n">
+      <c r="K159" s="13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L159" s="10" t="n">
         <v>1.695206892923135</v>
       </c>
-      <c r="I159" s="9" t="n">
+      <c r="M159" s="10" t="n">
         <v>-9.396555556995263</v>
       </c>
     </row>
@@ -5173,27 +7021,39 @@
           <t>Oesophagus wall, 190~200 um</t>
         </is>
       </c>
-      <c r="B160" s="9" t="n">
+      <c r="B160" s="13" t="n">
+        <v>1.037</v>
+      </c>
+      <c r="C160" s="10" t="n">
         <v>0.1030714170553999</v>
       </c>
-      <c r="C160" s="9" t="n">
+      <c r="D160" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E160" s="10" t="n">
         <v>0.08875562398853762</v>
       </c>
-      <c r="D160" s="9" t="n">
+      <c r="F160" s="10" t="n">
         <v>-13.88919787448705</v>
       </c>
-      <c r="F160" s="8" t="inlineStr">
+      <c r="H160" s="8" t="inlineStr">
         <is>
           <t>Oesophagus wall, 190~200 um</t>
         </is>
       </c>
-      <c r="G160" s="9" t="n">
+      <c r="I160" s="13" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="J160" s="10" t="n">
         <v>0.1006174687635021</v>
       </c>
-      <c r="H160" s="9" t="n">
+      <c r="K160" s="13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L160" s="10" t="n">
         <v>0.09116519793572886</v>
       </c>
-      <c r="I160" s="9" t="n">
+      <c r="M160" s="10" t="n">
         <v>-9.39426418089538</v>
       </c>
     </row>
@@ -5203,27 +7063,39 @@
           <t>Oesophagus wall, 200 um~surface</t>
         </is>
       </c>
-      <c r="B161" s="9" t="n">
+      <c r="B161" s="13" t="n">
+        <v>1.037</v>
+      </c>
+      <c r="C161" s="10" t="n">
         <v>49.78305164129575</v>
       </c>
-      <c r="C161" s="9" t="n">
+      <c r="D161" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E161" s="10" t="n">
         <v>42.87567226975619</v>
       </c>
-      <c r="D161" s="9" t="n">
+      <c r="F161" s="10" t="n">
         <v>-13.87496174663946</v>
       </c>
-      <c r="F161" s="8" t="inlineStr">
+      <c r="H161" s="8" t="inlineStr">
         <is>
           <t>Oesophagus wall, 200 um~surface</t>
         </is>
       </c>
-      <c r="G161" s="9" t="n">
+      <c r="I161" s="13" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="J161" s="10" t="n">
         <v>41.24658622120165</v>
       </c>
-      <c r="H161" s="9" t="n">
+      <c r="K161" s="13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L161" s="10" t="n">
         <v>37.37059873376737</v>
       </c>
-      <c r="I161" s="9" t="n">
+      <c r="M161" s="10" t="n">
         <v>-9.397110991556284</v>
       </c>
     </row>
@@ -5233,27 +7105,39 @@
           <t>Oesophagus contents</t>
         </is>
       </c>
-      <c r="B162" s="9" t="n">
+      <c r="B162" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="C162" s="10" t="n">
         <v>22.86999765708919</v>
       </c>
-      <c r="C162" s="9" t="n">
+      <c r="D162" s="13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E162" s="10" t="n">
         <v>19.44670555051056</v>
       </c>
-      <c r="D162" s="9" t="n">
+      <c r="F162" s="10" t="n">
         <v>-14.96848472792687</v>
       </c>
-      <c r="F162" s="8" t="inlineStr">
+      <c r="H162" s="8" t="inlineStr">
         <is>
           <t>Oesophagus contents</t>
         </is>
       </c>
-      <c r="G162" s="9" t="n">
+      <c r="I162" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="J162" s="10" t="n">
         <v>21.24000375262649</v>
       </c>
-      <c r="H162" s="9" t="n">
+      <c r="K162" s="13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L162" s="10" t="n">
         <v>18.9788469626333</v>
       </c>
-      <c r="I162" s="9" t="n">
+      <c r="M162" s="10" t="n">
         <v>-10.64574571797607</v>
       </c>
     </row>
@@ -5263,27 +7147,39 @@
           <t>Pancreas</t>
         </is>
       </c>
-      <c r="B163" s="9" t="n">
+      <c r="B163" s="13" t="n">
+        <v>1.044</v>
+      </c>
+      <c r="C163" s="10" t="n">
         <v>173.6312955899278</v>
       </c>
-      <c r="C163" s="9" t="n">
+      <c r="D163" s="13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E163" s="10" t="n">
         <v>115.540043560013</v>
       </c>
-      <c r="D163" s="9" t="n">
+      <c r="F163" s="10" t="n">
         <v>-33.45667140969296</v>
       </c>
-      <c r="F163" s="8" t="inlineStr">
+      <c r="H163" s="8" t="inlineStr">
         <is>
           <t>Ovary, left</t>
         </is>
       </c>
-      <c r="G163" s="9" t="n">
+      <c r="I163" s="13" t="n">
+        <v>1.051</v>
+      </c>
+      <c r="J163" s="10" t="n">
         <v>6.318272094822889</v>
       </c>
-      <c r="H163" s="9" t="n">
+      <c r="K163" s="13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L163" s="10" t="n">
         <v>5.638293540862303</v>
       </c>
-      <c r="I163" s="9" t="n">
+      <c r="M163" s="10" t="n">
         <v>-10.76209672131327</v>
       </c>
     </row>
@@ -5293,27 +7189,39 @@
           <t>Pituitary gland</t>
         </is>
       </c>
-      <c r="B164" s="9" t="n">
+      <c r="B164" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="C164" s="10" t="n">
         <v>0.6218196488304819</v>
       </c>
-      <c r="C164" s="9" t="n">
+      <c r="D164" s="13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E164" s="10" t="n">
         <v>0.5971625833320849</v>
       </c>
-      <c r="D164" s="9" t="n">
+      <c r="F164" s="10" t="n">
         <v>-3.965308195836521</v>
       </c>
-      <c r="F164" s="8" t="inlineStr">
+      <c r="H164" s="8" t="inlineStr">
         <is>
           <t>Ovary, right</t>
         </is>
       </c>
-      <c r="G164" s="9" t="n">
+      <c r="I164" s="13" t="n">
+        <v>1.051</v>
+      </c>
+      <c r="J164" s="10" t="n">
         <v>6.318275588501757</v>
       </c>
-      <c r="H164" s="9" t="n">
+      <c r="K164" s="13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L164" s="10" t="n">
         <v>5.638298869418686</v>
       </c>
-      <c r="I164" s="9" t="n">
+      <c r="M164" s="10" t="n">
         <v>-10.76206172963583</v>
       </c>
     </row>
@@ -5323,27 +7231,39 @@
           <t>Prostate</t>
         </is>
       </c>
-      <c r="B165" s="9" t="n">
+      <c r="B165" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="C165" s="10" t="n">
         <v>17.61814418639862</v>
       </c>
-      <c r="C165" s="9" t="n">
+      <c r="D165" s="13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E165" s="10" t="n">
         <v>19.11067222888436</v>
       </c>
-      <c r="D165" s="9" t="n">
+      <c r="F165" s="10" t="n">
         <v>8.471539491872175</v>
       </c>
-      <c r="F165" s="8" t="inlineStr">
+      <c r="H165" s="8" t="inlineStr">
         <is>
           <t>Pancreas</t>
         </is>
       </c>
-      <c r="G165" s="9" t="n">
+      <c r="I165" s="13" t="n">
+        <v>1.043</v>
+      </c>
+      <c r="J165" s="10" t="n">
         <v>144.5516199997302</v>
       </c>
-      <c r="H165" s="9" t="n">
+      <c r="K165" s="13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L165" s="10" t="n">
         <v>100.2789415883176</v>
       </c>
-      <c r="I165" s="9" t="n">
+      <c r="M165" s="10" t="n">
         <v>-30.62759062229484</v>
       </c>
     </row>
@@ -5353,27 +7273,39 @@
           <t>RST, head</t>
         </is>
       </c>
-      <c r="B166" s="9" t="n">
+      <c r="B166" s="13" t="n">
+        <v>0.9389999999999999</v>
+      </c>
+      <c r="C166" s="10" t="n">
         <v>975.6224151055426</v>
       </c>
-      <c r="C166" s="9" t="n">
+      <c r="D166" s="13" t="n">
+        <v>0.9833</v>
+      </c>
+      <c r="E166" s="10" t="n">
         <v>16326.10872032889</v>
       </c>
-      <c r="D166" s="9" t="n">
+      <c r="F166" s="10" t="n">
         <v>1573.404430602667</v>
       </c>
-      <c r="F166" s="8" t="inlineStr">
+      <c r="H166" s="8" t="inlineStr">
         <is>
           <t>Pituitary gland</t>
         </is>
       </c>
-      <c r="G166" s="9" t="n">
+      <c r="I166" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="J166" s="10" t="n">
         <v>0.6150875891179538</v>
       </c>
-      <c r="H166" s="9" t="n">
+      <c r="K166" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L166" s="10" t="n">
         <v>0.6067660241616125</v>
       </c>
-      <c r="I166" s="9" t="n">
+      <c r="M166" s="10" t="n">
         <v>-1.352907310042551</v>
       </c>
     </row>
@@ -5383,27 +7315,39 @@
           <t>RST, trunk</t>
         </is>
       </c>
-      <c r="B167" s="9" t="n">
+      <c r="B167" s="13" t="n">
+        <v>0.9389999999999999</v>
+      </c>
+      <c r="C167" s="10" t="n">
         <v>11176.90036487355</v>
       </c>
-      <c r="C167" s="9" t="n">
+      <c r="D167" s="13" t="n">
+        <v>0.9833</v>
+      </c>
+      <c r="E167" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D167" s="9" t="n">
+      <c r="F167" s="10" t="n">
         <v>-100</v>
       </c>
-      <c r="F167" s="8" t="inlineStr">
+      <c r="H167" s="8" t="inlineStr">
         <is>
           <t>RST, head</t>
         </is>
       </c>
-      <c r="G167" s="9" t="n">
+      <c r="I167" s="13" t="n">
+        <v>0.946</v>
+      </c>
+      <c r="J167" s="10" t="n">
         <v>844.5432189000495</v>
       </c>
-      <c r="H167" s="9" t="n">
+      <c r="K167" s="13" t="n">
+        <v>0.9298</v>
+      </c>
+      <c r="L167" s="10" t="n">
         <v>22844.22969252125</v>
       </c>
-      <c r="I167" s="9" t="n">
+      <c r="M167" s="10" t="n">
         <v>2604.921332773715</v>
       </c>
     </row>
@@ -5413,27 +7357,39 @@
           <t>RST, arms</t>
         </is>
       </c>
-      <c r="B168" s="9" t="n">
+      <c r="B168" s="13" t="n">
+        <v>0.9389999999999999</v>
+      </c>
+      <c r="C168" s="10" t="n">
         <v>1549.841514616755</v>
       </c>
-      <c r="C168" s="9" t="n">
+      <c r="D168" s="13" t="n">
+        <v>0.9833</v>
+      </c>
+      <c r="E168" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D168" s="9" t="n">
+      <c r="F168" s="10" t="n">
         <v>-100</v>
       </c>
-      <c r="F168" s="8" t="inlineStr">
+      <c r="H168" s="8" t="inlineStr">
         <is>
           <t>RST, trunk</t>
         </is>
       </c>
-      <c r="G168" s="9" t="n">
+      <c r="I168" s="13" t="n">
+        <v>0.946</v>
+      </c>
+      <c r="J168" s="10" t="n">
         <v>11513.36291310824</v>
       </c>
-      <c r="H168" s="9" t="n">
+      <c r="K168" s="13" t="n">
+        <v>0.9298</v>
+      </c>
+      <c r="L168" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="I168" s="9" t="n">
+      <c r="M168" s="10" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -5443,27 +7399,39 @@
           <t>RST, legs</t>
         </is>
       </c>
-      <c r="B169" s="9" t="n">
+      <c r="B169" s="13" t="n">
+        <v>0.9389999999999999</v>
+      </c>
+      <c r="C169" s="10" t="n">
         <v>4510.133508867629</v>
       </c>
-      <c r="C169" s="9" t="n">
+      <c r="D169" s="13" t="n">
+        <v>0.9833</v>
+      </c>
+      <c r="E169" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D169" s="9" t="n">
+      <c r="F169" s="10" t="n">
         <v>-100</v>
       </c>
-      <c r="F169" s="8" t="inlineStr">
+      <c r="H169" s="8" t="inlineStr">
         <is>
           <t>RST, arms</t>
         </is>
       </c>
-      <c r="G169" s="9" t="n">
+      <c r="I169" s="13" t="n">
+        <v>0.946</v>
+      </c>
+      <c r="J169" s="10" t="n">
         <v>2171.587829468973</v>
       </c>
-      <c r="H169" s="9" t="n">
+      <c r="K169" s="13" t="n">
+        <v>0.9298</v>
+      </c>
+      <c r="L169" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="I169" s="9" t="n">
+      <c r="M169" s="10" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -5473,27 +7441,39 @@
           <t>Salivary glands, left</t>
         </is>
       </c>
-      <c r="B170" s="9" t="n">
+      <c r="B170" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="C170" s="10" t="n">
         <v>44.0453586880419</v>
       </c>
-      <c r="C170" s="9" t="n">
+      <c r="D170" s="13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E170" s="10" t="n">
         <v>40.19878582876223</v>
       </c>
-      <c r="D170" s="9" t="n">
+      <c r="F170" s="10" t="n">
         <v>-8.733208160532021</v>
       </c>
-      <c r="F170" s="8" t="inlineStr">
+      <c r="H170" s="8" t="inlineStr">
         <is>
           <t>RST, legs</t>
         </is>
       </c>
-      <c r="G170" s="9" t="n">
+      <c r="I170" s="13" t="n">
+        <v>0.946</v>
+      </c>
+      <c r="J170" s="10" t="n">
         <v>7795.947644148337</v>
       </c>
-      <c r="H170" s="9" t="n">
+      <c r="K170" s="13" t="n">
+        <v>0.9298</v>
+      </c>
+      <c r="L170" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="I170" s="9" t="n">
+      <c r="M170" s="10" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -5503,27 +7483,39 @@
           <t>Salivary glands, right</t>
         </is>
       </c>
-      <c r="B171" s="9" t="n">
+      <c r="B171" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="C171" s="10" t="n">
         <v>44.04536236692604</v>
       </c>
-      <c r="C171" s="9" t="n">
+      <c r="D171" s="13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E171" s="10" t="n">
         <v>40.21630356152732</v>
       </c>
-      <c r="D171" s="9" t="n">
+      <c r="F171" s="10" t="n">
         <v>-8.693443758051547</v>
       </c>
-      <c r="F171" s="8" t="inlineStr">
+      <c r="H171" s="8" t="inlineStr">
         <is>
           <t>Salivary glands, left</t>
         </is>
       </c>
-      <c r="G171" s="9" t="n">
+      <c r="I171" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="J171" s="10" t="n">
         <v>35.87984162388322</v>
       </c>
-      <c r="H171" s="9" t="n">
+      <c r="K171" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L171" s="10" t="n">
         <v>35.03071275106278</v>
       </c>
-      <c r="I171" s="9" t="n">
+      <c r="M171" s="10" t="n">
         <v>-2.366590359348815</v>
       </c>
     </row>
@@ -5533,27 +7525,39 @@
           <t>Skin, head, insensitive</t>
         </is>
       </c>
-      <c r="B172" s="9" t="n">
+      <c r="B172" s="13" t="n">
+        <v>1.089</v>
+      </c>
+      <c r="C172" s="10" t="n">
         <v>259.2303086461898</v>
       </c>
-      <c r="C172" s="9" t="n">
+      <c r="D172" s="13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E172" s="10" t="n">
         <v>3021.408583228268</v>
       </c>
-      <c r="D172" s="9" t="n">
+      <c r="F172" s="10" t="n">
         <v>1065.530604429451</v>
       </c>
-      <c r="F172" s="8" t="inlineStr">
+      <c r="H172" s="8" t="inlineStr">
         <is>
           <t>Salivary glands, right</t>
         </is>
       </c>
-      <c r="G172" s="9" t="n">
+      <c r="I172" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="J172" s="10" t="n">
         <v>35.87987861730591</v>
       </c>
-      <c r="H172" s="9" t="n">
+      <c r="K172" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L172" s="10" t="n">
         <v>35.04695441449689</v>
       </c>
-      <c r="I172" s="9" t="n">
+      <c r="M172" s="10" t="n">
         <v>-2.321424249209344</v>
       </c>
     </row>
@@ -5563,27 +7567,39 @@
           <t>Skin, head, sensitive, 50~100 um</t>
         </is>
       </c>
-      <c r="B173" s="9" t="n">
+      <c r="B173" s="13" t="n">
+        <v>1.089</v>
+      </c>
+      <c r="C173" s="10" t="n">
         <v>8.47000153082754</v>
       </c>
-      <c r="C173" s="9" t="n">
+      <c r="D173" s="13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E173" s="10" t="n">
         <v>91.83380330053728</v>
       </c>
-      <c r="D173" s="9" t="n">
+      <c r="F173" s="10" t="n">
         <v>984.2241641432726</v>
       </c>
-      <c r="F173" s="8" t="inlineStr">
+      <c r="H173" s="8" t="inlineStr">
         <is>
           <t>Skin, head, insensitive</t>
         </is>
       </c>
-      <c r="G173" s="9" t="n">
+      <c r="I173" s="13" t="n">
+        <v>1.088</v>
+      </c>
+      <c r="J173" s="10" t="n">
         <v>155.582078378946</v>
       </c>
-      <c r="H173" s="9" t="n">
+      <c r="K173" s="13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="L173" s="10" t="n">
         <v>2212.981936505788</v>
       </c>
-      <c r="I173" s="9" t="n">
+      <c r="M173" s="10" t="n">
         <v>1322.388722122418</v>
       </c>
     </row>
@@ -5593,27 +7609,39 @@
           <t>Skin, trunk, insensitive</t>
         </is>
       </c>
-      <c r="B174" s="9" t="n">
+      <c r="B174" s="13" t="n">
+        <v>1.089</v>
+      </c>
+      <c r="C174" s="10" t="n">
         <v>1271.006475196992</v>
       </c>
-      <c r="C174" s="9" t="n">
+      <c r="D174" s="13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E174" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D174" s="9" t="n">
+      <c r="F174" s="10" t="n">
         <v>-100</v>
       </c>
-      <c r="F174" s="8" t="inlineStr">
+      <c r="H174" s="8" t="inlineStr">
         <is>
           <t>Skin, head, sensitive, 50~100 um</t>
         </is>
       </c>
-      <c r="G174" s="9" t="n">
+      <c r="I174" s="13" t="n">
+        <v>1.088</v>
+      </c>
+      <c r="J174" s="10" t="n">
         <v>6.324483800426981</v>
       </c>
-      <c r="H174" s="9" t="n">
+      <c r="K174" s="13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="L174" s="10" t="n">
         <v>84.21138654649137</v>
       </c>
-      <c r="I174" s="9" t="n">
+      <c r="M174" s="10" t="n">
         <v>1231.513989186059</v>
       </c>
     </row>
@@ -5623,27 +7651,39 @@
           <t>Skin, trunk, sensitive, 50~100 um</t>
         </is>
       </c>
-      <c r="B175" s="9" t="n">
+      <c r="B175" s="13" t="n">
+        <v>1.089</v>
+      </c>
+      <c r="C175" s="10" t="n">
         <v>38.41782704156981</v>
       </c>
-      <c r="C175" s="9" t="n">
+      <c r="D175" s="13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E175" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D175" s="9" t="n">
+      <c r="F175" s="10" t="n">
         <v>-100</v>
       </c>
-      <c r="F175" s="8" t="inlineStr">
+      <c r="H175" s="8" t="inlineStr">
         <is>
           <t>Skin, trunk, insensitive</t>
         </is>
       </c>
-      <c r="G175" s="9" t="n">
+      <c r="I175" s="13" t="n">
+        <v>1.088</v>
+      </c>
+      <c r="J175" s="10" t="n">
         <v>871.6032649399771</v>
       </c>
-      <c r="H175" s="9" t="n">
+      <c r="K175" s="13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="L175" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="I175" s="9" t="n">
+      <c r="M175" s="10" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -5653,27 +7693,39 @@
           <t>Skin, arms, insensitive</t>
         </is>
       </c>
-      <c r="B176" s="9" t="n">
+      <c r="B176" s="13" t="n">
+        <v>1.089</v>
+      </c>
+      <c r="C176" s="10" t="n">
         <v>575.7089401467681</v>
       </c>
-      <c r="C176" s="9" t="n">
+      <c r="D176" s="13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E176" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D176" s="9" t="n">
+      <c r="F176" s="10" t="n">
         <v>-100</v>
       </c>
-      <c r="F176" s="8" t="inlineStr">
+      <c r="H176" s="8" t="inlineStr">
         <is>
           <t>Skin, trunk, sensitive, 50~100 um</t>
         </is>
       </c>
-      <c r="G176" s="9" t="n">
+      <c r="I176" s="13" t="n">
+        <v>1.088</v>
+      </c>
+      <c r="J176" s="10" t="n">
         <v>32.36827260895312</v>
       </c>
-      <c r="H176" s="9" t="n">
+      <c r="K176" s="13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="L176" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="I176" s="9" t="n">
+      <c r="M176" s="10" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -5683,27 +7735,39 @@
           <t>Skin, arms, sensitive, 50~100 um</t>
         </is>
       </c>
-      <c r="B177" s="9" t="n">
+      <c r="B177" s="13" t="n">
+        <v>1.089</v>
+      </c>
+      <c r="C177" s="10" t="n">
         <v>18.84302051824883</v>
       </c>
-      <c r="C177" s="9" t="n">
+      <c r="D177" s="13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E177" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D177" s="9" t="n">
+      <c r="F177" s="10" t="n">
         <v>-100</v>
       </c>
-      <c r="F177" s="8" t="inlineStr">
+      <c r="H177" s="8" t="inlineStr">
         <is>
           <t>Skin, arms, insensitive</t>
         </is>
       </c>
-      <c r="G177" s="9" t="n">
+      <c r="I177" s="13" t="n">
+        <v>1.088</v>
+      </c>
+      <c r="J177" s="10" t="n">
         <v>380.905394359025</v>
       </c>
-      <c r="H177" s="9" t="n">
+      <c r="K177" s="13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="L177" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="I177" s="9" t="n">
+      <c r="M177" s="10" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -5713,27 +7777,39 @@
           <t>Skin, legs, insensitive</t>
         </is>
       </c>
-      <c r="B178" s="9" t="n">
+      <c r="B178" s="13" t="n">
+        <v>1.089</v>
+      </c>
+      <c r="C178" s="10" t="n">
         <v>1259.982015955084</v>
       </c>
-      <c r="C178" s="9" t="n">
+      <c r="D178" s="13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E178" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D178" s="9" t="n">
+      <c r="F178" s="10" t="n">
         <v>-100</v>
       </c>
-      <c r="F178" s="8" t="inlineStr">
+      <c r="H178" s="8" t="inlineStr">
         <is>
           <t>Skin, arms, sensitive, 50~100 um</t>
         </is>
       </c>
-      <c r="G178" s="9" t="n">
+      <c r="I178" s="13" t="n">
+        <v>1.088</v>
+      </c>
+      <c r="J178" s="10" t="n">
         <v>15.59845875365075</v>
       </c>
-      <c r="H178" s="9" t="n">
+      <c r="K178" s="13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="L178" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="I178" s="9" t="n">
+      <c r="M178" s="10" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -5743,27 +7819,39 @@
           <t>Skin, legs, sensitive, 50~100 um</t>
         </is>
       </c>
-      <c r="B179" s="9" t="n">
+      <c r="B179" s="13" t="n">
+        <v>1.089</v>
+      </c>
+      <c r="C179" s="10" t="n">
         <v>37.78988120926353</v>
       </c>
-      <c r="C179" s="9" t="n">
+      <c r="D179" s="13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E179" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D179" s="9" t="n">
+      <c r="F179" s="10" t="n">
         <v>-100</v>
       </c>
-      <c r="F179" s="8" t="inlineStr">
+      <c r="H179" s="8" t="inlineStr">
         <is>
           <t>Skin, legs, insensitive</t>
         </is>
       </c>
-      <c r="G179" s="9" t="n">
+      <c r="I179" s="13" t="n">
+        <v>1.088</v>
+      </c>
+      <c r="J179" s="10" t="n">
         <v>924.5843396886984</v>
       </c>
-      <c r="H179" s="9" t="n">
+      <c r="K179" s="13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="L179" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="I179" s="9" t="n">
+      <c r="M179" s="10" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -5773,27 +7861,39 @@
           <t>Spinal cord</t>
         </is>
       </c>
-      <c r="B180" s="9" t="n">
+      <c r="B180" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="C180" s="10" t="n">
         <v>37.95172331616698</v>
       </c>
-      <c r="C180" s="9" t="n">
+      <c r="D180" s="13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E180" s="10" t="n">
         <v>32.84842395808656</v>
       </c>
-      <c r="D180" s="9" t="n">
+      <c r="F180" s="10" t="n">
         <v>-13.44681851616072</v>
       </c>
-      <c r="F180" s="8" t="inlineStr">
+      <c r="H180" s="8" t="inlineStr">
         <is>
           <t>Skin, legs, sensitive, 50~100 um</t>
         </is>
       </c>
-      <c r="G180" s="9" t="n">
+      <c r="I180" s="13" t="n">
+        <v>1.088</v>
+      </c>
+      <c r="J180" s="10" t="n">
         <v>35.02462939650827</v>
       </c>
-      <c r="H180" s="9" t="n">
+      <c r="K180" s="13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="L180" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="I180" s="9" t="n">
+      <c r="M180" s="10" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -5803,27 +7903,39 @@
           <t>Spleen</t>
         </is>
       </c>
-      <c r="B181" s="9" t="n">
+      <c r="B181" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="C181" s="10" t="n">
         <v>228.3999950695007</v>
       </c>
-      <c r="C181" s="9" t="n">
+      <c r="D181" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E181" s="10" t="n">
         <v>194.0007915883084</v>
       </c>
-      <c r="D181" s="9" t="n">
+      <c r="F181" s="10" t="n">
         <v>-15.06094755856925</v>
       </c>
-      <c r="F181" s="8" t="inlineStr">
+      <c r="H181" s="8" t="inlineStr">
         <is>
           <t>Spinal cord</t>
         </is>
       </c>
-      <c r="G181" s="9" t="n">
+      <c r="I181" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="J181" s="10" t="n">
         <v>19.09830624380668</v>
       </c>
-      <c r="H181" s="9" t="n">
+      <c r="K181" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L181" s="10" t="n">
         <v>18.19153458808441</v>
       </c>
-      <c r="I181" s="9" t="n">
+      <c r="M181" s="10" t="n">
         <v>-4.747916617036744</v>
       </c>
     </row>
@@ -5833,27 +7945,39 @@
           <t>Teeth</t>
         </is>
       </c>
-      <c r="B182" s="9" t="n">
+      <c r="B182" s="13" t="n">
+        <v>2.688</v>
+      </c>
+      <c r="C182" s="10" t="n">
         <v>50.72662087588219</v>
       </c>
-      <c r="C182" s="9" t="n">
+      <c r="D182" s="13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E182" s="10" t="n">
         <v>35.61686179834471</v>
       </c>
-      <c r="D182" s="9" t="n">
+      <c r="F182" s="10" t="n">
         <v>-29.78664617638933</v>
       </c>
-      <c r="F182" s="8" t="inlineStr">
+      <c r="H182" s="8" t="inlineStr">
         <is>
           <t>Spleen</t>
         </is>
       </c>
-      <c r="G182" s="9" t="n">
+      <c r="I182" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="J182" s="10" t="n">
         <v>187.3999945542682</v>
       </c>
-      <c r="H182" s="9" t="n">
+      <c r="K182" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="L182" s="10" t="n">
         <v>151.2087953072944</v>
       </c>
-      <c r="I182" s="9" t="n">
+      <c r="M182" s="10" t="n">
         <v>-19.31227337175478</v>
       </c>
     </row>
@@ -5863,27 +7987,39 @@
           <t>Teeth, retention region</t>
         </is>
       </c>
-      <c r="B183" s="9" t="n">
+      <c r="B183" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="C183" s="10" t="n">
         <v>0.04313799171157471</v>
       </c>
-      <c r="C183" s="9" t="n">
+      <c r="D183" s="13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E183" s="10" t="n">
         <v>0.0383935902735709</v>
       </c>
-      <c r="D183" s="9" t="n">
+      <c r="F183" s="10" t="n">
         <v>-10.99819729607579</v>
       </c>
-      <c r="F183" s="8" t="inlineStr">
+      <c r="H183" s="8" t="inlineStr">
         <is>
           <t>Teeth</t>
         </is>
       </c>
-      <c r="G183" s="9" t="n">
+      <c r="I183" s="13" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="J183" s="10" t="n">
         <v>40.5623965368835</v>
       </c>
-      <c r="H183" s="9" t="n">
+      <c r="K183" s="13" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="L183" s="10" t="n">
         <v>29.42913485468649</v>
       </c>
-      <c r="I183" s="9" t="n">
+      <c r="M183" s="10" t="n">
         <v>-27.44724827112597</v>
       </c>
     </row>
@@ -5893,27 +8029,39 @@
           <t>Testis, left</t>
         </is>
       </c>
-      <c r="B184" s="9" t="n">
+      <c r="B184" s="13" t="n">
+        <v>1.041</v>
+      </c>
+      <c r="C184" s="10" t="n">
         <v>18.61675321733138</v>
       </c>
-      <c r="C184" s="9" t="n">
+      <c r="D184" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E184" s="10" t="n">
         <v>15.39997571196156</v>
       </c>
-      <c r="D184" s="9" t="n">
+      <c r="F184" s="10" t="n">
         <v>-17.27893939301482</v>
       </c>
-      <c r="F184" s="8" t="inlineStr">
+      <c r="H184" s="8" t="inlineStr">
         <is>
           <t>Teeth, retention region</t>
         </is>
       </c>
-      <c r="G184" s="9" t="n">
+      <c r="I184" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="J184" s="10" t="n">
         <v>0.03608964951674797</v>
       </c>
-      <c r="H184" s="9" t="n">
+      <c r="K184" s="13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L184" s="10" t="n">
         <v>0.03320892431511876</v>
       </c>
-      <c r="I184" s="9" t="n">
+      <c r="M184" s="10" t="n">
         <v>-7.982136818182088</v>
       </c>
     </row>
@@ -5923,27 +8071,39 @@
           <t>Testis, right</t>
         </is>
       </c>
-      <c r="B185" s="9" t="n">
+      <c r="B185" s="13" t="n">
+        <v>1.041</v>
+      </c>
+      <c r="C185" s="10" t="n">
         <v>18.61674983677091</v>
       </c>
-      <c r="C185" s="9" t="n">
+      <c r="D185" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E185" s="10" t="n">
         <v>15.40196284824228</v>
       </c>
-      <c r="D185" s="9" t="n">
+      <c r="F185" s="10" t="n">
         <v>-17.26825045572097</v>
       </c>
-      <c r="F185" s="8" t="inlineStr">
+      <c r="H185" s="8" t="inlineStr">
         <is>
           <t>Thymus</t>
         </is>
       </c>
-      <c r="G185" s="9" t="n">
+      <c r="I185" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="J185" s="10" t="n">
         <v>20.50279131498598</v>
       </c>
-      <c r="H185" s="9" t="n">
+      <c r="K185" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L185" s="10" t="n">
         <v>19.382607877709</v>
       </c>
-      <c r="I185" s="9" t="n">
+      <c r="M185" s="10" t="n">
         <v>-5.463565521725894</v>
       </c>
     </row>
@@ -5953,27 +8113,39 @@
           <t>Thymus</t>
         </is>
       </c>
-      <c r="B186" s="9" t="n">
+      <c r="B186" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="C186" s="10" t="n">
         <v>25.90902854878556</v>
       </c>
-      <c r="C186" s="9" t="n">
+      <c r="D186" s="13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E186" s="10" t="n">
         <v>22.22297070977168</v>
       </c>
-      <c r="D186" s="9" t="n">
+      <c r="F186" s="10" t="n">
         <v>-14.22692414759277</v>
       </c>
-      <c r="F186" s="8" t="inlineStr">
+      <c r="H186" s="8" t="inlineStr">
         <is>
           <t>Thyroid</t>
         </is>
       </c>
-      <c r="G186" s="9" t="n">
+      <c r="I186" s="13" t="n">
+        <v>1.051</v>
+      </c>
+      <c r="J186" s="10" t="n">
         <v>19.45530683430379</v>
       </c>
-      <c r="H186" s="9" t="n">
+      <c r="K186" s="13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L186" s="10" t="n">
         <v>10.31559865205495</v>
       </c>
-      <c r="I186" s="9" t="n">
+      <c r="M186" s="10" t="n">
         <v>-46.97796986749968</v>
       </c>
     </row>
@@ -5983,27 +8155,39 @@
           <t>Thyroid</t>
         </is>
       </c>
-      <c r="B187" s="9" t="n">
+      <c r="B187" s="13" t="n">
+        <v>1.051</v>
+      </c>
+      <c r="C187" s="10" t="n">
         <v>23.35052428911649</v>
       </c>
-      <c r="C187" s="9" t="n">
+      <c r="D187" s="13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E187" s="10" t="n">
         <v>13.51644535395652</v>
       </c>
-      <c r="D187" s="9" t="n">
+      <c r="F187" s="10" t="n">
         <v>-42.11502411422754</v>
       </c>
-      <c r="F187" s="8" t="inlineStr">
+      <c r="H187" s="8" t="inlineStr">
         <is>
           <t>Tongue, upper (food)</t>
         </is>
       </c>
-      <c r="G187" s="9" t="n">
+      <c r="I187" s="13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="J187" s="10" t="n">
         <v>20.99518908485927</v>
       </c>
-      <c r="H187" s="9" t="n">
+      <c r="K187" s="13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L187" s="10" t="n">
         <v>19.36297875550504</v>
       </c>
-      <c r="I187" s="9" t="n">
+      <c r="M187" s="10" t="n">
         <v>-7.774211143119921</v>
       </c>
     </row>
@@ -6013,27 +8197,39 @@
           <t>Tongue, upper (food)</t>
         </is>
       </c>
-      <c r="B188" s="9" t="n">
+      <c r="B188" s="13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="C188" s="10" t="n">
         <v>20.99303754407316</v>
       </c>
-      <c r="C188" s="9" t="n">
+      <c r="D188" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E188" s="10" t="n">
         <v>18.71204725544514</v>
       </c>
-      <c r="D188" s="9" t="n">
+      <c r="F188" s="10" t="n">
         <v>-10.86546091216797</v>
       </c>
-      <c r="F188" s="8" t="inlineStr">
+      <c r="H188" s="8" t="inlineStr">
         <is>
           <t>Tongue, lower</t>
         </is>
       </c>
-      <c r="G188" s="9" t="n">
+      <c r="I188" s="13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="J188" s="10" t="n">
         <v>40.4153302562648</v>
       </c>
-      <c r="H188" s="9" t="n">
+      <c r="K188" s="13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L188" s="10" t="n">
         <v>37.09374249794044</v>
       </c>
-      <c r="I188" s="9" t="n">
+      <c r="M188" s="10" t="n">
         <v>-8.218633219777969</v>
       </c>
     </row>
@@ -6043,27 +8239,39 @@
           <t>Tongue, lower</t>
         </is>
       </c>
-      <c r="B189" s="9" t="n">
+      <c r="B189" s="13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="C189" s="10" t="n">
         <v>54.55215826284434</v>
       </c>
-      <c r="C189" s="9" t="n">
+      <c r="D189" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E189" s="10" t="n">
         <v>48.32402519712944</v>
       </c>
-      <c r="D189" s="9" t="n">
+      <c r="F189" s="10" t="n">
         <v>-11.41684080711597</v>
       </c>
-      <c r="F189" s="8" t="inlineStr">
+      <c r="H189" s="8" t="inlineStr">
         <is>
           <t>Tonsils</t>
         </is>
       </c>
-      <c r="G189" s="9" t="n">
+      <c r="I189" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="J189" s="10" t="n">
         <v>3.075414924309439</v>
       </c>
-      <c r="H189" s="9" t="n">
+      <c r="K189" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L189" s="10" t="n">
         <v>3.005954741799077</v>
       </c>
-      <c r="I189" s="9" t="n">
+      <c r="M189" s="10" t="n">
         <v>-2.258562965319503</v>
       </c>
     </row>
@@ -6073,27 +8281,39 @@
           <t>Tonsils</t>
         </is>
       </c>
-      <c r="B190" s="9" t="n">
+      <c r="B190" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="C190" s="10" t="n">
         <v>3.109094748914422</v>
       </c>
-      <c r="C190" s="9" t="n">
+      <c r="D190" s="13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E190" s="10" t="n">
         <v>2.948005220152291</v>
       </c>
-      <c r="D190" s="9" t="n">
+      <c r="F190" s="10" t="n">
         <v>-5.181235754181417</v>
       </c>
-      <c r="F190" s="8" t="inlineStr">
+      <c r="H190" s="8" t="inlineStr">
         <is>
           <t>Ureter, left</t>
         </is>
       </c>
-      <c r="G190" s="9" t="n">
+      <c r="I190" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="J190" s="10" t="n">
         <v>7.688548223295017</v>
       </c>
-      <c r="H190" s="9" t="n">
+      <c r="K190" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L190" s="10" t="n">
         <v>7.268478044225119</v>
       </c>
-      <c r="I190" s="9" t="n">
+      <c r="M190" s="10" t="n">
         <v>-5.463582549916978</v>
       </c>
     </row>
@@ -6103,27 +8323,39 @@
           <t>Ureter, left</t>
         </is>
       </c>
-      <c r="B191" s="9" t="n">
+      <c r="B191" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="C191" s="10" t="n">
         <v>8.809067046598571</v>
       </c>
-      <c r="C191" s="9" t="n">
+      <c r="D191" s="13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E191" s="10" t="n">
         <v>7.92259504789644</v>
       </c>
-      <c r="D191" s="9" t="n">
+      <c r="F191" s="10" t="n">
         <v>-10.0631768836908</v>
       </c>
-      <c r="F191" s="8" t="inlineStr">
+      <c r="H191" s="8" t="inlineStr">
         <is>
           <t>Ureter, right</t>
         </is>
       </c>
-      <c r="G191" s="9" t="n">
+      <c r="I191" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="J191" s="10" t="n">
         <v>7.688548546825454</v>
       </c>
-      <c r="H191" s="9" t="n">
+      <c r="K191" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L191" s="10" t="n">
         <v>7.268479971758198</v>
       </c>
-      <c r="I191" s="9" t="n">
+      <c r="M191" s="10" t="n">
         <v>-5.46356145778256</v>
       </c>
     </row>
@@ -6133,27 +8365,39 @@
           <t>Ureter, right</t>
         </is>
       </c>
-      <c r="B192" s="9" t="n">
+      <c r="B192" s="13" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="C192" s="10" t="n">
         <v>7.772708595145708</v>
       </c>
-      <c r="C192" s="9" t="n">
+      <c r="D192" s="13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E192" s="10" t="n">
         <v>6.990526271815036</v>
       </c>
-      <c r="D192" s="9" t="n">
+      <c r="F192" s="10" t="n">
         <v>-10.06318857520489</v>
       </c>
-      <c r="F192" s="8" t="inlineStr">
+      <c r="H192" s="8" t="inlineStr">
         <is>
           <t>Urinary bladder wall, insensitive</t>
         </is>
       </c>
-      <c r="G192" s="9" t="n">
+      <c r="I192" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="J192" s="10" t="n">
         <v>39.45905292020476</v>
       </c>
-      <c r="H192" s="9" t="n">
+      <c r="K192" s="13" t="n">
+        <v>1.041</v>
+      </c>
+      <c r="L192" s="10" t="n">
         <v>35.47669586782713</v>
       </c>
-      <c r="I192" s="9" t="n">
+      <c r="M192" s="10" t="n">
         <v>-10.09237870060104</v>
       </c>
     </row>
@@ -6163,27 +8407,39 @@
           <t>Urinary bladder wall, insensitive</t>
         </is>
       </c>
-      <c r="B193" s="9" t="n">
+      <c r="B193" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="C193" s="10" t="n">
         <v>49.78112323614282</v>
       </c>
-      <c r="C193" s="9" t="n">
+      <c r="D193" s="13" t="n">
+        <v>1.041</v>
+      </c>
+      <c r="E193" s="10" t="n">
         <v>42.13423245573929</v>
       </c>
-      <c r="D193" s="9" t="n">
+      <c r="F193" s="10" t="n">
         <v>-15.36102498959207</v>
       </c>
-      <c r="F193" s="8" t="inlineStr">
+      <c r="H193" s="8" t="inlineStr">
         <is>
           <t>Urinary bladder wall, sensitive, 118/116~193/185 um</t>
         </is>
       </c>
-      <c r="G193" s="9" t="n">
+      <c r="I193" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="J193" s="10" t="n">
         <v>1.345473855991772</v>
       </c>
-      <c r="H193" s="9" t="n">
+      <c r="K193" s="13" t="n">
+        <v>1.041</v>
+      </c>
+      <c r="L193" s="10" t="n">
         <v>2.079175649030298</v>
       </c>
-      <c r="I193" s="9" t="n">
+      <c r="M193" s="10" t="n">
         <v>54.53110736943313</v>
       </c>
     </row>
@@ -6193,27 +8449,39 @@
           <t>Urinary bladder wall, sensitive, 118/116~193/185 um</t>
         </is>
       </c>
-      <c r="B194" s="9" t="n">
+      <c r="B194" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="C194" s="10" t="n">
         <v>1.317737831556219</v>
       </c>
-      <c r="C194" s="9" t="n">
+      <c r="D194" s="13" t="n">
+        <v>1.041</v>
+      </c>
+      <c r="E194" s="10" t="n">
         <v>1.779590726703723</v>
       </c>
-      <c r="D194" s="9" t="n">
+      <c r="F194" s="10" t="n">
         <v>35.04892127154508</v>
       </c>
-      <c r="F194" s="8" t="inlineStr">
+      <c r="H194" s="8" t="inlineStr">
         <is>
           <t>Urinary bladder contents</t>
         </is>
       </c>
-      <c r="G194" s="9" t="n">
+      <c r="I194" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="J194" s="10" t="n">
         <v>199.9999984226185</v>
       </c>
-      <c r="H194" s="9" t="n">
+      <c r="K194" s="13" t="n">
+        <v>1.042</v>
+      </c>
+      <c r="L194" s="10" t="n">
         <v>184.253746519952</v>
       </c>
-      <c r="I194" s="9" t="n">
+      <c r="M194" s="10" t="n">
         <v>-7.873126013427852</v>
       </c>
     </row>
@@ -6223,27 +8491,39 @@
           <t>Urinary bladder contents</t>
         </is>
       </c>
-      <c r="B195" s="9" t="n">
+      <c r="B195" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="C195" s="10" t="n">
         <v>200.0000029860481</v>
       </c>
-      <c r="C195" s="9" t="n">
+      <c r="D195" s="13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E195" s="10" t="n">
         <v>168.4105541235137</v>
       </c>
-      <c r="D195" s="9" t="n">
+      <c r="F195" s="10" t="n">
         <v>-15.79472419544818</v>
       </c>
-      <c r="F195" s="8" t="inlineStr">
+      <c r="H195" s="8" t="inlineStr">
         <is>
           <t>Uterus</t>
         </is>
       </c>
-      <c r="G195" s="9" t="n">
+      <c r="I195" s="13" t="n">
+        <v>1.021</v>
+      </c>
+      <c r="J195" s="10" t="n">
         <v>81.99316851617225</v>
       </c>
-      <c r="H195" s="9" t="n">
+      <c r="K195" s="13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="L195" s="10" t="n">
         <v>51.43397802708195</v>
       </c>
-      <c r="I195" s="9" t="n">
+      <c r="M195" s="10" t="n">
         <v>-37.27041050141005</v>
       </c>
     </row>
@@ -6253,38 +8533,50 @@
           <t>Air inside body</t>
         </is>
       </c>
-      <c r="B196" s="9" t="n">
+      <c r="B196" s="13" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C196" s="10" t="n">
         <v>0.1401650804136397</v>
       </c>
-      <c r="C196" s="9" t="n">
+      <c r="D196" s="13" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="E196" s="10" t="n">
         <v>0.1257642289710419</v>
       </c>
-      <c r="D196" s="9" t="n">
+      <c r="F196" s="10" t="n">
         <v>-10.27420767005567</v>
       </c>
-      <c r="F196" s="8" t="inlineStr">
+      <c r="H196" s="8" t="inlineStr">
         <is>
           <t>Air inside body</t>
         </is>
       </c>
-      <c r="G196" s="9" t="n">
+      <c r="I196" s="13" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="J196" s="10" t="n">
         <v>0.03600626171428052</v>
       </c>
-      <c r="H196" s="9" t="n">
+      <c r="K196" s="13" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="L196" s="10" t="n">
         <v>0.03387082009572941</v>
       </c>
-      <c r="I196" s="9" t="n">
+      <c r="M196" s="10" t="n">
         <v>-5.930750699687807</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="F9:I9"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="F4:I4"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="H4:M4"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="H9:M9"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A2:M2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
